--- a/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
+++ b/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-038-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42306D88-6FD8-4A84-93C1-C28BC91718EC}"/>
+  <xr:revisionPtr revIDLastSave="422" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5D559AA-9825-4149-9AC4-E308E382366B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MasterDataTable!$A$2:$BM$277</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,8 +39,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={FF16B357-339F-45F1-8E08-77BC469B5CFA}</author>
+  </authors>
+  <commentList>
+    <comment ref="BI12" authorId="0" shapeId="0" xr:uid="{FF16B357-339F-45F1-8E08-77BC469B5CFA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Override MPC feed rate with CSFR</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="84">
   <si>
     <t>Batch Data</t>
   </si>
@@ -284,6 +301,15 @@
   </si>
   <si>
     <t>Reactor was found to be contaminated</t>
+  </si>
+  <si>
+    <t>Changed to CSFR flow rate until Julia code was run at 4pm</t>
+  </si>
+  <si>
+    <t>CSFR Flow rates were used</t>
+  </si>
+  <si>
+    <t>Contaminated on day 3</t>
   </si>
 </sst>
 </file>
@@ -966,7 +992,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1049,6 +1075,17 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="41" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="14" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1100,10 +1137,6 @@
     <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1192,6 +1225,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Yu Luo" id="{39B0911F-58E9-4732-93E1-F7F715DFAAAC}" userId="S::yu.8.luo@gsk.com::5e93f0cf-7e56-492e-afc9-2cfd7b5fd269" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1489,13 +1528,22 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="BI12" dT="2024-07-20T18:22:09.75" personId="{39B0911F-58E9-4732-93E1-F7F715DFAAAC}" id="{FF16B357-339F-45F1-8E08-77BC469B5CFA}">
+    <text>Override MPC feed rate with CSFR</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BP46"/>
   <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="5" width="10.6640625" customWidth="1"/>
+    <col min="2" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" customWidth="1"/>
     <col min="6" max="6" width="16.88671875" customWidth="1"/>
     <col min="7" max="18" width="12.6640625" customWidth="1"/>
     <col min="19" max="19" width="15.109375" bestFit="1" customWidth="1"/>
@@ -1506,88 +1554,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:68" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67" t="s">
+      <c r="A1" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
-      <c r="V1" s="68"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="69"/>
-      <c r="AE1" s="80" t="s">
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="77"/>
+      <c r="T1" s="77"/>
+      <c r="U1" s="77"/>
+      <c r="V1" s="77"/>
+      <c r="W1" s="77"/>
+      <c r="X1" s="77"/>
+      <c r="Y1" s="77"/>
+      <c r="Z1" s="77"/>
+      <c r="AA1" s="77"/>
+      <c r="AB1" s="77"/>
+      <c r="AC1" s="77"/>
+      <c r="AD1" s="78"/>
+      <c r="AE1" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="81"/>
-      <c r="AG1" s="81"/>
-      <c r="AH1" s="81"/>
-      <c r="AI1" s="81"/>
-      <c r="AJ1" s="81"/>
-      <c r="AK1" s="81"/>
-      <c r="AL1" s="81"/>
-      <c r="AM1" s="81"/>
-      <c r="AN1" s="81"/>
-      <c r="AO1" s="81"/>
-      <c r="AP1" s="81"/>
-      <c r="AQ1" s="81"/>
-      <c r="AR1" s="81"/>
-      <c r="AS1" s="81"/>
-      <c r="AT1" s="82"/>
-      <c r="AU1" s="75" t="s">
+      <c r="AF1" s="90"/>
+      <c r="AG1" s="90"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="90"/>
+      <c r="AJ1" s="90"/>
+      <c r="AK1" s="90"/>
+      <c r="AL1" s="90"/>
+      <c r="AM1" s="90"/>
+      <c r="AN1" s="90"/>
+      <c r="AO1" s="90"/>
+      <c r="AP1" s="90"/>
+      <c r="AQ1" s="90"/>
+      <c r="AR1" s="90"/>
+      <c r="AS1" s="90"/>
+      <c r="AT1" s="91"/>
+      <c r="AU1" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="75"/>
-      <c r="AX1" s="75"/>
-      <c r="AY1" s="76"/>
-      <c r="AZ1" s="77" t="s">
+      <c r="AV1" s="84"/>
+      <c r="AW1" s="84"/>
+      <c r="AX1" s="84"/>
+      <c r="AY1" s="85"/>
+      <c r="AZ1" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="BA1" s="78"/>
-      <c r="BB1" s="79"/>
-      <c r="BC1" s="73" t="s">
+      <c r="BA1" s="87"/>
+      <c r="BB1" s="88"/>
+      <c r="BC1" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="BD1" s="74"/>
-      <c r="BE1" s="74"/>
-      <c r="BF1" s="74"/>
-      <c r="BG1" s="74"/>
-      <c r="BH1" s="74"/>
-      <c r="BI1" s="74"/>
-      <c r="BJ1" s="74"/>
-      <c r="BK1" s="74"/>
-      <c r="BL1" s="74"/>
-      <c r="BM1" s="74"/>
-      <c r="BN1" s="70" t="s">
+      <c r="BD1" s="83"/>
+      <c r="BE1" s="83"/>
+      <c r="BF1" s="83"/>
+      <c r="BG1" s="83"/>
+      <c r="BH1" s="83"/>
+      <c r="BI1" s="83"/>
+      <c r="BJ1" s="83"/>
+      <c r="BK1" s="83"/>
+      <c r="BL1" s="83"/>
+      <c r="BM1" s="83"/>
+      <c r="BN1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="BO1" s="71"/>
-      <c r="BP1" s="72"/>
+      <c r="BO1" s="80"/>
+      <c r="BP1" s="81"/>
     </row>
     <row r="2" spans="1:68" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
@@ -1602,7 +1650,7 @@
       <c r="D2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="72" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="26" t="s">
@@ -1809,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="84">
+      <c r="F3" s="66">
         <v>45491.472488425898</v>
       </c>
       <c r="G3" s="3">
@@ -2010,17 +2058,16 @@
       <c r="A4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="83">
+      <c r="C4">
         <v>12</v>
       </c>
-      <c r="D4" s="83">
-        <v>0</v>
-      </c>
-      <c r="E4" s="83"/>
-      <c r="F4" s="85">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="67">
         <v>45491.474918981497</v>
       </c>
       <c r="G4">
@@ -2221,17 +2268,16 @@
       <c r="A5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="83">
+      <c r="C5">
         <v>12</v>
       </c>
-      <c r="D5" s="83">
-        <v>0</v>
-      </c>
-      <c r="E5" s="83"/>
-      <c r="F5" s="85">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="67">
         <v>45491.477488425902</v>
       </c>
       <c r="G5">
@@ -2441,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="86">
+      <c r="F6" s="68">
         <v>45491.480787036999</v>
       </c>
       <c r="G6" s="5">
@@ -2652,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="85">
+      <c r="F7" s="67">
         <v>45492.338194444441</v>
       </c>
       <c r="G7" s="3">
@@ -2859,19 +2905,19 @@
       <c r="A8" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="83">
+      <c r="C8">
         <v>12</v>
       </c>
-      <c r="D8" s="83">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" s="83" t="s">
+      <c r="E8" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="85">
+      <c r="F8" s="67">
         <v>45492.34097222222</v>
       </c>
       <c r="G8">
@@ -3078,17 +3124,16 @@
       <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="83">
+      <c r="C9">
         <v>12</v>
       </c>
-      <c r="D9" s="83">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="83"/>
-      <c r="F9" s="85">
+      <c r="F9" s="67">
         <v>45492.34375</v>
       </c>
       <c r="G9">
@@ -3291,17 +3336,16 @@
       <c r="A10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="83">
+      <c r="C10">
         <v>12</v>
       </c>
-      <c r="D10" s="83">
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" s="83"/>
-      <c r="F10" s="85">
+      <c r="F10" s="67">
         <v>45492.345833333333</v>
       </c>
       <c r="G10" s="5">
@@ -3515,8 +3559,10 @@
       <c r="D11" s="3">
         <v>2</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="84">
+      <c r="E11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="66">
         <v>45493.525694444397</v>
       </c>
       <c r="G11">
@@ -3614,7 +3660,7 @@
       </c>
       <c r="AM11" s="56">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1.9587601193460299E-2</v>
       </c>
       <c r="AN11" s="6">
         <v>16</v>
@@ -3656,9 +3702,15 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AZ11" s="8"/>
-      <c r="BA11" s="9"/>
-      <c r="BB11" s="28"/>
-      <c r="BC11" s="8">
+      <c r="BA11" s="9">
+        <f>BJ11*24*60/BE11</f>
+        <v>1.6416168450565701E-2</v>
+      </c>
+      <c r="BB11" s="28">
+        <f>BM11/BE11</f>
+        <v>7.0438155546433375E-3</v>
+      </c>
+      <c r="BC11" s="71">
         <f t="shared" si="0"/>
         <v>1.1494711169999998E-2</v>
       </c>
@@ -3680,15 +3732,14 @@
       </c>
       <c r="BH11" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>28.206145718582832</v>
       </c>
       <c r="BI11" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(B11="Python",AZ11*BE11/24/60,"")</f>
         <v/>
       </c>
       <c r="BJ11" s="10">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1.9587601193460299E-2</v>
       </c>
       <c r="BK11" s="45" t="str">
         <f t="shared" si="6"/>
@@ -3699,37 +3750,38 @@
         <v/>
       </c>
       <c r="BM11" s="10">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <v>12.1026345792793</v>
       </c>
       <c r="BN11" s="34">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>50.876886216780001</v>
       </c>
       <c r="BO11" s="48">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1.9587601193460299E-2</v>
       </c>
       <c r="BP11" s="39">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>12.1026345792793</v>
       </c>
     </row>
     <row r="12" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="83">
+      <c r="C12">
         <v>12</v>
       </c>
-      <c r="D12" s="83">
+      <c r="D12">
         <v>2</v>
       </c>
-      <c r="E12" s="83"/>
-      <c r="F12" s="85">
+      <c r="E12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="67">
         <v>45493.528472222199</v>
       </c>
       <c r="G12">
@@ -3827,7 +3879,7 @@
       </c>
       <c r="AM12" s="57">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1.190824173E-2</v>
       </c>
       <c r="AN12" s="22">
         <v>16</v>
@@ -3868,9 +3920,11 @@
       <c r="AY12" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AZ12" s="11"/>
+      <c r="AZ12" s="11">
+        <v>4.4999999999999997E-3</v>
+      </c>
       <c r="BB12" s="29"/>
-      <c r="BC12" s="11">
+      <c r="BC12" s="69">
         <f t="shared" si="0"/>
         <v>1.190824173E-2</v>
       </c>
@@ -3892,11 +3946,10 @@
       </c>
       <c r="BH12" s="24">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BI12" s="24">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <v>17.147868091199999</v>
+      </c>
+      <c r="BI12" s="73">
+        <v>1.190824173E-2</v>
       </c>
       <c r="BJ12" s="24" t="str">
         <f t="shared" si="13"/>
@@ -3916,11 +3969,11 @@
       </c>
       <c r="BN12" s="35">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>30.930498</v>
       </c>
       <c r="BO12" s="49">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <f>IF(BI12&lt;&gt;"",BI12,IF(BJ12&lt;&gt;"",BJ12,BK12))</f>
+        <v>1.190824173E-2</v>
       </c>
       <c r="BP12" s="37">
         <f t="shared" si="7"/>
@@ -3940,8 +3993,10 @@
       <c r="D13" s="5">
         <v>2</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="86">
+      <c r="E13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="68">
         <v>45493.536805555603</v>
       </c>
       <c r="G13">
@@ -4039,7 +4094,7 @@
       </c>
       <c r="AM13" s="58">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1.1710864169999998E-2</v>
       </c>
       <c r="AN13" s="7">
         <v>18</v>
@@ -4080,9 +4135,11 @@
       <c r="AY13" s="13">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AZ13" s="12"/>
+      <c r="AZ13" s="12">
+        <v>4.5000000009706104E-3</v>
+      </c>
       <c r="BB13" s="30"/>
-      <c r="BC13" s="12">
+      <c r="BC13" s="70">
         <f t="shared" si="0"/>
         <v>1.1710864169999998E-2</v>
       </c>
@@ -4104,11 +4161,10 @@
       </c>
       <c r="BH13" s="14">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BI13" s="14">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <v>16.863644404799995</v>
+      </c>
+      <c r="BI13" s="74">
+        <v>1.1710864169999998E-2</v>
       </c>
       <c r="BJ13" s="14" t="str">
         <f t="shared" si="13"/>
@@ -4128,11 +4184,11 @@
       </c>
       <c r="BN13" s="36">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>30.41782901298701</v>
       </c>
       <c r="BO13" s="50">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1.1710864169999998E-2</v>
       </c>
       <c r="BP13" s="38">
         <f t="shared" si="7"/>
@@ -4153,62 +4209,126 @@
         <v>3</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="84"/>
+      <c r="F14" s="66">
+        <v>45494.550289351901</v>
+      </c>
       <c r="G14" s="3">
         <v>1505.08</v>
       </c>
       <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
+      <c r="I14" s="6">
+        <v>1446.18</v>
+      </c>
+      <c r="J14" s="6">
+        <v>24</v>
+      </c>
+      <c r="K14" s="6">
+        <v>23.1</v>
+      </c>
+      <c r="L14" s="6">
+        <v>96</v>
+      </c>
+      <c r="M14" s="6">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="N14" s="6">
+        <v>350</v>
+      </c>
+      <c r="O14" s="6">
+        <v>1.58</v>
+      </c>
+      <c r="P14" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>2.0099999999999998</v>
+      </c>
       <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
-      <c r="AB14" s="6"/>
-      <c r="AC14" s="6"/>
-      <c r="AD14" s="19"/>
-      <c r="AE14" s="53"/>
-      <c r="AF14" s="6"/>
-      <c r="AG14" s="6"/>
+      <c r="S14" s="6">
+        <v>0</v>
+      </c>
+      <c r="T14" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="U14" s="6">
+        <v>2.76</v>
+      </c>
+      <c r="V14" s="6">
+        <v>7.218</v>
+      </c>
+      <c r="W14" s="6">
+        <v>139.80000000000001</v>
+      </c>
+      <c r="X14" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>2.92</v>
+      </c>
+      <c r="Z14" s="6">
+        <v>149</v>
+      </c>
+      <c r="AA14" s="6">
+        <v>55.4</v>
+      </c>
+      <c r="AB14" s="6">
+        <v>122.6</v>
+      </c>
+      <c r="AC14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="19">
+        <v>7.2590000000000003</v>
+      </c>
+      <c r="AE14" s="53">
+        <v>300</v>
+      </c>
+      <c r="AF14" s="6">
+        <v>49.2</v>
+      </c>
+      <c r="AG14" s="6">
+        <v>7.19</v>
+      </c>
       <c r="AH14" s="56">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI14" s="6"/>
-      <c r="AJ14" s="6"/>
-      <c r="AK14" s="6"/>
-      <c r="AL14" s="6"/>
+        <v>0.49200000000000005</v>
+      </c>
+      <c r="AI14" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ14" s="6">
+        <v>27.664999999999999</v>
+      </c>
+      <c r="AK14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="6">
+        <v>4</v>
+      </c>
       <c r="AM14" s="56">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN14" s="6"/>
-      <c r="AO14" s="6"/>
-      <c r="AP14" s="6"/>
+      <c r="AN14" s="6">
+        <v>42</v>
+      </c>
+      <c r="AO14" s="6">
+        <v>31</v>
+      </c>
+      <c r="AP14" s="6">
+        <v>668</v>
+      </c>
       <c r="AQ14" s="56">
         <f t="shared" si="20"/>
-        <v>-16</v>
+        <v>26</v>
       </c>
       <c r="AR14" s="56">
         <f t="shared" si="21"/>
-        <v>-18</v>
+        <v>13</v>
       </c>
       <c r="AS14" s="56">
         <f t="shared" si="22"/>
-        <v>695</v>
+        <v>27</v>
       </c>
       <c r="AT14" s="31">
         <v>15</v>
@@ -4233,23 +4353,23 @@
       <c r="BB14" s="28"/>
       <c r="BC14" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.2090528449999999E-2</v>
       </c>
       <c r="BD14" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.410360967999999</v>
       </c>
       <c r="BE14" s="9">
         <f t="shared" si="17"/>
-        <v>1640</v>
-      </c>
-      <c r="BF14" s="10" t="e">
+        <v>1744.665</v>
+      </c>
+      <c r="BF14" s="10">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BG14" s="10" t="e">
+        <v>2.4073389447257783E-2</v>
+      </c>
+      <c r="BG14" s="10">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>2.4705882352941175E-2</v>
       </c>
       <c r="BH14" s="10">
         <f t="shared" si="5"/>
@@ -4292,72 +4412,135 @@
       <c r="A15" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="83" t="s">
+      <c r="B15" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="83">
+      <c r="C15">
         <v>12</v>
       </c>
-      <c r="D15" s="83">
+      <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" s="83"/>
-      <c r="F15" s="85"/>
+      <c r="F15" s="67">
+        <v>45494.554664351897</v>
+      </c>
       <c r="G15">
         <v>1505.08</v>
       </c>
       <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
+      <c r="I15" s="22">
+        <v>1350.49</v>
+      </c>
+      <c r="J15" s="22">
+        <v>24</v>
+      </c>
+      <c r="K15" s="22">
+        <v>22.7</v>
+      </c>
+      <c r="L15" s="22">
+        <v>94.4</v>
+      </c>
+      <c r="M15" s="22">
+        <v>16.5</v>
+      </c>
+      <c r="N15" s="22">
+        <v>372</v>
+      </c>
+      <c r="O15" s="22">
+        <v>2.68</v>
+      </c>
+      <c r="P15" s="22">
+        <v>0.4</v>
+      </c>
+      <c r="Q15" s="22">
+        <v>0.01</v>
+      </c>
       <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="22"/>
-      <c r="AC15" s="22"/>
-      <c r="AD15" s="20"/>
-      <c r="AE15" s="54"/>
-      <c r="AF15" s="22"/>
-      <c r="AG15" s="22"/>
+      <c r="S15" s="22">
+        <v>0.08</v>
+      </c>
+      <c r="T15" s="22">
+        <v>0.1</v>
+      </c>
+      <c r="U15" s="22">
+        <v>3.17</v>
+      </c>
+      <c r="V15" s="22">
+        <v>7.3440000000000003</v>
+      </c>
+      <c r="W15" s="22">
+        <v>146.69999999999999</v>
+      </c>
+      <c r="X15" s="22">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="22">
+        <v>3.6</v>
+      </c>
+      <c r="Z15" s="22">
+        <v>167.8</v>
+      </c>
+      <c r="AA15" s="22">
+        <v>78</v>
+      </c>
+      <c r="AB15" s="22">
+        <v>128.6</v>
+      </c>
+      <c r="AC15" s="22">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="20">
+        <v>7.3869999999999996</v>
+      </c>
+      <c r="AE15" s="54">
+        <v>300</v>
+      </c>
+      <c r="AF15" s="22">
+        <v>52.2</v>
+      </c>
+      <c r="AG15" s="22">
+        <v>7.29</v>
+      </c>
       <c r="AH15" s="57">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI15" s="22"/>
-      <c r="AJ15" s="22"/>
-      <c r="AK15" s="22"/>
-      <c r="AL15" s="22"/>
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="AI15" s="22">
+        <v>34</v>
+      </c>
+      <c r="AJ15" s="22">
+        <v>37.567</v>
+      </c>
+      <c r="AK15" s="22">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="22">
+        <v>4</v>
+      </c>
       <c r="AM15" s="57">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN15" s="22"/>
-      <c r="AO15" s="22"/>
-      <c r="AP15" s="22"/>
+      <c r="AN15" s="22">
+        <v>33</v>
+      </c>
+      <c r="AO15" s="22">
+        <v>34</v>
+      </c>
+      <c r="AP15" s="22">
+        <v>743</v>
+      </c>
       <c r="AQ15" s="57">
         <f t="shared" si="20"/>
-        <v>-16</v>
+        <v>17</v>
       </c>
       <c r="AR15" s="57">
         <f t="shared" si="21"/>
-        <v>-20</v>
+        <v>14</v>
       </c>
       <c r="AS15" s="57">
         <f t="shared" si="22"/>
-        <v>762</v>
+        <v>19</v>
       </c>
       <c r="AT15" s="32">
         <v>15</v>
@@ -4382,23 +4565,23 @@
       <c r="BB15" s="29"/>
       <c r="BC15" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.1907741269999999E-2</v>
       </c>
       <c r="BD15" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.147147428799997</v>
       </c>
       <c r="BE15" s="23">
         <f t="shared" si="17"/>
-        <v>1640</v>
-      </c>
-      <c r="BF15" s="24" t="e">
+        <v>1748.567</v>
+      </c>
+      <c r="BF15" s="24">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BG15" s="24" t="e">
+        <v>1.8872596817851417E-2</v>
+      </c>
+      <c r="BG15" s="24">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>1.9411764705882354E-2</v>
       </c>
       <c r="BH15" s="24">
         <f t="shared" si="5"/>
@@ -4418,7 +4601,7 @@
       </c>
       <c r="BL15" s="24">
         <f t="shared" si="19"/>
-        <v>12.3</v>
+        <v>13.070538324999999</v>
       </c>
       <c r="BM15" s="24" t="str">
         <f t="shared" si="14"/>
@@ -4434,7 +4617,7 @@
       </c>
       <c r="BP15" s="37">
         <f t="shared" si="7"/>
-        <v>12.3</v>
+        <v>13.070538324999999</v>
       </c>
     </row>
     <row r="16" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4450,8 +4633,10 @@
       <c r="D16" s="5">
         <v>3</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="86"/>
+      <c r="E16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="68"/>
       <c r="G16" s="5">
         <v>1505.08</v>
       </c>
@@ -4478,35 +4663,55 @@
       <c r="AB16" s="7"/>
       <c r="AC16" s="7"/>
       <c r="AD16" s="21"/>
-      <c r="AE16" s="55"/>
-      <c r="AF16" s="7"/>
-      <c r="AG16" s="7"/>
+      <c r="AE16" s="55">
+        <v>300</v>
+      </c>
+      <c r="AF16" s="7">
+        <v>11.1</v>
+      </c>
+      <c r="AG16" s="7">
+        <v>7.31</v>
+      </c>
       <c r="AH16" s="58">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI16" s="7"/>
-      <c r="AJ16" s="7"/>
-      <c r="AK16" s="7"/>
-      <c r="AL16" s="7"/>
+        <v>0.111</v>
+      </c>
+      <c r="AI16" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ16" s="7">
+        <v>38.723999999999997</v>
+      </c>
+      <c r="AK16" s="7">
+        <v>8.9086999999999996</v>
+      </c>
+      <c r="AL16" s="7">
+        <v>3</v>
+      </c>
       <c r="AM16" s="58">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN16" s="7"/>
-      <c r="AO16" s="7"/>
-      <c r="AP16" s="7"/>
+      <c r="AN16" s="7">
+        <v>34</v>
+      </c>
+      <c r="AO16" s="7">
+        <v>30</v>
+      </c>
+      <c r="AP16" s="7">
+        <v>591</v>
+      </c>
       <c r="AQ16" s="58">
         <f t="shared" si="20"/>
-        <v>-18</v>
+        <v>16</v>
       </c>
       <c r="AR16" s="58">
         <f t="shared" si="21"/>
-        <v>-18</v>
+        <v>12</v>
       </c>
       <c r="AS16" s="58">
         <f t="shared" si="22"/>
-        <v>608</v>
+        <v>17</v>
       </c>
       <c r="AT16" s="33">
         <v>15</v>
@@ -4539,15 +4744,15 @@
       </c>
       <c r="BE16" s="13">
         <f t="shared" si="17"/>
-        <v>1640</v>
-      </c>
-      <c r="BF16" s="14" t="e">
+        <v>1754.6327000000001</v>
+      </c>
+      <c r="BF16" s="14">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BG16" s="14" t="e">
+        <v>1.9377274799449479E-2</v>
+      </c>
+      <c r="BG16" s="14">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>0.02</v>
       </c>
       <c r="BH16" s="14">
         <f t="shared" si="5"/>
@@ -4567,7 +4772,7 @@
       </c>
       <c r="BL16" s="14">
         <f t="shared" si="19"/>
-        <v>12.3</v>
+        <v>13.15974525</v>
       </c>
       <c r="BM16" s="14" t="str">
         <f t="shared" si="14"/>
@@ -4583,24 +4788,23 @@
       </c>
       <c r="BP16" s="37">
         <f t="shared" si="7"/>
-        <v>12.3</v>
+        <v>13.15974525</v>
       </c>
     </row>
     <row r="17" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="83" t="s">
+      <c r="B17" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="83">
+      <c r="C17">
         <v>12</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17">
         <v>4</v>
       </c>
-      <c r="E17" s="83"/>
-      <c r="F17" s="85"/>
+      <c r="F17" s="67"/>
       <c r="G17">
         <v>2119.61</v>
       </c>
@@ -4647,15 +4851,15 @@
       <c r="AP17" s="6"/>
       <c r="AQ17" s="56">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="AR17" s="56">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="AS17" s="56">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="AT17" s="31">
         <v>15</v>
@@ -4739,17 +4943,16 @@
       <c r="A18" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="83" t="s">
+      <c r="B18" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="83">
+      <c r="C18">
         <v>12</v>
       </c>
-      <c r="D18" s="83">
+      <c r="D18">
         <v>4</v>
       </c>
-      <c r="E18" s="83"/>
-      <c r="F18" s="85"/>
+      <c r="F18" s="67"/>
       <c r="G18">
         <v>2119.61</v>
       </c>
@@ -4796,15 +4999,15 @@
       <c r="AP18" s="22"/>
       <c r="AQ18" s="57">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="AR18" s="57">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="AS18" s="57">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>743</v>
       </c>
       <c r="AT18" s="32">
         <v>15</v>
@@ -4888,17 +5091,16 @@
       <c r="A19" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="83" t="s">
+      <c r="B19" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="83">
+      <c r="C19">
         <v>12</v>
       </c>
-      <c r="D19" s="83">
+      <c r="D19">
         <v>4</v>
       </c>
-      <c r="E19" s="83"/>
-      <c r="F19" s="85"/>
+      <c r="F19" s="67"/>
       <c r="G19">
         <v>2119.61</v>
       </c>
@@ -4945,15 +5147,15 @@
       <c r="AP19" s="7"/>
       <c r="AQ19" s="58">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="AR19" s="58">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AS19" s="58">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="AT19" s="33">
         <v>15</v>
@@ -5047,7 +5249,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="3"/>
-      <c r="F20" s="84"/>
+      <c r="F20" s="66"/>
       <c r="G20" s="3">
         <v>2716.05</v>
       </c>
@@ -5186,17 +5388,16 @@
       <c r="A21" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="83" t="s">
+      <c r="B21" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="83">
+      <c r="C21">
         <v>12</v>
       </c>
-      <c r="D21" s="83">
+      <c r="D21">
         <v>5</v>
       </c>
-      <c r="E21" s="83"/>
-      <c r="F21" s="85"/>
+      <c r="F21" s="67"/>
       <c r="G21">
         <v>2716.05</v>
       </c>
@@ -5345,7 +5546,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="86"/>
+      <c r="F22" s="68"/>
       <c r="G22" s="5">
         <v>2716.05</v>
       </c>
@@ -5484,17 +5685,16 @@
       <c r="A23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="83" t="s">
+      <c r="B23" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="83">
+      <c r="C23">
         <v>12</v>
       </c>
-      <c r="D23" s="83">
+      <c r="D23">
         <v>6</v>
       </c>
-      <c r="E23" s="83"/>
-      <c r="F23" s="85"/>
+      <c r="F23" s="67"/>
       <c r="G23">
         <v>3307.9</v>
       </c>
@@ -5633,17 +5833,16 @@
       <c r="A24" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="83" t="s">
+      <c r="B24" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="83">
+      <c r="C24">
         <v>12</v>
       </c>
-      <c r="D24" s="83">
+      <c r="D24">
         <v>6</v>
       </c>
-      <c r="E24" s="83"/>
-      <c r="F24" s="85"/>
+      <c r="F24" s="67"/>
       <c r="G24">
         <v>3307.9</v>
       </c>
@@ -5782,17 +5981,16 @@
       <c r="A25" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="B25" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="83">
+      <c r="C25">
         <v>12</v>
       </c>
-      <c r="D25" s="83">
+      <c r="D25">
         <v>6</v>
       </c>
-      <c r="E25" s="83"/>
-      <c r="F25" s="85"/>
+      <c r="F25" s="67"/>
       <c r="G25">
         <v>3307.9</v>
       </c>
@@ -5941,7 +6139,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="3"/>
-      <c r="F26" s="84"/>
+      <c r="F26" s="66"/>
       <c r="G26" s="3">
         <v>3888.32</v>
       </c>
@@ -6080,17 +6278,16 @@
       <c r="A27" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="83" t="s">
+      <c r="B27" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="83">
+      <c r="C27">
         <v>12</v>
       </c>
-      <c r="D27" s="83">
+      <c r="D27">
         <v>7</v>
       </c>
-      <c r="E27" s="83"/>
-      <c r="F27" s="85"/>
+      <c r="F27" s="67"/>
       <c r="G27">
         <v>3888.32</v>
       </c>
@@ -6239,7 +6436,7 @@
         <v>7</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="F28" s="86"/>
+      <c r="F28" s="68"/>
       <c r="G28" s="5">
         <v>3888.32</v>
       </c>
@@ -6378,17 +6575,16 @@
       <c r="A29" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="83" t="s">
+      <c r="B29" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="83">
+      <c r="C29">
         <v>12</v>
       </c>
-      <c r="D29" s="83">
+      <c r="D29">
         <v>8</v>
       </c>
-      <c r="E29" s="83"/>
-      <c r="F29" s="85"/>
+      <c r="F29" s="67"/>
       <c r="G29">
         <v>4309.7</v>
       </c>
@@ -6527,17 +6723,16 @@
       <c r="A30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="83" t="s">
+      <c r="B30" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="83">
+      <c r="C30">
         <v>12</v>
       </c>
-      <c r="D30" s="83">
+      <c r="D30">
         <v>8</v>
       </c>
-      <c r="E30" s="83"/>
-      <c r="F30" s="85"/>
+      <c r="F30" s="67"/>
       <c r="G30">
         <v>4309.7</v>
       </c>
@@ -6676,17 +6871,16 @@
       <c r="A31" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="83" t="s">
+      <c r="B31" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="83">
+      <c r="C31">
         <v>12</v>
       </c>
-      <c r="D31" s="83">
+      <c r="D31">
         <v>8</v>
       </c>
-      <c r="E31" s="83"/>
-      <c r="F31" s="85"/>
+      <c r="F31" s="67"/>
       <c r="G31">
         <v>4309.7</v>
       </c>
@@ -6835,7 +7029,7 @@
         <v>9</v>
       </c>
       <c r="E32" s="3"/>
-      <c r="F32" s="84"/>
+      <c r="F32" s="66"/>
       <c r="G32" s="3">
         <v>4805.7299999999996</v>
       </c>
@@ -6974,17 +7168,16 @@
       <c r="A33" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="83" t="s">
+      <c r="B33" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="83">
+      <c r="C33">
         <v>12</v>
       </c>
-      <c r="D33" s="83">
+      <c r="D33">
         <v>9</v>
       </c>
-      <c r="E33" s="83"/>
-      <c r="F33" s="85"/>
+      <c r="F33" s="67"/>
       <c r="G33">
         <v>4805.7299999999996</v>
       </c>
@@ -7133,7 +7326,7 @@
         <v>9</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="86"/>
+      <c r="F34" s="68"/>
       <c r="G34" s="5">
         <v>4805.7299999999996</v>
       </c>
@@ -7272,17 +7465,16 @@
       <c r="A35" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="83" t="s">
+      <c r="B35" t="s">
         <v>75</v>
       </c>
-      <c r="C35" s="83">
+      <c r="C35">
         <v>12</v>
       </c>
-      <c r="D35" s="83">
+      <c r="D35">
         <v>10</v>
       </c>
-      <c r="E35" s="83"/>
-      <c r="F35" s="85"/>
+      <c r="F35" s="67"/>
       <c r="G35" s="62">
         <v>5497.99</v>
       </c>
@@ -7421,17 +7613,16 @@
       <c r="A36" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="83" t="s">
+      <c r="B36" t="s">
         <v>78</v>
       </c>
-      <c r="C36" s="83">
+      <c r="C36">
         <v>12</v>
       </c>
-      <c r="D36" s="83">
+      <c r="D36">
         <v>10</v>
       </c>
-      <c r="E36" s="83"/>
-      <c r="F36" s="85"/>
+      <c r="F36" s="67"/>
       <c r="G36" s="62">
         <v>5497.99</v>
       </c>
@@ -7570,17 +7761,16 @@
       <c r="A37" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B37" s="83" t="s">
+      <c r="B37" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="83">
+      <c r="C37">
         <v>12</v>
       </c>
-      <c r="D37" s="83">
+      <c r="D37">
         <v>10</v>
       </c>
-      <c r="E37" s="83"/>
-      <c r="F37" s="85"/>
+      <c r="F37" s="67"/>
       <c r="G37" s="62">
         <v>5497.99</v>
       </c>
@@ -7729,7 +7919,7 @@
         <v>11</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="84"/>
+      <c r="F38" s="66"/>
       <c r="G38" s="63">
         <v>6057.48</v>
       </c>
@@ -7868,17 +8058,16 @@
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="83" t="s">
+      <c r="B39" t="s">
         <v>78</v>
       </c>
-      <c r="C39" s="83">
+      <c r="C39">
         <v>12</v>
       </c>
-      <c r="D39" s="83">
+      <c r="D39">
         <v>11</v>
       </c>
-      <c r="E39" s="83"/>
-      <c r="F39" s="85"/>
+      <c r="F39" s="67"/>
       <c r="G39" s="62">
         <v>6057.48</v>
       </c>
@@ -8025,7 +8214,7 @@
         <v>11</v>
       </c>
       <c r="E40" s="5"/>
-      <c r="F40" s="86"/>
+      <c r="F40" s="68"/>
       <c r="G40" s="62">
         <v>6057.48</v>
       </c>
@@ -8173,7 +8362,7 @@
         <v>12</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="F41" s="84"/>
+      <c r="F41" s="66"/>
       <c r="G41" s="63">
         <v>6478.05</v>
       </c>
@@ -8312,17 +8501,16 @@
       <c r="A42" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="83" t="s">
+      <c r="B42" t="s">
         <v>78</v>
       </c>
-      <c r="C42" s="83">
+      <c r="C42">
         <v>12</v>
       </c>
-      <c r="D42" s="83">
+      <c r="D42">
         <v>12</v>
       </c>
-      <c r="E42" s="83"/>
-      <c r="F42" s="85"/>
+      <c r="F42" s="67"/>
       <c r="G42" s="62">
         <v>6478.05</v>
       </c>
@@ -8470,7 +8658,7 @@
         <v>12</v>
       </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="86"/>
+      <c r="F43" s="68"/>
       <c r="G43" s="64">
         <v>6478.05</v>
       </c>
@@ -8645,6 +8833,7 @@
   <ignoredErrors>
     <ignoredError sqref="BE8:BE10" formulaRange="1"/>
   </ignoredErrors>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -8659,15 +8848,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -8890,7 +9070,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
@@ -8908,15 +9088,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8935,13 +9116,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
     <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
+++ b/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-038-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="466" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AE022AA-A055-466E-BA9B-E50BF3D932D7}"/>
+  <xr:revisionPtr revIDLastSave="537" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{297C3AE4-042B-4D04-A2F8-688BF6A89B74}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="85">
   <si>
     <t>Batch Data</t>
   </si>
@@ -316,6 +316,12 @@
   </si>
   <si>
     <t>CSFR Flow rates were used</t>
+  </si>
+  <si>
+    <t>NMPC-bound FER805 was re-routed to LMPC</t>
+  </si>
+  <si>
+    <t>CSFR Flow rates were used, Reactor was found to be contaminated the next day</t>
   </si>
 </sst>
 </file>
@@ -523,10 +529,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="42">
@@ -1041,7 +1049,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1107,45 +1115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="38" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1171,15 +1140,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="39" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="38" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="38" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="38" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1190,15 +1150,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1216,8 +1167,67 @@
     </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="41" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1311,7 +1321,7 @@
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Yu Luo" id="{39B0911F-58E9-4732-93E1-F7F715DFAAAC}" userId="S::yu.8.luo@gsk.com::5e93f0cf-7e56-492e-afc9-2cfd7b5fd269" providerId="AD"/>
-  <person displayName="Zach Hatzenbeller" id="{C69CAE13-5997-41D2-9ADC-7A401FC5421C}" userId="S::zach.a.hatzenbeller@gsk.com::4c73105f-9498-483c-b968-fc87645f65e2" providerId="AD"/>
+  <person displayName="Zach Hatzenbeller" id="{7997E0CA-849D-4189-9CD6-84C395997746}" userId="S::zach.a.hatzenbeller@gsk.com::4c73105f-9498-483c-b968-fc87645f65e2" providerId="AD"/>
 </personList>
 </file>
 
@@ -1615,7 +1625,7 @@
   <threadedComment ref="BI12" dT="2024-07-20T18:22:09.75" personId="{39B0911F-58E9-4732-93E1-F7F715DFAAAC}" id="{FF16B357-339F-45F1-8E08-77BC469B5CFA}">
     <text>Override MPC feed rate with CSFR</text>
   </threadedComment>
-  <threadedComment ref="J14" dT="2024-07-22T14:36:12.43" personId="{C69CAE13-5997-41D2-9ADC-7A401FC5421C}" id="{85F96BBA-2507-4D48-80E4-7214138DEA92}">
+  <threadedComment ref="J14" dT="2024-07-22T14:36:12.43" personId="{7997E0CA-849D-4189-9CD6-84C395997746}" id="{85F96BBA-2507-4D48-80E4-7214138DEA92}">
     <text>Updated on day 4 due to DCA pullback being fixed</text>
   </threadedComment>
 </ThreadedComments>
@@ -1625,104 +1635,104 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BP28"/>
-  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="53" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="18" width="12.7109375" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="65" width="12.7109375" customWidth="1"/>
-    <col min="66" max="66" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="16.28515625" customWidth="1"/>
+    <col min="2" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="49" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" customWidth="1"/>
+    <col min="7" max="18" width="12.6640625" customWidth="1"/>
+    <col min="19" max="19" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="65" width="12.6640625" customWidth="1"/>
+    <col min="66" max="66" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="54" t="s">
+    <row r="1" spans="1:68" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
-      <c r="AD1" s="56"/>
-      <c r="AE1" s="63" t="s">
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="103"/>
+      <c r="T1" s="103"/>
+      <c r="U1" s="103"/>
+      <c r="V1" s="103"/>
+      <c r="W1" s="103"/>
+      <c r="X1" s="103"/>
+      <c r="Y1" s="103"/>
+      <c r="Z1" s="103"/>
+      <c r="AA1" s="103"/>
+      <c r="AB1" s="103"/>
+      <c r="AC1" s="103"/>
+      <c r="AD1" s="104"/>
+      <c r="AE1" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="64"/>
-      <c r="AG1" s="64"/>
-      <c r="AH1" s="64"/>
-      <c r="AI1" s="64"/>
-      <c r="AJ1" s="64"/>
-      <c r="AK1" s="64"/>
-      <c r="AL1" s="64"/>
-      <c r="AM1" s="64"/>
-      <c r="AN1" s="64"/>
-      <c r="AO1" s="64"/>
-      <c r="AP1" s="64"/>
-      <c r="AQ1" s="64"/>
-      <c r="AR1" s="64"/>
-      <c r="AS1" s="64"/>
-      <c r="AT1" s="65"/>
-      <c r="AU1" s="102" t="s">
+      <c r="AF1" s="118"/>
+      <c r="AG1" s="118"/>
+      <c r="AH1" s="118"/>
+      <c r="AI1" s="118"/>
+      <c r="AJ1" s="118"/>
+      <c r="AK1" s="118"/>
+      <c r="AL1" s="118"/>
+      <c r="AM1" s="118"/>
+      <c r="AN1" s="118"/>
+      <c r="AO1" s="118"/>
+      <c r="AP1" s="118"/>
+      <c r="AQ1" s="118"/>
+      <c r="AR1" s="118"/>
+      <c r="AS1" s="118"/>
+      <c r="AT1" s="119"/>
+      <c r="AU1" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="AV1" s="103"/>
-      <c r="AW1" s="103"/>
-      <c r="AX1" s="103"/>
-      <c r="AY1" s="104"/>
-      <c r="AZ1" s="60" t="s">
+      <c r="AV1" s="112"/>
+      <c r="AW1" s="112"/>
+      <c r="AX1" s="112"/>
+      <c r="AY1" s="113"/>
+      <c r="AZ1" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="BA1" s="61"/>
-      <c r="BB1" s="62"/>
-      <c r="BC1" s="89" t="s">
+      <c r="BA1" s="115"/>
+      <c r="BB1" s="116"/>
+      <c r="BC1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="BD1" s="90"/>
-      <c r="BE1" s="90"/>
-      <c r="BF1" s="90"/>
-      <c r="BG1" s="90"/>
-      <c r="BH1" s="90"/>
-      <c r="BI1" s="90"/>
-      <c r="BJ1" s="90"/>
-      <c r="BK1" s="90"/>
-      <c r="BL1" s="90"/>
-      <c r="BM1" s="91"/>
-      <c r="BN1" s="57" t="s">
+      <c r="BD1" s="109"/>
+      <c r="BE1" s="109"/>
+      <c r="BF1" s="109"/>
+      <c r="BG1" s="109"/>
+      <c r="BH1" s="109"/>
+      <c r="BI1" s="109"/>
+      <c r="BJ1" s="109"/>
+      <c r="BK1" s="109"/>
+      <c r="BL1" s="109"/>
+      <c r="BM1" s="110"/>
+      <c r="BN1" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="BO1" s="58"/>
-      <c r="BP1" s="59"/>
+      <c r="BO1" s="106"/>
+      <c r="BP1" s="107"/>
     </row>
-    <row r="2" spans="1:68" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:68" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>7</v>
       </c>
@@ -1744,70 +1754,70 @@
       <c r="G2" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="112" t="s">
+      <c r="H2" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="112" t="s">
+      <c r="I2" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="113" t="s">
+      <c r="J2" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="113" t="s">
+      <c r="K2" s="94" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="113" t="s">
+      <c r="L2" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="113" t="s">
+      <c r="M2" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="109" t="s">
+      <c r="N2" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="109" t="s">
+      <c r="O2" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="109" t="s">
+      <c r="P2" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="109" t="s">
+      <c r="Q2" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="109" t="s">
+      <c r="R2" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="109" t="s">
+      <c r="S2" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="109" t="s">
+      <c r="T2" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="109" t="s">
+      <c r="U2" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="V2" s="109" t="s">
+      <c r="V2" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="W2" s="109" t="s">
+      <c r="W2" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="109" t="s">
+      <c r="X2" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="109" t="s">
+      <c r="Y2" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="109" t="s">
+      <c r="Z2" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="109" t="s">
+      <c r="AA2" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="109" t="s">
+      <c r="AB2" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="109" t="s">
+      <c r="AC2" s="90" t="s">
         <v>35</v>
       </c>
       <c r="AD2" s="34" t="s">
@@ -1816,46 +1826,46 @@
       <c r="AE2" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" s="87" t="s">
+      <c r="AF2" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="AG2" s="87" t="s">
+      <c r="AG2" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="AH2" s="87" t="s">
+      <c r="AH2" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="AI2" s="87" t="s">
+      <c r="AI2" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="AJ2" s="87" t="s">
+      <c r="AJ2" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="AK2" s="87" t="s">
+      <c r="AK2" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="AL2" s="87" t="s">
+      <c r="AL2" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="AM2" s="87" t="s">
+      <c r="AM2" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="AN2" s="87" t="s">
+      <c r="AN2" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="AO2" s="87" t="s">
+      <c r="AO2" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="AP2" s="87" t="s">
+      <c r="AP2" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="AQ2" s="87" t="s">
+      <c r="AQ2" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="AR2" s="87" t="s">
+      <c r="AR2" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="AS2" s="87" t="s">
+      <c r="AS2" s="74" t="s">
         <v>51</v>
       </c>
       <c r="AT2" s="15" t="s">
@@ -1864,13 +1874,13 @@
       <c r="AU2" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="AV2" s="87" t="s">
+      <c r="AV2" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="AW2" s="87" t="s">
+      <c r="AW2" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="AX2" s="87" t="s">
+      <c r="AX2" s="74" t="s">
         <v>40</v>
       </c>
       <c r="AY2" s="15" t="s">
@@ -1879,7 +1889,7 @@
       <c r="AZ2" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="BA2" s="87" t="s">
+      <c r="BA2" s="74" t="s">
         <v>58</v>
       </c>
       <c r="BB2" s="15" t="s">
@@ -1888,31 +1898,31 @@
       <c r="BC2" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="BD2" s="87" t="s">
+      <c r="BD2" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="BE2" s="87" t="s">
+      <c r="BE2" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="BF2" s="87" t="s">
+      <c r="BF2" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="BG2" s="87" t="s">
+      <c r="BG2" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="BH2" s="87" t="s">
+      <c r="BH2" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="BI2" s="87" t="s">
+      <c r="BI2" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="BJ2" s="87" t="s">
+      <c r="BJ2" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="BK2" s="87" t="s">
+      <c r="BK2" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="BL2" s="87" t="s">
+      <c r="BL2" s="74" t="s">
         <v>69</v>
       </c>
       <c r="BM2" s="15" t="s">
@@ -1921,14 +1931,14 @@
       <c r="BN2" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="BO2" s="87" t="s">
+      <c r="BO2" s="74" t="s">
         <v>72</v>
       </c>
       <c r="BP2" s="15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>74</v>
       </c>
@@ -1942,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="75">
+      <c r="F3" s="62">
         <v>45491.472488425898</v>
       </c>
       <c r="G3" s="2">
@@ -2032,7 +2042,7 @@
       <c r="AJ3" s="6">
         <v>3.3</v>
       </c>
-      <c r="AK3" s="69">
+      <c r="AK3" s="56">
         <v>0</v>
       </c>
       <c r="AL3" s="6">
@@ -2063,7 +2073,7 @@
       <c r="AT3" s="24">
         <v>15</v>
       </c>
-      <c r="AU3" s="105">
+      <c r="AU3" s="86">
         <v>1700</v>
       </c>
       <c r="AV3" s="6">
@@ -2123,7 +2133,7 @@
         <v/>
       </c>
       <c r="BL3" s="10"/>
-      <c r="BM3" s="92">
+      <c r="BM3" s="76">
         <v>1.685E-4</v>
       </c>
       <c r="BN3" s="27">
@@ -2139,7 +2149,7 @@
         <v>1.685E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>76</v>
       </c>
@@ -2152,72 +2162,72 @@
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="F4" s="68">
+      <c r="F4" s="55">
         <v>45491.474918981497</v>
       </c>
       <c r="G4" s="1">
         <v>146.51</v>
       </c>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69">
+      <c r="H4" s="56"/>
+      <c r="I4" s="56">
         <v>118.99</v>
       </c>
-      <c r="J4" s="69">
+      <c r="J4" s="56">
         <v>13.1</v>
       </c>
-      <c r="K4" s="69">
+      <c r="K4" s="56">
         <v>12.9</v>
       </c>
-      <c r="L4" s="69">
+      <c r="L4" s="56">
         <v>98.6</v>
       </c>
-      <c r="M4" s="69">
+      <c r="M4" s="56">
         <v>16.7</v>
       </c>
-      <c r="N4" s="69">
+      <c r="N4" s="56">
         <v>329</v>
       </c>
-      <c r="O4" s="69">
+      <c r="O4" s="56">
         <v>0.63</v>
       </c>
-      <c r="P4" s="69">
+      <c r="P4" s="56">
         <v>0.6</v>
       </c>
-      <c r="Q4" s="69">
+      <c r="Q4" s="56">
         <v>5.93</v>
       </c>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69">
+      <c r="R4" s="56"/>
+      <c r="S4" s="56">
         <v>0.98</v>
       </c>
-      <c r="T4" s="69">
+      <c r="T4" s="56">
         <v>2.34</v>
       </c>
-      <c r="U4" s="69">
+      <c r="U4" s="56">
         <v>0.89</v>
       </c>
-      <c r="V4" s="69">
+      <c r="V4" s="56">
         <v>7.0279999999999996</v>
       </c>
-      <c r="W4" s="69">
+      <c r="W4" s="56">
         <v>103</v>
       </c>
-      <c r="X4" s="69">
+      <c r="X4" s="56">
         <v>59.4</v>
       </c>
-      <c r="Y4" s="69">
+      <c r="Y4" s="56">
         <v>6.56</v>
       </c>
-      <c r="Z4" s="69">
+      <c r="Z4" s="56">
         <v>108.4</v>
       </c>
-      <c r="AA4" s="69">
+      <c r="AA4" s="56">
         <v>26.1</v>
       </c>
-      <c r="AB4" s="69">
+      <c r="AB4" s="56">
         <v>90.3</v>
       </c>
-      <c r="AC4" s="69">
+      <c r="AC4" s="56">
         <v>48.3</v>
       </c>
       <c r="AD4" s="17">
@@ -2226,70 +2236,70 @@
       <c r="AE4" s="41">
         <v>300</v>
       </c>
-      <c r="AF4" s="69">
+      <c r="AF4" s="56">
         <v>50</v>
       </c>
-      <c r="AG4" s="69">
+      <c r="AG4" s="56">
         <v>7.1</v>
       </c>
-      <c r="AH4" s="70">
+      <c r="AH4" s="57">
         <f t="shared" ref="AH4:AH25" si="8">AF4/100</f>
         <v>0.5</v>
       </c>
-      <c r="AI4" s="69">
+      <c r="AI4" s="56">
         <v>34</v>
       </c>
-      <c r="AJ4" s="69">
+      <c r="AJ4" s="56">
         <v>2.94</v>
       </c>
-      <c r="AK4" s="69">
-        <v>0</v>
-      </c>
-      <c r="AL4" s="69">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="70">
+      <c r="AK4" s="56">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="56">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="57">
         <f t="shared" ref="AM4:AM25" si="9">BO4</f>
         <v>4.6805555555555498E-3</v>
       </c>
-      <c r="AN4" s="69">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="69">
-        <v>0</v>
-      </c>
-      <c r="AP4" s="69">
+      <c r="AN4" s="56">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="56">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="56">
         <v>670</v>
       </c>
-      <c r="AQ4" s="70">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="70">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="70">
+      <c r="AQ4" s="57">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="57">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="57">
         <v>0</v>
       </c>
       <c r="AT4" s="25">
         <v>15</v>
       </c>
-      <c r="AU4" s="106">
+      <c r="AU4" s="87">
         <v>1700</v>
       </c>
-      <c r="AV4" s="69">
+      <c r="AV4" s="56">
         <v>34</v>
       </c>
-      <c r="AW4" s="69">
+      <c r="AW4" s="56">
         <v>7.2</v>
       </c>
-      <c r="AX4" s="69">
+      <c r="AX4" s="56">
         <v>50</v>
       </c>
       <c r="AY4" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AZ4" s="11"/>
-      <c r="BA4" s="71">
+      <c r="BA4" s="58">
         <f>BJ4*24*60/BE4</f>
         <v>3.9999999999999957E-3</v>
       </c>
@@ -2301,46 +2311,46 @@
         <f t="shared" si="0"/>
         <v>6.5209499999999993E-3</v>
       </c>
-      <c r="BD4" s="71">
+      <c r="BD4" s="58">
         <f t="shared" si="1"/>
         <v>9.3901679999999992</v>
       </c>
-      <c r="BE4" s="71">
+      <c r="BE4" s="58">
         <f t="shared" si="2"/>
         <v>1685</v>
       </c>
-      <c r="BF4" s="72">
+      <c r="BF4" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BG4" s="72">
+      <c r="BG4" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BH4" s="72">
+      <c r="BH4" s="59">
         <f t="shared" si="5"/>
         <v>6.7399999999999922</v>
       </c>
-      <c r="BI4" s="72" t="str">
+      <c r="BI4" s="59" t="str">
         <f t="shared" ref="BI4:BI21" si="10">IF(B4="Python",AZ4*BE4/24/60,"")</f>
         <v/>
       </c>
-      <c r="BJ4" s="72">
+      <c r="BJ4" s="59">
         <v>4.6805555555555498E-3</v>
       </c>
-      <c r="BK4" s="73" t="str">
+      <c r="BK4" s="60" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL4" s="72"/>
-      <c r="BM4" s="93">
+      <c r="BL4" s="59"/>
+      <c r="BM4" s="77">
         <v>1.685E-4</v>
       </c>
       <c r="BN4" s="28">
         <f t="shared" ref="BN4:BN23" si="11">IF(BI4&lt;&gt;"",BI4/0.000385,IF(BJ4&lt;&gt;"",BJ4/0.000385,BK4/0.000385))</f>
         <v>12.157287157287143</v>
       </c>
-      <c r="BO4" s="74">
+      <c r="BO4" s="61">
         <f t="shared" ref="BO4:BO23" si="12">IF(BI4&lt;&gt;"",BI4,IF(BJ4&lt;&gt;"",BJ4,BK4))</f>
         <v>4.6805555555555498E-3</v>
       </c>
@@ -2349,7 +2359,7 @@
         <v>1.685E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>77</v>
       </c>
@@ -2362,72 +2372,72 @@
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="F5" s="68">
+      <c r="F5" s="55">
         <v>45491.477488425902</v>
       </c>
       <c r="G5" s="1">
         <v>146.51</v>
       </c>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69">
+      <c r="H5" s="56"/>
+      <c r="I5" s="56">
         <v>118.11</v>
       </c>
-      <c r="J5" s="69">
+      <c r="J5" s="56">
         <v>13.5</v>
       </c>
-      <c r="K5" s="69">
+      <c r="K5" s="56">
         <v>13.3</v>
       </c>
-      <c r="L5" s="69">
+      <c r="L5" s="56">
         <v>98.1</v>
       </c>
-      <c r="M5" s="69">
+      <c r="M5" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="N5" s="69">
+      <c r="N5" s="56">
         <v>327</v>
       </c>
-      <c r="O5" s="69">
+      <c r="O5" s="56">
         <v>0.63</v>
       </c>
-      <c r="P5" s="69">
+      <c r="P5" s="56">
         <v>0.61</v>
       </c>
-      <c r="Q5" s="69">
+      <c r="Q5" s="56">
         <v>5.96</v>
       </c>
-      <c r="R5" s="69"/>
-      <c r="S5" s="69">
+      <c r="R5" s="56"/>
+      <c r="S5" s="56">
         <v>0.97</v>
       </c>
-      <c r="T5" s="69">
+      <c r="T5" s="56">
         <v>2.36</v>
       </c>
-      <c r="U5" s="69">
+      <c r="U5" s="56">
         <v>0.93</v>
       </c>
-      <c r="V5" s="69">
+      <c r="V5" s="56">
         <v>7.0679999999999996</v>
       </c>
-      <c r="W5" s="69">
+      <c r="W5" s="56">
         <v>95</v>
       </c>
-      <c r="X5" s="69">
+      <c r="X5" s="56">
         <v>55.9</v>
       </c>
-      <c r="Y5" s="69">
+      <c r="Y5" s="56">
         <v>6.59</v>
       </c>
-      <c r="Z5" s="69">
+      <c r="Z5" s="56">
         <v>106.4</v>
       </c>
-      <c r="AA5" s="69">
+      <c r="AA5" s="56">
         <v>26.4</v>
       </c>
-      <c r="AB5" s="69">
+      <c r="AB5" s="56">
         <v>83.4</v>
       </c>
-      <c r="AC5" s="69">
+      <c r="AC5" s="56">
         <v>45.4</v>
       </c>
       <c r="AD5" s="17">
@@ -2436,63 +2446,63 @@
       <c r="AE5" s="41">
         <v>300</v>
       </c>
-      <c r="AF5" s="69">
+      <c r="AF5" s="56">
         <v>49.3</v>
       </c>
-      <c r="AG5" s="69">
+      <c r="AG5" s="56">
         <v>7.1</v>
       </c>
-      <c r="AH5" s="70">
+      <c r="AH5" s="57">
         <f t="shared" si="8"/>
         <v>0.49299999999999999</v>
       </c>
-      <c r="AI5" s="69">
+      <c r="AI5" s="56">
         <v>34</v>
       </c>
-      <c r="AJ5" s="69">
+      <c r="AJ5" s="56">
         <v>3.13</v>
       </c>
-      <c r="AK5" s="69">
-        <v>0</v>
-      </c>
-      <c r="AL5" s="69">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="70">
+      <c r="AK5" s="56">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="56">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="57">
         <f t="shared" si="9"/>
         <v>6.9716747687283455E-3</v>
       </c>
-      <c r="AN5" s="69">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="69">
-        <v>0</v>
-      </c>
-      <c r="AP5" s="69">
+      <c r="AN5" s="56">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="56">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="56">
         <v>775</v>
       </c>
-      <c r="AQ5" s="70">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="70">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="70">
+      <c r="AQ5" s="57">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="57">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="57">
         <v>0</v>
       </c>
       <c r="AT5" s="25">
         <v>15</v>
       </c>
-      <c r="AU5" s="106">
+      <c r="AU5" s="87">
         <v>1700</v>
       </c>
-      <c r="AV5" s="69">
+      <c r="AV5" s="56">
         <v>34</v>
       </c>
-      <c r="AW5" s="69">
+      <c r="AW5" s="56">
         <v>7.2</v>
       </c>
-      <c r="AX5" s="69">
+      <c r="AX5" s="56">
         <v>50</v>
       </c>
       <c r="AY5" s="22">
@@ -2501,48 +2511,48 @@
       <c r="AZ5" s="11">
         <v>5.9579891198627997E-3</v>
       </c>
-      <c r="BA5" s="67"/>
+      <c r="BA5" s="54"/>
       <c r="BB5" s="22"/>
       <c r="BC5" s="11">
         <f t="shared" si="0"/>
         <v>6.7231499999999998E-3</v>
       </c>
-      <c r="BD5" s="71">
+      <c r="BD5" s="58">
         <f t="shared" si="1"/>
         <v>9.6813359999999999</v>
       </c>
-      <c r="BE5" s="71">
+      <c r="BE5" s="58">
         <f t="shared" si="2"/>
         <v>1685</v>
       </c>
-      <c r="BF5" s="72">
+      <c r="BF5" s="59">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BG5" s="72">
+      <c r="BG5" s="59">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BH5" s="72">
+      <c r="BH5" s="59">
         <f t="shared" si="5"/>
         <v>10.039211666968818</v>
       </c>
-      <c r="BI5" s="72">
+      <c r="BI5" s="59">
         <f t="shared" si="10"/>
         <v>6.9716747687283455E-3</v>
       </c>
-      <c r="BJ5" s="73" t="str">
+      <c r="BJ5" s="60" t="str">
         <f t="shared" ref="BJ5:BJ21" si="13">IF(B5="Julia",BA5*BE5/24/60,"")</f>
         <v/>
       </c>
-      <c r="BK5" s="73" t="str">
+      <c r="BK5" s="60" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL5" s="72">
-        <v>0</v>
-      </c>
-      <c r="BM5" s="93" t="str">
+      <c r="BL5" s="59">
+        <v>0</v>
+      </c>
+      <c r="BM5" s="77" t="str">
         <f t="shared" ref="BM5:BM21" si="14">IF(B5="Julia",BB5*BE5,"")</f>
         <v/>
       </c>
@@ -2550,7 +2560,7 @@
         <f t="shared" si="11"/>
         <v>18.10824615254116</v>
       </c>
-      <c r="BO5" s="74">
+      <c r="BO5" s="61">
         <f t="shared" si="12"/>
         <v>6.9716747687283455E-3</v>
       </c>
@@ -2559,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>79</v>
       </c>
@@ -2573,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="76">
+      <c r="F6" s="63">
         <v>45491.480787036999</v>
       </c>
       <c r="G6" s="4">
@@ -2694,7 +2704,7 @@
       <c r="AT6" s="26">
         <v>15</v>
       </c>
-      <c r="AU6" s="107">
+      <c r="AU6" s="88">
         <v>1700</v>
       </c>
       <c r="AV6" s="7">
@@ -2742,7 +2752,7 @@
         <f t="shared" si="10"/>
         <v>8.4868529347877988E-3</v>
       </c>
-      <c r="BJ6" s="73" t="str">
+      <c r="BJ6" s="60" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -2753,7 +2763,7 @@
       <c r="BL6" s="14">
         <v>0</v>
       </c>
-      <c r="BM6" s="94" t="str">
+      <c r="BM6" s="78" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -2770,7 +2780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>74</v>
       </c>
@@ -2784,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="68">
+      <c r="F7" s="55">
         <v>45492.338194444441</v>
       </c>
       <c r="G7" s="2">
@@ -2908,7 +2918,7 @@
       <c r="AT7" s="24">
         <v>15</v>
       </c>
-      <c r="AU7" s="105">
+      <c r="AU7" s="86">
         <v>1700</v>
       </c>
       <c r="AV7" s="6">
@@ -2971,14 +2981,14 @@
         <f>IF(IF(B7&lt;&gt;"Julia",((5-Q7)*BE7)/400, "")&lt;0,0,IF(B7&lt;&gt;"Julia",((5-Q7)*BE7)/400, ""))</f>
         <v/>
       </c>
-      <c r="BM7" s="92">
+      <c r="BM7" s="76">
         <v>16.832071720300799</v>
       </c>
       <c r="BN7" s="28">
         <f t="shared" si="11"/>
         <v>18.257305664268703</v>
       </c>
-      <c r="BO7" s="74">
+      <c r="BO7" s="61">
         <f t="shared" si="12"/>
         <v>7.0290626807434503E-3</v>
       </c>
@@ -2987,7 +2997,7 @@
         <v>16.832071720300799</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>76</v>
       </c>
@@ -3003,72 +3013,72 @@
       <c r="E8" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="68">
+      <c r="F8" s="55">
         <v>45492.34097222222</v>
       </c>
       <c r="G8" s="1">
         <v>509.83</v>
       </c>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69">
+      <c r="H8" s="56"/>
+      <c r="I8" s="56">
         <v>436.43</v>
       </c>
-      <c r="J8" s="69">
+      <c r="J8" s="56">
         <v>17.8</v>
       </c>
-      <c r="K8" s="69">
+      <c r="K8" s="56">
         <v>17.399999999999999</v>
       </c>
-      <c r="L8" s="69">
+      <c r="L8" s="56">
         <v>97.6</v>
       </c>
-      <c r="M8" s="69">
+      <c r="M8" s="56">
         <v>16.7</v>
       </c>
-      <c r="N8" s="69">
+      <c r="N8" s="56">
         <v>338</v>
       </c>
-      <c r="O8" s="69">
+      <c r="O8" s="56">
         <v>3.49</v>
       </c>
-      <c r="P8" s="69">
+      <c r="P8" s="56">
         <v>0.52</v>
       </c>
-      <c r="Q8" s="69">
+      <c r="Q8" s="56">
         <v>0.46</v>
       </c>
-      <c r="R8" s="69"/>
-      <c r="S8" s="69">
+      <c r="R8" s="56"/>
+      <c r="S8" s="56">
         <v>0.4</v>
       </c>
-      <c r="T8" s="69">
+      <c r="T8" s="56">
         <v>1.81</v>
       </c>
-      <c r="U8" s="69">
+      <c r="U8" s="56">
         <v>3.15</v>
       </c>
-      <c r="V8" s="69">
+      <c r="V8" s="56">
         <v>7.1050000000000004</v>
       </c>
-      <c r="W8" s="69">
+      <c r="W8" s="56">
         <v>137.69999999999999</v>
       </c>
-      <c r="X8" s="69">
+      <c r="X8" s="56">
         <v>24.9</v>
       </c>
-      <c r="Y8" s="69">
+      <c r="Y8" s="56">
         <v>137.19999999999999</v>
       </c>
-      <c r="Z8" s="69">
+      <c r="Z8" s="56">
         <v>4.97</v>
       </c>
-      <c r="AA8" s="69">
+      <c r="AA8" s="56">
         <v>41.9</v>
       </c>
-      <c r="AB8" s="69">
+      <c r="AB8" s="56">
         <v>120.8</v>
       </c>
-      <c r="AC8" s="69">
+      <c r="AC8" s="56">
         <v>20.100000000000001</v>
       </c>
       <c r="AD8" s="17">
@@ -3077,73 +3087,73 @@
       <c r="AE8" s="41">
         <v>300</v>
       </c>
-      <c r="AF8" s="69">
+      <c r="AF8" s="56">
         <v>47.8</v>
       </c>
-      <c r="AG8" s="69">
+      <c r="AG8" s="56">
         <v>7.1</v>
       </c>
-      <c r="AH8" s="70">
+      <c r="AH8" s="57">
         <f t="shared" si="8"/>
         <v>0.47799999999999998</v>
       </c>
-      <c r="AI8" s="69">
+      <c r="AI8" s="56">
         <v>34</v>
       </c>
-      <c r="AJ8" s="69">
+      <c r="AJ8" s="56">
         <v>19.71</v>
       </c>
-      <c r="AK8" s="69">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="69">
+      <c r="AK8" s="56">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="56">
         <v>1</v>
       </c>
-      <c r="AM8" s="70">
+      <c r="AM8" s="57">
         <f t="shared" si="9"/>
         <v>7.37045380679486E-3</v>
       </c>
-      <c r="AN8" s="69">
+      <c r="AN8" s="56">
         <v>5</v>
       </c>
-      <c r="AO8" s="69">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="69">
+      <c r="AO8" s="56">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="56">
         <v>640</v>
       </c>
-      <c r="AQ8" s="70">
+      <c r="AQ8" s="57">
         <f t="shared" si="15"/>
         <v>5</v>
       </c>
-      <c r="AR8" s="70">
+      <c r="AR8" s="57">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AS8" s="70">
+      <c r="AS8" s="57">
         <f t="shared" ref="AS8:AS11" si="18">AP4-AP8</f>
         <v>30</v>
       </c>
       <c r="AT8" s="25">
         <v>15</v>
       </c>
-      <c r="AU8" s="106">
+      <c r="AU8" s="87">
         <v>1700</v>
       </c>
-      <c r="AV8" s="69">
+      <c r="AV8" s="56">
         <v>34</v>
       </c>
-      <c r="AW8" s="69">
+      <c r="AW8" s="56">
         <v>7.2</v>
       </c>
-      <c r="AX8" s="69">
+      <c r="AX8" s="56">
         <v>50</v>
       </c>
       <c r="AY8" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="AZ8" s="11"/>
-      <c r="BA8" s="71">
+      <c r="BA8" s="58">
         <f>BJ8*24*60/BE8</f>
         <v>6.2590027078831875E-3</v>
       </c>
@@ -3155,49 +3165,49 @@
         <f t="shared" si="0"/>
         <v>8.8516061999999989E-3</v>
       </c>
-      <c r="BD8" s="71">
+      <c r="BD8" s="58">
         <f t="shared" si="1"/>
         <v>12.746312927999998</v>
       </c>
-      <c r="BE8" s="71">
+      <c r="BE8" s="58">
         <f t="shared" si="17"/>
         <v>1695.71</v>
       </c>
-      <c r="BF8" s="72">
+      <c r="BF8" s="59">
         <f t="shared" si="3"/>
         <v>2.9486173933042795E-3</v>
       </c>
-      <c r="BG8" s="72">
+      <c r="BG8" s="59">
         <f t="shared" si="4"/>
         <v>2.9411764705882353E-3</v>
       </c>
-      <c r="BH8" s="72">
+      <c r="BH8" s="59">
         <f t="shared" si="5"/>
         <v>10.6134534817846</v>
       </c>
-      <c r="BI8" s="72" t="str">
+      <c r="BI8" s="59" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="BJ8" s="72">
+      <c r="BJ8" s="59">
         <v>7.37045380679486E-3</v>
       </c>
-      <c r="BK8" s="73" t="str">
+      <c r="BK8" s="60" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL8" s="72" t="str">
+      <c r="BL8" s="59" t="str">
         <f>IF(IF(B8&lt;&gt;"Julia",((5-Q8)*BE8)/400, "")&lt;0,0,IF(B8&lt;&gt;"Julia",((5-Q8)*BE8)/400, ""))</f>
         <v/>
       </c>
-      <c r="BM8" s="93">
+      <c r="BM8" s="77">
         <v>18.617318338672099</v>
       </c>
       <c r="BN8" s="28">
         <f t="shared" si="11"/>
         <v>19.144035861804831</v>
       </c>
-      <c r="BO8" s="74">
+      <c r="BO8" s="61">
         <f t="shared" si="12"/>
         <v>7.37045380679486E-3</v>
       </c>
@@ -3206,7 +3216,7 @@
         <v>18.617318338672099</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
@@ -3219,72 +3229,72 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="F9" s="68">
+      <c r="F9" s="55">
         <v>45492.34375</v>
       </c>
       <c r="G9" s="1">
         <v>509.83</v>
       </c>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69">
+      <c r="H9" s="56"/>
+      <c r="I9" s="56">
         <v>433.26</v>
       </c>
-      <c r="J9" s="69">
+      <c r="J9" s="56">
         <v>17.100000000000001</v>
       </c>
-      <c r="K9" s="69">
+      <c r="K9" s="56">
         <v>16.8</v>
       </c>
-      <c r="L9" s="69">
+      <c r="L9" s="56">
         <v>98.4</v>
       </c>
-      <c r="M9" s="69">
+      <c r="M9" s="56">
         <v>17</v>
       </c>
-      <c r="N9" s="69">
+      <c r="N9" s="56">
         <v>339</v>
       </c>
-      <c r="O9" s="69">
+      <c r="O9" s="56">
         <v>1.85</v>
       </c>
-      <c r="P9" s="69">
+      <c r="P9" s="56">
         <v>0.54</v>
       </c>
-      <c r="Q9" s="69">
+      <c r="Q9" s="56">
         <v>1.1100000000000001</v>
       </c>
-      <c r="R9" s="69"/>
-      <c r="S9" s="69">
+      <c r="R9" s="56"/>
+      <c r="S9" s="56">
         <v>0.68</v>
       </c>
-      <c r="T9" s="69">
+      <c r="T9" s="56">
         <v>2.56</v>
       </c>
-      <c r="U9" s="69">
+      <c r="U9" s="56">
         <v>2.99</v>
       </c>
-      <c r="V9" s="69">
+      <c r="V9" s="56">
         <v>7.07</v>
       </c>
-      <c r="W9" s="69">
+      <c r="W9" s="56">
         <v>117.2</v>
       </c>
-      <c r="X9" s="69">
+      <c r="X9" s="56">
         <v>54.1</v>
       </c>
-      <c r="Y9" s="69">
+      <c r="Y9" s="56">
         <v>136.30000000000001</v>
       </c>
-      <c r="Z9" s="69">
+      <c r="Z9" s="56">
         <v>5</v>
       </c>
-      <c r="AA9" s="69">
+      <c r="AA9" s="56">
         <v>32.799999999999997</v>
       </c>
-      <c r="AB9" s="69">
+      <c r="AB9" s="56">
         <v>102.8</v>
       </c>
-      <c r="AC9" s="69">
+      <c r="AC9" s="56">
         <v>43.9</v>
       </c>
       <c r="AD9" s="17">
@@ -3293,66 +3303,66 @@
       <c r="AE9" s="41">
         <v>300</v>
       </c>
-      <c r="AF9" s="69">
+      <c r="AF9" s="56">
         <v>49.5</v>
       </c>
-      <c r="AG9" s="69">
+      <c r="AG9" s="56">
         <v>7.1</v>
       </c>
-      <c r="AH9" s="70">
+      <c r="AH9" s="57">
         <f t="shared" si="8"/>
         <v>0.495</v>
       </c>
-      <c r="AI9" s="69">
+      <c r="AI9" s="56">
         <v>34</v>
       </c>
-      <c r="AJ9" s="69">
+      <c r="AJ9" s="56">
         <v>19.48</v>
       </c>
-      <c r="AK9" s="69">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="69">
+      <c r="AK9" s="56">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="56">
         <v>1</v>
       </c>
-      <c r="AM9" s="70">
+      <c r="AM9" s="57">
         <f t="shared" si="9"/>
         <v>5.3061875000344899E-3</v>
       </c>
-      <c r="AN9" s="69">
+      <c r="AN9" s="56">
         <v>7.5</v>
       </c>
-      <c r="AO9" s="69">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="69">
+      <c r="AO9" s="56">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="56">
         <v>772</v>
       </c>
-      <c r="AQ9" s="70">
+      <c r="AQ9" s="57">
         <f t="shared" si="15"/>
         <v>7.5</v>
       </c>
-      <c r="AR9" s="70">
+      <c r="AR9" s="57">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AS9" s="70">
+      <c r="AS9" s="57">
         <f t="shared" si="18"/>
         <v>3</v>
       </c>
       <c r="AT9" s="25">
         <v>15</v>
       </c>
-      <c r="AU9" s="106">
+      <c r="AU9" s="87">
         <v>1700</v>
       </c>
-      <c r="AV9" s="69">
+      <c r="AV9" s="56">
         <v>34</v>
       </c>
-      <c r="AW9" s="69">
+      <c r="AW9" s="56">
         <v>7.2</v>
       </c>
-      <c r="AX9" s="69">
+      <c r="AX9" s="56">
         <v>50</v>
       </c>
       <c r="AY9" s="22">
@@ -3361,49 +3371,49 @@
       <c r="AZ9" s="11">
         <v>4.5000000000292497E-3</v>
       </c>
-      <c r="BA9" s="67"/>
-      <c r="BB9" s="99"/>
+      <c r="BA9" s="54"/>
+      <c r="BB9" s="83"/>
       <c r="BC9" s="11">
         <f t="shared" si="0"/>
         <v>8.5578191999999987E-3</v>
       </c>
-      <c r="BD9" s="71">
+      <c r="BD9" s="58">
         <f t="shared" si="1"/>
         <v>12.323259647999999</v>
       </c>
-      <c r="BE9" s="71">
+      <c r="BE9" s="58">
         <f t="shared" si="17"/>
         <v>1697.98</v>
       </c>
-      <c r="BF9" s="72">
+      <c r="BF9" s="59">
         <f t="shared" si="3"/>
         <v>4.4170131568098568E-3</v>
       </c>
-      <c r="BG9" s="72">
+      <c r="BG9" s="59">
         <f t="shared" si="4"/>
         <v>4.4117647058823529E-3</v>
       </c>
-      <c r="BH9" s="72">
+      <c r="BH9" s="59">
         <f t="shared" si="5"/>
         <v>7.640910000049665</v>
       </c>
-      <c r="BI9" s="72">
+      <c r="BI9" s="59">
         <f t="shared" si="10"/>
         <v>5.3061875000344899E-3</v>
       </c>
-      <c r="BJ9" s="72" t="str">
+      <c r="BJ9" s="59" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="BK9" s="73" t="str">
+      <c r="BK9" s="60" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL9" s="95">
+      <c r="BL9" s="79">
         <f>IF(IF(B9&lt;&gt;"Julia",((5-Q9)*BE9)/400, "")&lt;0,0,IF(B9&lt;&gt;"Julia",((5-Q9)*BE9)/400, ""))</f>
         <v>16.512855499999997</v>
       </c>
-      <c r="BM9" s="93" t="str">
+      <c r="BM9" s="77" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -3411,7 +3421,7 @@
         <f t="shared" si="11"/>
         <v>13.78230519489478</v>
       </c>
-      <c r="BO9" s="74">
+      <c r="BO9" s="61">
         <f t="shared" si="12"/>
         <v>5.3061875000344899E-3</v>
       </c>
@@ -3420,7 +3430,7 @@
         <v>16.512855499999997</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>79</v>
       </c>
@@ -3433,7 +3443,7 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="F10" s="68">
+      <c r="F10" s="55">
         <v>45492.345833333333</v>
       </c>
       <c r="G10" s="4">
@@ -3557,7 +3567,7 @@
       <c r="AT10" s="26">
         <v>15</v>
       </c>
-      <c r="AU10" s="107">
+      <c r="AU10" s="88">
         <v>1700</v>
       </c>
       <c r="AV10" s="7">
@@ -3617,7 +3627,7 @@
         <f>IF(IF(B10&lt;&gt;"Julia",((5-Q10)*BE10)/400, "")&lt;0,0,IF(B10&lt;&gt;"Julia",((5-Q10)*BE10)/400, ""))</f>
         <v>17.037286999999999</v>
       </c>
-      <c r="BM10" s="94" t="str">
+      <c r="BM10" s="78" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -3625,7 +3635,7 @@
         <f t="shared" si="11"/>
         <v>13.794480530314367</v>
       </c>
-      <c r="BO10" s="74">
+      <c r="BO10" s="61">
         <f t="shared" si="12"/>
         <v>5.3108750041710312E-3</v>
       </c>
@@ -3634,7 +3644,7 @@
         <v>17.037286999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>74</v>
       </c>
@@ -3650,72 +3660,72 @@
       <c r="E11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="62">
         <v>45493.525694444397</v>
       </c>
       <c r="G11" s="1">
         <v>997.91</v>
       </c>
-      <c r="H11" s="69"/>
-      <c r="I11" s="69">
+      <c r="H11" s="56"/>
+      <c r="I11" s="56">
         <v>933.27</v>
       </c>
-      <c r="J11" s="69">
+      <c r="J11" s="56">
         <v>22.8</v>
       </c>
-      <c r="K11" s="69">
+      <c r="K11" s="56">
         <v>22.3</v>
       </c>
-      <c r="L11" s="69">
+      <c r="L11" s="56">
         <v>97.8</v>
       </c>
-      <c r="M11" s="69">
+      <c r="M11" s="56">
         <v>16.899999999999999</v>
       </c>
-      <c r="N11" s="69">
+      <c r="N11" s="56">
         <v>331</v>
       </c>
-      <c r="O11" s="69">
+      <c r="O11" s="56">
         <v>1.6</v>
       </c>
-      <c r="P11" s="69">
+      <c r="P11" s="56">
         <v>0.43</v>
       </c>
-      <c r="Q11" s="69">
+      <c r="Q11" s="56">
         <v>0.04</v>
       </c>
-      <c r="R11" s="69"/>
-      <c r="S11" s="69">
+      <c r="R11" s="56"/>
+      <c r="S11" s="56">
         <v>0.1</v>
       </c>
-      <c r="T11" s="69">
+      <c r="T11" s="56">
         <v>0.04</v>
       </c>
-      <c r="U11" s="69">
+      <c r="U11" s="56">
         <v>3.86</v>
       </c>
-      <c r="V11" s="69">
+      <c r="V11" s="56">
         <v>7.0960000000000001</v>
       </c>
-      <c r="W11" s="69">
+      <c r="W11" s="56">
         <v>126.4</v>
       </c>
-      <c r="X11" s="69">
+      <c r="X11" s="56">
         <v>57.8</v>
       </c>
-      <c r="Y11" s="69">
+      <c r="Y11" s="56">
         <v>147.5</v>
       </c>
-      <c r="Z11" s="69">
+      <c r="Z11" s="56">
         <v>3.37</v>
       </c>
-      <c r="AA11" s="69">
+      <c r="AA11" s="56">
         <v>37.6</v>
       </c>
-      <c r="AB11" s="69">
+      <c r="AB11" s="56">
         <v>110.9</v>
       </c>
-      <c r="AC11" s="69">
+      <c r="AC11" s="56">
         <v>47</v>
       </c>
       <c r="AD11" s="17">
@@ -3774,7 +3784,7 @@
       <c r="AT11" s="24">
         <v>15</v>
       </c>
-      <c r="AU11" s="105">
+      <c r="AU11" s="86">
         <v>1700</v>
       </c>
       <c r="AV11" s="6">
@@ -3837,7 +3847,7 @@
         <f t="shared" ref="BL11:BL25" si="19">IF(IF(B11&lt;&gt;"Julia",((1.5-Q11)*BE11)/400, "")&lt;0,0,IF(B11&lt;&gt;"Julia",((3-Q11)*BE11)/400, ""))</f>
         <v/>
       </c>
-      <c r="BM11" s="92">
+      <c r="BM11" s="76">
         <v>12.1026345792793</v>
       </c>
       <c r="BN11" s="27">
@@ -3853,7 +3863,7 @@
         <v>12.1026345792793</v>
       </c>
     </row>
-    <row r="12" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>77</v>
       </c>
@@ -3869,72 +3879,72 @@
       <c r="E12" t="s">
         <v>82</v>
       </c>
-      <c r="F12" s="68">
+      <c r="F12" s="55">
         <v>45493.528472222199</v>
       </c>
       <c r="G12" s="1">
         <v>997.91</v>
       </c>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69">
+      <c r="H12" s="56"/>
+      <c r="I12" s="56">
         <v>919.68</v>
       </c>
-      <c r="J12" s="69">
+      <c r="J12" s="56">
         <v>23.6</v>
       </c>
-      <c r="K12" s="69">
+      <c r="K12" s="56">
         <v>23.1</v>
       </c>
-      <c r="L12" s="69">
+      <c r="L12" s="56">
         <v>98.1</v>
       </c>
-      <c r="M12" s="69">
+      <c r="M12" s="56">
         <v>16.8</v>
       </c>
-      <c r="N12" s="69">
+      <c r="N12" s="56">
         <v>327</v>
       </c>
-      <c r="O12" s="69">
+      <c r="O12" s="56">
         <v>1.55</v>
       </c>
-      <c r="P12" s="69">
+      <c r="P12" s="56">
         <v>0.44</v>
       </c>
-      <c r="Q12" s="69">
-        <v>0</v>
-      </c>
-      <c r="R12" s="69"/>
-      <c r="S12" s="69">
+      <c r="Q12" s="56">
+        <v>0</v>
+      </c>
+      <c r="R12" s="56"/>
+      <c r="S12" s="56">
         <v>0.11</v>
       </c>
-      <c r="T12" s="69">
+      <c r="T12" s="56">
         <v>0.03</v>
       </c>
-      <c r="U12" s="69">
+      <c r="U12" s="56">
         <v>3.55</v>
       </c>
-      <c r="V12" s="69">
+      <c r="V12" s="56">
         <v>7.1550000000000002</v>
       </c>
-      <c r="W12" s="69">
+      <c r="W12" s="56">
         <v>119</v>
       </c>
-      <c r="X12" s="69">
+      <c r="X12" s="56">
         <v>20.399999999999999</v>
       </c>
-      <c r="Y12" s="69">
+      <c r="Y12" s="56">
         <v>145.4</v>
       </c>
-      <c r="Z12" s="69">
+      <c r="Z12" s="56">
         <v>3.49</v>
       </c>
-      <c r="AA12" s="69">
+      <c r="AA12" s="56">
         <v>40.6</v>
       </c>
-      <c r="AB12" s="69">
+      <c r="AB12" s="56">
         <v>104.3</v>
       </c>
-      <c r="AC12" s="69">
+      <c r="AC12" s="56">
         <v>16.5</v>
       </c>
       <c r="AD12" s="17">
@@ -3943,66 +3953,66 @@
       <c r="AE12" s="41">
         <v>300</v>
       </c>
-      <c r="AF12" s="69">
+      <c r="AF12" s="56">
         <v>51.1</v>
       </c>
-      <c r="AG12" s="69">
+      <c r="AG12" s="56">
         <v>7.13</v>
       </c>
-      <c r="AH12" s="70">
+      <c r="AH12" s="57">
         <f t="shared" si="8"/>
         <v>0.51100000000000001</v>
       </c>
-      <c r="AI12" s="69">
+      <c r="AI12" s="56">
         <v>34</v>
       </c>
-      <c r="AJ12" s="69">
+      <c r="AJ12" s="56">
         <v>24.361000000000001</v>
       </c>
-      <c r="AK12" s="69">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="69">
+      <c r="AK12" s="56">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="56">
         <v>3</v>
       </c>
-      <c r="AM12" s="70">
+      <c r="AM12" s="57">
         <f t="shared" si="9"/>
         <v>1.190824173E-2</v>
       </c>
-      <c r="AN12" s="69">
+      <c r="AN12" s="56">
         <v>16</v>
       </c>
-      <c r="AO12" s="69">
+      <c r="AO12" s="56">
         <v>20</v>
       </c>
-      <c r="AP12" s="69">
+      <c r="AP12" s="56">
         <v>762</v>
       </c>
-      <c r="AQ12" s="70">
+      <c r="AQ12" s="57">
         <f t="shared" ref="AQ12:AQ15" si="20">AN12-AN9</f>
         <v>8.5</v>
       </c>
-      <c r="AR12" s="70">
+      <c r="AR12" s="57">
         <f t="shared" ref="AR12:AR15" si="21">AO12-AO9</f>
         <v>20</v>
       </c>
-      <c r="AS12" s="70">
+      <c r="AS12" s="57">
         <f t="shared" ref="AS12:AS15" si="22">AP9-AP12</f>
         <v>10</v>
       </c>
       <c r="AT12" s="25">
         <v>15</v>
       </c>
-      <c r="AU12" s="106">
+      <c r="AU12" s="87">
         <v>1700</v>
       </c>
-      <c r="AV12" s="69">
+      <c r="AV12" s="56">
         <v>34</v>
       </c>
-      <c r="AW12" s="69">
+      <c r="AW12" s="56">
         <v>7.2</v>
       </c>
-      <c r="AX12" s="69">
+      <c r="AX12" s="56">
         <v>50</v>
       </c>
       <c r="AY12" s="22">
@@ -4011,48 +4021,48 @@
       <c r="AZ12" s="11">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="BA12" s="67"/>
+      <c r="BA12" s="54"/>
       <c r="BB12" s="22"/>
       <c r="BC12" s="48">
         <f t="shared" si="0"/>
         <v>1.190824173E-2</v>
       </c>
-      <c r="BD12" s="71">
+      <c r="BD12" s="58">
         <f t="shared" si="1"/>
         <v>17.147868091199999</v>
       </c>
-      <c r="BE12" s="71">
+      <c r="BE12" s="58">
         <f t="shared" si="17"/>
         <v>1718.3610000000001</v>
       </c>
-      <c r="BF12" s="72">
+      <c r="BF12" s="59">
         <f t="shared" si="3"/>
         <v>9.3111982872050737E-3</v>
       </c>
-      <c r="BG12" s="72">
+      <c r="BG12" s="59">
         <f t="shared" si="4"/>
         <v>9.4117647058823521E-3</v>
       </c>
-      <c r="BH12" s="72">
+      <c r="BH12" s="59">
         <f t="shared" si="5"/>
         <v>17.147868091199999</v>
       </c>
-      <c r="BI12" s="96">
+      <c r="BI12" s="80">
         <v>1.190824173E-2</v>
       </c>
-      <c r="BJ12" s="72" t="str">
+      <c r="BJ12" s="59" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="BK12" s="73" t="str">
+      <c r="BK12" s="60" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL12" s="72">
+      <c r="BL12" s="59">
         <f t="shared" si="19"/>
         <v>12.887707500000001</v>
       </c>
-      <c r="BM12" s="93" t="str">
+      <c r="BM12" s="77" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -4060,7 +4070,7 @@
         <f t="shared" si="11"/>
         <v>30.930498</v>
       </c>
-      <c r="BO12" s="74">
+      <c r="BO12" s="61">
         <f>IF(BI12&lt;&gt;"",BI12,IF(BJ12&lt;&gt;"",BJ12,BK12))</f>
         <v>1.190824173E-2</v>
       </c>
@@ -4069,7 +4079,7 @@
         <v>12.887707500000001</v>
       </c>
     </row>
-    <row r="13" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>79</v>
       </c>
@@ -4083,74 +4093,74 @@
         <v>2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="76">
+        <v>84</v>
+      </c>
+      <c r="F13" s="63">
         <v>45493.536805555603</v>
       </c>
       <c r="G13" s="1">
         <v>997.91</v>
       </c>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69">
+      <c r="H13" s="56"/>
+      <c r="I13" s="56">
         <v>949.59</v>
       </c>
-      <c r="J13" s="69">
+      <c r="J13" s="56">
         <v>23.2</v>
       </c>
-      <c r="K13" s="69">
+      <c r="K13" s="56">
         <v>22.7</v>
       </c>
-      <c r="L13" s="69">
+      <c r="L13" s="56">
         <v>97.9</v>
       </c>
-      <c r="M13" s="69">
+      <c r="M13" s="56">
         <v>16.899999999999999</v>
       </c>
-      <c r="N13" s="69">
+      <c r="N13" s="56">
         <v>338</v>
       </c>
-      <c r="O13" s="69">
+      <c r="O13" s="56">
         <v>1.47</v>
       </c>
-      <c r="P13" s="69">
+      <c r="P13" s="56">
         <v>0.43</v>
       </c>
-      <c r="Q13" s="69">
+      <c r="Q13" s="56">
         <v>0.45</v>
       </c>
-      <c r="R13" s="69"/>
-      <c r="S13" s="69">
+      <c r="R13" s="56"/>
+      <c r="S13" s="56">
         <v>0.14000000000000001</v>
       </c>
-      <c r="T13" s="69">
+      <c r="T13" s="56">
         <v>0.01</v>
       </c>
-      <c r="U13" s="69">
+      <c r="U13" s="56">
         <v>4.01</v>
       </c>
-      <c r="V13" s="69">
+      <c r="V13" s="56">
         <v>7.093</v>
       </c>
-      <c r="W13" s="69">
+      <c r="W13" s="56">
         <v>118.1</v>
       </c>
-      <c r="X13" s="69">
+      <c r="X13" s="56">
         <v>30.6</v>
       </c>
-      <c r="Y13" s="69">
+      <c r="Y13" s="56">
         <v>148.19999999999999</v>
       </c>
-      <c r="Z13" s="69">
+      <c r="Z13" s="56">
         <v>3.26</v>
       </c>
-      <c r="AA13" s="69">
+      <c r="AA13" s="56">
         <v>34.9</v>
       </c>
-      <c r="AB13" s="69">
+      <c r="AB13" s="56">
         <v>103.6</v>
       </c>
-      <c r="AC13" s="69">
+      <c r="AC13" s="56">
         <v>24.7</v>
       </c>
       <c r="AD13" s="17">
@@ -4209,7 +4219,7 @@
       <c r="AT13" s="26">
         <v>15</v>
       </c>
-      <c r="AU13" s="107">
+      <c r="AU13" s="88">
         <v>1700</v>
       </c>
       <c r="AV13" s="7">
@@ -4227,7 +4237,7 @@
       <c r="AZ13" s="12">
         <v>4.5000000009706104E-3</v>
       </c>
-      <c r="BA13" s="67"/>
+      <c r="BA13" s="54"/>
       <c r="BB13" s="23"/>
       <c r="BC13" s="49">
         <f t="shared" si="0"/>
@@ -4268,7 +4278,7 @@
         <f t="shared" si="19"/>
         <v>10.962813374999998</v>
       </c>
-      <c r="BM13" s="94" t="str">
+      <c r="BM13" s="78" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -4285,7 +4295,7 @@
         <v>10.962813374999998</v>
       </c>
     </row>
-    <row r="14" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>74</v>
       </c>
@@ -4299,7 +4309,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="75">
+      <c r="F14" s="62">
         <v>45494.550289351901</v>
       </c>
       <c r="G14" s="2">
@@ -4309,16 +4319,16 @@
       <c r="I14" s="6">
         <v>1446.18</v>
       </c>
-      <c r="J14" s="66">
+      <c r="J14" s="53">
         <v>24</v>
       </c>
-      <c r="K14" s="66">
+      <c r="K14" s="53">
         <v>23.1</v>
       </c>
-      <c r="L14" s="66">
+      <c r="L14" s="53">
         <v>96</v>
       </c>
-      <c r="M14" s="66">
+      <c r="M14" s="53">
         <v>17.100000000000001</v>
       </c>
       <c r="N14" s="6">
@@ -4423,7 +4433,7 @@
       <c r="AT14" s="24">
         <v>15</v>
       </c>
-      <c r="AU14" s="105">
+      <c r="AU14" s="86">
         <v>1700</v>
       </c>
       <c r="AV14" s="6">
@@ -4486,14 +4496,14 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="BM14" s="92">
+      <c r="BM14" s="76">
         <v>11.3869050015914</v>
       </c>
       <c r="BN14" s="28">
         <f t="shared" si="11"/>
         <v>23.009669497392963</v>
       </c>
-      <c r="BO14" s="74">
+      <c r="BO14" s="61">
         <f t="shared" si="12"/>
         <v>8.8587227564962904E-3</v>
       </c>
@@ -4502,7 +4512,7 @@
         <v>11.3869050015914</v>
       </c>
     </row>
-    <row r="15" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>77</v>
       </c>
@@ -4515,72 +4525,72 @@
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="F15" s="68">
+      <c r="F15" s="55">
         <v>45494.554664351897</v>
       </c>
       <c r="G15" s="1">
         <v>1505.08</v>
       </c>
-      <c r="H15" s="69"/>
-      <c r="I15" s="69">
+      <c r="H15" s="56"/>
+      <c r="I15" s="56">
         <v>1350.49</v>
       </c>
-      <c r="J15" s="114">
+      <c r="J15" s="95">
         <v>24.8</v>
       </c>
-      <c r="K15" s="114">
+      <c r="K15" s="95">
         <v>23.3</v>
       </c>
-      <c r="L15" s="114">
+      <c r="L15" s="95">
         <v>94.2</v>
       </c>
-      <c r="M15" s="114">
+      <c r="M15" s="95">
         <v>16.5</v>
       </c>
-      <c r="N15" s="69">
+      <c r="N15" s="56">
         <v>372</v>
       </c>
-      <c r="O15" s="69">
+      <c r="O15" s="56">
         <v>2.68</v>
       </c>
-      <c r="P15" s="69">
+      <c r="P15" s="56">
         <v>0.4</v>
       </c>
-      <c r="Q15" s="69">
+      <c r="Q15" s="56">
         <v>0.01</v>
       </c>
-      <c r="R15" s="69"/>
-      <c r="S15" s="69">
+      <c r="R15" s="56"/>
+      <c r="S15" s="56">
         <v>0.08</v>
       </c>
-      <c r="T15" s="69">
+      <c r="T15" s="56">
         <v>0.1</v>
       </c>
-      <c r="U15" s="69">
+      <c r="U15" s="56">
         <v>3.17</v>
       </c>
-      <c r="V15" s="69">
+      <c r="V15" s="56">
         <v>7.3440000000000003</v>
       </c>
-      <c r="W15" s="69">
+      <c r="W15" s="56">
         <v>146.69999999999999</v>
       </c>
-      <c r="X15" s="69">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="69">
+      <c r="X15" s="56">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="56">
         <v>3.6</v>
       </c>
-      <c r="Z15" s="69">
+      <c r="Z15" s="56">
         <v>167.8</v>
       </c>
-      <c r="AA15" s="69">
+      <c r="AA15" s="56">
         <v>78</v>
       </c>
-      <c r="AB15" s="69">
+      <c r="AB15" s="56">
         <v>128.6</v>
       </c>
-      <c r="AC15" s="69">
+      <c r="AC15" s="56">
         <v>0</v>
       </c>
       <c r="AD15" s="17">
@@ -4589,66 +4599,66 @@
       <c r="AE15" s="41">
         <v>300</v>
       </c>
-      <c r="AF15" s="69">
+      <c r="AF15" s="56">
         <v>52.2</v>
       </c>
-      <c r="AG15" s="69">
+      <c r="AG15" s="56">
         <v>7.29</v>
       </c>
-      <c r="AH15" s="70">
+      <c r="AH15" s="57">
         <f t="shared" si="8"/>
         <v>0.52200000000000002</v>
       </c>
-      <c r="AI15" s="69">
+      <c r="AI15" s="56">
         <v>34</v>
       </c>
-      <c r="AJ15" s="69">
+      <c r="AJ15" s="56">
         <v>37.567</v>
       </c>
-      <c r="AK15" s="69">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="69">
+      <c r="AK15" s="56">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="56">
         <v>4</v>
       </c>
-      <c r="AM15" s="70">
+      <c r="AM15" s="57">
         <f t="shared" si="9"/>
         <v>4.7913410285290454E-2</v>
       </c>
-      <c r="AN15" s="69">
+      <c r="AN15" s="56">
         <v>33</v>
       </c>
-      <c r="AO15" s="69">
+      <c r="AO15" s="56">
         <v>34</v>
       </c>
-      <c r="AP15" s="69">
+      <c r="AP15" s="56">
         <v>743</v>
       </c>
-      <c r="AQ15" s="70">
+      <c r="AQ15" s="57">
         <f t="shared" si="20"/>
         <v>17</v>
       </c>
-      <c r="AR15" s="70">
+      <c r="AR15" s="57">
         <f t="shared" si="21"/>
         <v>14</v>
       </c>
-      <c r="AS15" s="70">
+      <c r="AS15" s="57">
         <f t="shared" si="22"/>
         <v>19</v>
       </c>
       <c r="AT15" s="25">
         <v>15</v>
       </c>
-      <c r="AU15" s="106">
+      <c r="AU15" s="87">
         <v>1700</v>
       </c>
-      <c r="AV15" s="69">
+      <c r="AV15" s="56">
         <v>34</v>
       </c>
-      <c r="AW15" s="69">
+      <c r="AW15" s="56">
         <v>7.2</v>
       </c>
-      <c r="AX15" s="69">
+      <c r="AX15" s="56">
         <v>50</v>
       </c>
       <c r="AY15" s="22">
@@ -4657,49 +4667,49 @@
       <c r="AZ15" s="11">
         <v>3.9458202522876303E-2</v>
       </c>
-      <c r="BA15" s="71"/>
+      <c r="BA15" s="58"/>
       <c r="BB15" s="22"/>
       <c r="BC15" s="11">
         <f t="shared" si="0"/>
         <v>1.2222483329999999E-2</v>
       </c>
-      <c r="BD15" s="71">
+      <c r="BD15" s="58">
         <f t="shared" si="1"/>
         <v>17.600375995199997</v>
       </c>
-      <c r="BE15" s="71">
+      <c r="BE15" s="58">
         <f t="shared" si="17"/>
         <v>1748.567</v>
       </c>
-      <c r="BF15" s="72">
+      <c r="BF15" s="59">
         <f t="shared" si="3"/>
         <v>1.8872596817851417E-2</v>
       </c>
-      <c r="BG15" s="72">
+      <c r="BG15" s="59">
         <f t="shared" si="4"/>
         <v>1.9411764705882354E-2</v>
       </c>
-      <c r="BH15" s="72">
+      <c r="BH15" s="59">
         <f t="shared" si="5"/>
         <v>68.995310810818253</v>
       </c>
-      <c r="BI15" s="72">
+      <c r="BI15" s="59">
         <f t="shared" si="10"/>
         <v>4.7913410285290454E-2</v>
       </c>
-      <c r="BJ15" s="72" t="str">
+      <c r="BJ15" s="59" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="BK15" s="73" t="str">
+      <c r="BK15" s="60" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL15" s="72">
+      <c r="BL15" s="59">
         <f t="shared" si="19"/>
         <v>13.070538324999999</v>
       </c>
-      <c r="BM15" s="93" t="str">
+      <c r="BM15" s="77" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -4707,7 +4717,7 @@
         <f t="shared" si="11"/>
         <v>124.45041632542976</v>
       </c>
-      <c r="BO15" s="74">
+      <c r="BO15" s="61">
         <f t="shared" si="12"/>
         <v>4.7913410285290454E-2</v>
       </c>
@@ -4716,7 +4726,7 @@
         <v>13.070538324999999</v>
       </c>
     </row>
-    <row r="16" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>74</v>
       </c>
@@ -4729,8 +4739,12 @@
       <c r="D16" s="3">
         <v>4</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="75"/>
+      <c r="E16" s="98" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="62">
+        <v>45495.347314814797</v>
+      </c>
       <c r="G16" s="2">
         <v>2119.61</v>
       </c>
@@ -4826,7 +4840,7 @@
       </c>
       <c r="AM16" s="43">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5.6609312374999998E-2</v>
       </c>
       <c r="AN16" s="6">
         <v>57</v>
@@ -4838,11 +4852,11 @@
         <v>652</v>
       </c>
       <c r="AQ16" s="43">
-        <f>AN16-AN14</f>
+        <f t="shared" ref="AQ16:AR18" si="23">AN16-AN14</f>
         <v>15</v>
       </c>
       <c r="AR16" s="43">
-        <f>AO16-AO14</f>
+        <f t="shared" si="23"/>
         <v>12</v>
       </c>
       <c r="AS16" s="43">
@@ -4852,7 +4866,7 @@
       <c r="AT16" s="24">
         <v>15</v>
       </c>
-      <c r="AU16" s="105">
+      <c r="AU16" s="86">
         <v>1700</v>
       </c>
       <c r="AV16" s="6">
@@ -4867,9 +4881,17 @@
       <c r="AY16" s="21">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AZ16" s="8"/>
-      <c r="BA16" s="9"/>
-      <c r="BB16" s="21"/>
+      <c r="AZ16" s="8">
+        <v>4.6199999999999998E-2</v>
+      </c>
+      <c r="BA16" s="99">
+        <f>0.0233115320383875*24*60/BE16</f>
+        <v>1.9025010815166301E-2</v>
+      </c>
+      <c r="BB16" s="99">
+        <f>7.82697966420876/BE16</f>
+        <v>4.4359414913319028E-3</v>
+      </c>
       <c r="BC16" s="8">
         <f t="shared" si="0"/>
         <v>1.2809878686E-2</v>
@@ -4892,11 +4914,11 @@
       </c>
       <c r="BH16" s="10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>81.517409819999997</v>
       </c>
       <c r="BI16" s="10">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>5.6609312374999998E-2</v>
       </c>
       <c r="BJ16" s="10" t="str">
         <f t="shared" si="13"/>
@@ -4910,1407 +4932,1547 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BM16" s="92" t="str">
+      <c r="BM16" s="76" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="BN16" s="27">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>147.03717499999999</v>
       </c>
       <c r="BO16" s="37">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>5.6609312374999998E-2</v>
       </c>
       <c r="BP16" s="32">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="67">
+      <c r="C17" s="5">
         <v>12</v>
       </c>
-      <c r="D17" s="67">
+      <c r="D17" s="5">
         <v>4</v>
       </c>
-      <c r="E17" s="67" t="s">
+      <c r="E17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="1">
+      <c r="F17" s="63">
+        <v>45495.3506597222</v>
+      </c>
+      <c r="G17" s="4">
         <v>2119.61</v>
       </c>
-      <c r="H17" s="69"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69">
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="7">
         <v>32.299999999999997</v>
       </c>
-      <c r="K17" s="69">
+      <c r="K17" s="7">
         <v>28.4</v>
       </c>
-      <c r="L17" s="69">
+      <c r="L17" s="7">
         <v>88.1</v>
       </c>
-      <c r="M17" s="69">
+      <c r="M17" s="7">
         <v>16.399999999999999</v>
       </c>
-      <c r="N17" s="69">
+      <c r="N17" s="7">
         <v>382</v>
       </c>
-      <c r="O17" s="69">
+      <c r="O17" s="7">
         <v>1.62</v>
       </c>
-      <c r="P17" s="69">
+      <c r="P17" s="7">
         <v>0.35</v>
       </c>
-      <c r="Q17" s="69">
+      <c r="Q17" s="7">
         <v>1.1599999999999999</v>
       </c>
-      <c r="R17" s="69"/>
-      <c r="S17" s="69">
+      <c r="R17" s="7"/>
+      <c r="S17" s="7">
         <v>0.46</v>
       </c>
-      <c r="T17" s="69">
+      <c r="T17" s="7">
         <v>0.92</v>
       </c>
-      <c r="U17" s="69">
+      <c r="U17" s="7">
         <v>1.68</v>
       </c>
-      <c r="V17" s="69">
+      <c r="V17" s="7">
         <v>7.1740000000000004</v>
       </c>
-      <c r="W17" s="69">
+      <c r="W17" s="7">
         <v>161.9</v>
       </c>
-      <c r="X17" s="69">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="69">
+      <c r="X17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="7">
         <v>2.3199999999999998</v>
       </c>
-      <c r="Z17" s="69">
+      <c r="Z17" s="7">
         <v>169.6</v>
       </c>
-      <c r="AA17" s="69">
+      <c r="AA17" s="7">
         <v>57.8</v>
       </c>
-      <c r="AB17" s="69">
+      <c r="AB17" s="7">
         <v>142</v>
       </c>
-      <c r="AC17" s="69">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="17">
+      <c r="AC17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="18">
         <v>7.2140000000000004</v>
       </c>
-      <c r="AE17" s="41"/>
-      <c r="AF17" s="69"/>
-      <c r="AG17" s="69"/>
-      <c r="AH17" s="70">
+      <c r="AE17" s="100"/>
+      <c r="AF17" s="44"/>
+      <c r="AG17" s="44"/>
+      <c r="AH17" s="44">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AI17" s="69"/>
-      <c r="AJ17" s="69"/>
-      <c r="AK17" s="69"/>
-      <c r="AL17" s="69"/>
-      <c r="AM17" s="70">
+      <c r="AI17" s="44"/>
+      <c r="AJ17" s="44"/>
+      <c r="AK17" s="44"/>
+      <c r="AL17" s="44"/>
+      <c r="AM17" s="44">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AN17" s="69"/>
-      <c r="AO17" s="69"/>
-      <c r="AP17" s="69"/>
-      <c r="AQ17" s="70">
-        <f>AN17-AN15</f>
+        <v>4.2769097222222226E-2</v>
+      </c>
+      <c r="AN17" s="44"/>
+      <c r="AO17" s="44"/>
+      <c r="AP17" s="44"/>
+      <c r="AQ17" s="44">
+        <f t="shared" si="23"/>
         <v>-33</v>
       </c>
-      <c r="AR17" s="70">
-        <f>AO17-AO15</f>
+      <c r="AR17" s="44">
+        <f t="shared" si="23"/>
         <v>-34</v>
       </c>
-      <c r="AS17" s="70">
+      <c r="AS17" s="44">
         <f>AP15-AP17</f>
         <v>743</v>
       </c>
-      <c r="AT17" s="25">
+      <c r="AT17" s="26">
         <v>15</v>
       </c>
-      <c r="AU17" s="106">
+      <c r="AU17" s="88">
         <v>1700</v>
       </c>
-      <c r="AV17" s="69">
+      <c r="AV17" s="7">
         <v>34</v>
       </c>
-      <c r="AW17" s="69">
+      <c r="AW17" s="7">
         <v>7.2</v>
       </c>
-      <c r="AX17" s="69">
+      <c r="AX17" s="7">
         <v>50</v>
       </c>
-      <c r="AY17" s="22">
+      <c r="AY17" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AZ17" s="11"/>
-      <c r="BA17" s="71"/>
-      <c r="BB17" s="22"/>
-      <c r="BC17" s="11">
+      <c r="AZ17" s="12">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="BA17" s="13"/>
+      <c r="BB17" s="23"/>
+      <c r="BC17" s="12">
         <f t="shared" si="0"/>
         <v>1.3844999999999998E-2</v>
       </c>
-      <c r="BD17" s="71">
+      <c r="BD17" s="13">
         <f t="shared" si="1"/>
         <v>19.936799999999998</v>
       </c>
-      <c r="BE17" s="71">
+      <c r="BE17" s="13">
         <f t="shared" si="17"/>
         <v>1625</v>
       </c>
-      <c r="BF17" s="72" t="e">
+      <c r="BF17" s="14" t="e">
         <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
-      <c r="BG17" s="72" t="e">
+      <c r="BG17" s="14" t="e">
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="BH17" s="72">
+      <c r="BH17" s="14">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BI17" s="72">
+        <v>61.587500000000006</v>
+      </c>
+      <c r="BI17" s="14">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BJ17" s="72" t="str">
+        <v>4.2769097222222226E-2</v>
+      </c>
+      <c r="BJ17" s="14" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="BK17" s="73" t="str">
+      <c r="BK17" s="36" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL17" s="72">
+      <c r="BL17" s="14">
         <f t="shared" si="19"/>
         <v>7.4749999999999996</v>
       </c>
-      <c r="BM17" s="93" t="str">
+      <c r="BM17" s="78" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="BN17" s="28">
+      <c r="BN17" s="29">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BO17" s="74">
+        <v>111.08856421356423</v>
+      </c>
+      <c r="BO17" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BP17" s="30">
+        <v>4.2769097222222226E-2</v>
+      </c>
+      <c r="BP17" s="31">
         <f t="shared" si="7"/>
         <v>7.4749999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="65">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="65">
         <v>5</v>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="2">
+      <c r="E18" s="65"/>
+      <c r="F18" s="66">
+        <v>45496.345405092601</v>
+      </c>
+      <c r="G18" s="64">
         <v>2716.05</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
-      <c r="AB18" s="6"/>
-      <c r="AC18" s="6"/>
-      <c r="AD18" s="16"/>
-      <c r="AE18" s="40"/>
-      <c r="AF18" s="6"/>
-      <c r="AG18" s="6"/>
-      <c r="AH18" s="43">
+      <c r="H18" s="67"/>
+      <c r="I18" s="67">
+        <v>2348.04</v>
+      </c>
+      <c r="J18" s="67">
+        <v>24.8</v>
+      </c>
+      <c r="K18" s="67">
+        <v>23.6</v>
+      </c>
+      <c r="L18" s="67">
+        <v>95.2</v>
+      </c>
+      <c r="M18" s="67">
+        <v>17.5</v>
+      </c>
+      <c r="N18" s="67">
+        <v>378</v>
+      </c>
+      <c r="O18" s="67">
+        <v>1.46</v>
+      </c>
+      <c r="P18" s="67">
+        <v>0.31</v>
+      </c>
+      <c r="Q18" s="67">
+        <v>5.87</v>
+      </c>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67">
+        <v>0.43</v>
+      </c>
+      <c r="T18" s="67">
+        <v>0.37</v>
+      </c>
+      <c r="U18" s="67">
+        <v>1.69</v>
+      </c>
+      <c r="V18" s="67">
+        <v>7.2469999999999999</v>
+      </c>
+      <c r="W18" s="67">
+        <v>133.6</v>
+      </c>
+      <c r="X18" s="67">
+        <v>46.5</v>
+      </c>
+      <c r="Y18" s="67">
+        <v>2.27</v>
+      </c>
+      <c r="Z18" s="67">
+        <v>153.19999999999999</v>
+      </c>
+      <c r="AA18" s="67">
+        <v>56.6</v>
+      </c>
+      <c r="AB18" s="67">
+        <v>117.2</v>
+      </c>
+      <c r="AC18" s="67">
+        <v>37.6</v>
+      </c>
+      <c r="AD18" s="96">
+        <v>7.2880000000000003</v>
+      </c>
+      <c r="AE18" s="42">
+        <v>300</v>
+      </c>
+      <c r="AF18" s="7">
+        <v>51.3</v>
+      </c>
+      <c r="AG18" s="7">
+        <v>7.25</v>
+      </c>
+      <c r="AH18" s="68">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI18" s="6"/>
-      <c r="AJ18" s="6"/>
-      <c r="AK18" s="6"/>
-      <c r="AL18" s="6"/>
-      <c r="AM18" s="43">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="AI18" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ18" s="7">
+        <v>27.67</v>
+      </c>
+      <c r="AK18" s="7">
+        <v>8.17</v>
+      </c>
+      <c r="AL18" s="67">
+        <v>6</v>
+      </c>
+      <c r="AM18" s="68">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AN18" s="6"/>
-      <c r="AO18" s="6"/>
-      <c r="AP18" s="6"/>
-      <c r="AQ18" s="43">
-        <f>AN18-AN16</f>
-        <v>-57</v>
-      </c>
-      <c r="AR18" s="43">
-        <f>AO18-AO16</f>
+        <v>4.7622754435182282E-2</v>
+      </c>
+      <c r="AN18" s="7">
+        <v>113</v>
+      </c>
+      <c r="AO18" s="7">
+        <v>43</v>
+      </c>
+      <c r="AP18" s="7">
+        <v>591</v>
+      </c>
+      <c r="AQ18" s="68">
+        <f t="shared" si="23"/>
+        <v>56</v>
+      </c>
+      <c r="AR18" s="68">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="AS18" s="68">
+        <f>AP16-AP18</f>
+        <v>61</v>
+      </c>
+      <c r="AT18" s="92">
+        <v>15</v>
+      </c>
+      <c r="AU18" s="89">
+        <v>1700</v>
+      </c>
+      <c r="AV18" s="67">
+        <v>34</v>
+      </c>
+      <c r="AW18" s="67">
+        <v>7.2</v>
+      </c>
+      <c r="AX18" s="67">
+        <v>50</v>
+      </c>
+      <c r="AY18" s="84">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="AZ18" s="81">
+        <v>3.7932984327519299E-2</v>
+      </c>
+      <c r="BA18" s="99">
+        <f>0.0180279302940535/BE18*24*60</f>
+        <v>1.4359799331487878E-2</v>
+      </c>
+      <c r="BB18">
+        <f>0.000180183999999999/BE18</f>
+        <v>9.9668112222320009E-8</v>
+      </c>
+      <c r="BC18" s="81">
+        <f t="shared" si="0"/>
+        <v>1.7066009600000001E-2</v>
+      </c>
+      <c r="BD18" s="69">
+        <f t="shared" si="1"/>
+        <v>24.575053824000001</v>
+      </c>
+      <c r="BE18" s="69">
+        <f t="shared" si="17"/>
+        <v>1807.84</v>
+      </c>
+      <c r="BF18" s="70">
+        <f t="shared" si="3"/>
+        <v>6.2505531462961325E-2</v>
+      </c>
+      <c r="BG18" s="70">
+        <f t="shared" si="4"/>
+        <v>6.6470588235294115E-2</v>
+      </c>
+      <c r="BH18" s="70">
+        <f t="shared" si="5"/>
+        <v>68.576766386662499</v>
+      </c>
+      <c r="BI18" s="70">
+        <f t="shared" si="10"/>
+        <v>4.7622754435182282E-2</v>
+      </c>
+      <c r="BJ18" s="70" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="BK18" s="71" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BL18" s="70">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BM18" s="82" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="BN18" s="75">
+        <f t="shared" si="11"/>
+        <v>123.69546606540854</v>
+      </c>
+      <c r="BO18" s="72">
+        <f t="shared" si="12"/>
+        <v>4.7622754435182282E-2</v>
+      </c>
+      <c r="BP18" s="73">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="65" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="65">
+        <v>12</v>
+      </c>
+      <c r="D19" s="65">
+        <v>6</v>
+      </c>
+      <c r="E19" s="65"/>
+      <c r="F19" s="66">
+        <v>45497.344409722202</v>
+      </c>
+      <c r="G19" s="64">
+        <v>3307.9</v>
+      </c>
+      <c r="H19" s="67"/>
+      <c r="I19" s="67">
+        <v>2987.82</v>
+      </c>
+      <c r="J19" s="67">
+        <v>23.1</v>
+      </c>
+      <c r="K19" s="67">
+        <v>22</v>
+      </c>
+      <c r="L19" s="67">
+        <v>95.6</v>
+      </c>
+      <c r="M19" s="67">
+        <v>18.2</v>
+      </c>
+      <c r="N19" s="67">
+        <v>406</v>
+      </c>
+      <c r="O19" s="67">
+        <v>2.33</v>
+      </c>
+      <c r="P19" s="67">
+        <v>0.27</v>
+      </c>
+      <c r="Q19" s="67">
+        <v>7.7</v>
+      </c>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67">
+        <v>0.65</v>
+      </c>
+      <c r="T19" s="67">
+        <v>2</v>
+      </c>
+      <c r="U19" s="67">
+        <v>1.75</v>
+      </c>
+      <c r="V19" s="67">
+        <v>7.1079999999999997</v>
+      </c>
+      <c r="W19" s="67">
+        <v>124.9</v>
+      </c>
+      <c r="X19" s="67">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="67">
+        <v>1.94</v>
+      </c>
+      <c r="Z19" s="67">
+        <v>158.80000000000001</v>
+      </c>
+      <c r="AA19" s="67">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="AB19" s="67">
+        <v>109.6</v>
+      </c>
+      <c r="AC19" s="67">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="96">
+        <v>7.1470000000000002</v>
+      </c>
+      <c r="AE19" s="91">
+        <v>300</v>
+      </c>
+      <c r="AF19" s="67">
+        <v>51.6</v>
+      </c>
+      <c r="AG19" s="67">
+        <v>7.13</v>
+      </c>
+      <c r="AH19" s="68">
+        <f t="shared" si="8"/>
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="AI19" s="67">
+        <v>34</v>
+      </c>
+      <c r="AJ19" s="67">
+        <v>27.67</v>
+      </c>
+      <c r="AK19" s="67">
+        <v>8.17</v>
+      </c>
+      <c r="AL19" s="67">
+        <v>6</v>
+      </c>
+      <c r="AM19" s="68">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN19" s="67">
+        <v>184</v>
+      </c>
+      <c r="AO19" s="67">
+        <v>43</v>
+      </c>
+      <c r="AP19" s="67">
+        <v>515</v>
+      </c>
+      <c r="AQ19" s="68">
+        <f t="shared" ref="AQ19:AR25" si="24">AN19-AN18</f>
+        <v>71</v>
+      </c>
+      <c r="AR19" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AS19" s="68">
+        <f>AP18-AP19</f>
+        <v>76</v>
+      </c>
+      <c r="AT19" s="92">
+        <v>15</v>
+      </c>
+      <c r="AU19" s="89">
+        <v>1700</v>
+      </c>
+      <c r="AV19" s="67">
+        <v>34</v>
+      </c>
+      <c r="AW19" s="67">
+        <v>7.2</v>
+      </c>
+      <c r="AX19" s="67">
+        <v>50</v>
+      </c>
+      <c r="AY19" s="84">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="AZ19" s="81"/>
+      <c r="BA19" s="69"/>
+      <c r="BB19" s="84"/>
+      <c r="BC19" s="81">
+        <f t="shared" si="0"/>
+        <v>1.6401792000000005E-2</v>
+      </c>
+      <c r="BD19" s="69">
+        <f t="shared" si="1"/>
+        <v>23.618580480000009</v>
+      </c>
+      <c r="BE19" s="69">
+        <f t="shared" si="17"/>
+        <v>1863.8400000000001</v>
+      </c>
+      <c r="BF19" s="70">
+        <f t="shared" si="3"/>
+        <v>9.8720920250665284E-2</v>
+      </c>
+      <c r="BG19" s="70">
+        <f t="shared" si="4"/>
+        <v>0.10823529411764705</v>
+      </c>
+      <c r="BH19" s="70">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BI19" s="70">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BJ19" s="70" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="BK19" s="71" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="BL19" s="70">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="BM19" s="82" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="BN19" s="75">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BO19" s="72">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BP19" s="73">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="65" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="65">
+        <v>12</v>
+      </c>
+      <c r="D20" s="65">
+        <v>7</v>
+      </c>
+      <c r="E20" s="65"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="64">
+        <v>3888.32</v>
+      </c>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="67"/>
+      <c r="P20" s="67"/>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="67"/>
+      <c r="T20" s="67"/>
+      <c r="U20" s="67"/>
+      <c r="V20" s="67"/>
+      <c r="W20" s="67"/>
+      <c r="X20" s="67"/>
+      <c r="Y20" s="67"/>
+      <c r="Z20" s="67"/>
+      <c r="AA20" s="67"/>
+      <c r="AB20" s="67"/>
+      <c r="AC20" s="67"/>
+      <c r="AD20" s="96"/>
+      <c r="AE20" s="91"/>
+      <c r="AF20" s="67"/>
+      <c r="AG20" s="67"/>
+      <c r="AH20" s="68">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="67"/>
+      <c r="AJ20" s="67"/>
+      <c r="AK20" s="67"/>
+      <c r="AL20" s="67"/>
+      <c r="AM20" s="68">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="67"/>
+      <c r="AO20" s="67"/>
+      <c r="AP20" s="67"/>
+      <c r="AQ20" s="68">
+        <f t="shared" si="24"/>
+        <v>-184</v>
+      </c>
+      <c r="AR20" s="68">
+        <f t="shared" si="24"/>
         <v>-43</v>
       </c>
-      <c r="AS18" s="43">
-        <f>AP16-AP18</f>
-        <v>652</v>
-      </c>
-      <c r="AT18" s="24">
+      <c r="AS20" s="68">
+        <f t="shared" ref="AS20:AS25" si="25">AP19-AP20</f>
+        <v>515</v>
+      </c>
+      <c r="AT20" s="92">
         <v>15</v>
       </c>
-      <c r="AU18" s="105">
+      <c r="AU20" s="89">
         <v>1700</v>
       </c>
-      <c r="AV18" s="6">
+      <c r="AV20" s="67">
         <v>34</v>
       </c>
-      <c r="AW18" s="6">
+      <c r="AW20" s="67">
         <v>7.2</v>
       </c>
-      <c r="AX18" s="6">
+      <c r="AX20" s="67">
         <v>50</v>
       </c>
-      <c r="AY18" s="21">
+      <c r="AY20" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ18" s="8"/>
-      <c r="BA18" s="9"/>
-      <c r="BB18" s="21"/>
-      <c r="BC18" s="8">
+      <c r="AZ20" s="81"/>
+      <c r="BA20" s="69"/>
+      <c r="BB20" s="84"/>
+      <c r="BC20" s="81">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BD18" s="9">
+      <c r="BD20" s="69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BE18" s="9">
+      <c r="BE20" s="69">
         <f t="shared" si="17"/>
-        <v>1610</v>
-      </c>
-      <c r="BF18" s="10" t="e">
+        <v>1580</v>
+      </c>
+      <c r="BF20" s="70" t="e">
         <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
-      <c r="BG18" s="10" t="e">
+      <c r="BG20" s="70" t="e">
         <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
-      <c r="BH18" s="10">
+      <c r="BH20" s="70">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BI18" s="10">
+      <c r="BI20" s="70">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BJ18" s="10" t="str">
+      <c r="BJ20" s="70" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="BK18" s="35" t="str">
+      <c r="BK20" s="71" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="BL18" s="10">
+      <c r="BL20" s="70">
         <f t="shared" si="19"/>
-        <v>12.074999999999999</v>
-      </c>
-      <c r="BM18" s="92" t="str">
+        <v>11.85</v>
+      </c>
+      <c r="BM20" s="82" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="BN18" s="27">
+      <c r="BN20" s="75">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BO18" s="37">
+      <c r="BO20" s="72">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BP18" s="32">
+      <c r="BP20" s="73">
         <f t="shared" si="7"/>
-        <v>12.074999999999999</v>
+        <v>11.85</v>
       </c>
     </row>
-    <row r="19" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="77" t="s">
+    <row r="21" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="78" t="s">
+      <c r="B21" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="78">
+      <c r="C21" s="65">
         <v>12</v>
       </c>
-      <c r="D19" s="78">
-        <v>6</v>
-      </c>
-      <c r="E19" s="78"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="77">
-        <v>3307.9</v>
-      </c>
-      <c r="H19" s="80"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="80"/>
-      <c r="L19" s="80"/>
-      <c r="M19" s="80"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="80"/>
-      <c r="Q19" s="80"/>
-      <c r="R19" s="80"/>
-      <c r="S19" s="80"/>
-      <c r="T19" s="80"/>
-      <c r="U19" s="80"/>
-      <c r="V19" s="80"/>
-      <c r="W19" s="80"/>
-      <c r="X19" s="80"/>
-      <c r="Y19" s="80"/>
-      <c r="Z19" s="80"/>
-      <c r="AA19" s="80"/>
-      <c r="AB19" s="80"/>
-      <c r="AC19" s="80"/>
-      <c r="AD19" s="115"/>
-      <c r="AE19" s="110"/>
-      <c r="AF19" s="80"/>
-      <c r="AG19" s="80"/>
-      <c r="AH19" s="81">
+      <c r="D21" s="65">
+        <v>8</v>
+      </c>
+      <c r="E21" s="65"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="64">
+        <v>4309.7</v>
+      </c>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
+      <c r="N21" s="67"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="67"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="67"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="67"/>
+      <c r="U21" s="67"/>
+      <c r="V21" s="67"/>
+      <c r="W21" s="67"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="67"/>
+      <c r="AA21" s="67"/>
+      <c r="AB21" s="67"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="96"/>
+      <c r="AE21" s="91"/>
+      <c r="AF21" s="67"/>
+      <c r="AG21" s="67"/>
+      <c r="AH21" s="68">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AI19" s="80"/>
-      <c r="AJ19" s="80"/>
-      <c r="AK19" s="80"/>
-      <c r="AL19" s="80"/>
-      <c r="AM19" s="81">
+      <c r="AI21" s="67"/>
+      <c r="AJ21" s="67"/>
+      <c r="AK21" s="67"/>
+      <c r="AL21" s="67"/>
+      <c r="AM21" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="80"/>
-      <c r="AO19" s="80"/>
-      <c r="AP19" s="80"/>
-      <c r="AQ19" s="81">
-        <f>AN19-AN18</f>
-        <v>0</v>
-      </c>
-      <c r="AR19" s="81">
-        <f>AO19-AO18</f>
-        <v>0</v>
-      </c>
-      <c r="AS19" s="81">
-        <f>AP18-AP19</f>
-        <v>0</v>
-      </c>
-      <c r="AT19" s="111">
+      <c r="AN21" s="67"/>
+      <c r="AO21" s="67"/>
+      <c r="AP21" s="67"/>
+      <c r="AQ21" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AR21" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AS21" s="68">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AT21" s="92">
         <v>15</v>
       </c>
-      <c r="AU19" s="108">
+      <c r="AU21" s="64">
         <v>1700</v>
       </c>
-      <c r="AV19" s="80">
+      <c r="AV21" s="67">
         <v>34</v>
       </c>
-      <c r="AW19" s="80">
+      <c r="AW21" s="67">
         <v>7.2</v>
       </c>
-      <c r="AX19" s="80">
+      <c r="AX21" s="67">
         <v>50</v>
       </c>
-      <c r="AY19" s="100">
+      <c r="AY21" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ19" s="97"/>
-      <c r="BA19" s="82"/>
-      <c r="BB19" s="100"/>
-      <c r="BC19" s="97">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BD19" s="82">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BE19" s="82">
+      <c r="AZ21" s="81"/>
+      <c r="BA21" s="69"/>
+      <c r="BB21" s="84"/>
+      <c r="BC21" s="81">
+        <f t="shared" ref="BC21:BC25" si="26">AY21*K21*BE21/1000</f>
+        <v>0</v>
+      </c>
+      <c r="BD21" s="69">
+        <f t="shared" ref="BD21:BD25" si="27">BC21*24*60</f>
+        <v>0</v>
+      </c>
+      <c r="BE21" s="69">
         <f t="shared" si="17"/>
-        <v>1595</v>
-      </c>
-      <c r="BF19" s="83" t="e">
-        <f t="shared" si="3"/>
+        <v>1565</v>
+      </c>
+      <c r="BF21" s="70" t="e">
+        <f t="shared" ref="BF21:BF25" si="28">IF(ISBLANK(AN21),NA(),IFERROR(AN21/BE21,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="BG19" s="83" t="e">
-        <f t="shared" si="4"/>
+      <c r="BG21" s="70" t="e">
+        <f t="shared" ref="BG21:BG25" si="29">IF(ISBLANK(AN21),NA(),AN21/AU21)</f>
         <v>#N/A</v>
       </c>
-      <c r="BH19" s="83">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BI19" s="83">
+      <c r="BH21" s="70">
+        <f t="shared" ref="BH21:BH25" si="30">AM21*24*60</f>
+        <v>0</v>
+      </c>
+      <c r="BI21" s="70">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BJ19" s="83" t="str">
+      <c r="BJ21" s="70" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="BK19" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="BK21" s="71" t="str">
+        <f t="shared" ref="BK21:BK25" si="31">IF(B21="No MPC", AY21*K21*BE21/1000,"")</f>
         <v/>
       </c>
-      <c r="BL19" s="83">
+      <c r="BL21" s="70">
         <f t="shared" si="19"/>
-        <v>11.9625</v>
-      </c>
-      <c r="BM19" s="98" t="str">
+        <v>11.737500000000001</v>
+      </c>
+      <c r="BM21" s="82" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="BN19" s="88">
+      <c r="BN21" s="75">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BO19" s="85">
+      <c r="BO21" s="72">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BP19" s="86">
-        <f t="shared" si="7"/>
-        <v>11.9625</v>
+      <c r="BP21" s="73">
+        <f t="shared" ref="BP21:BP25" si="32">IF(BL21&lt;&gt;"",BL21,BM21)</f>
+        <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="22" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="67" t="s">
+      <c r="B22" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="67">
+      <c r="C22" s="65">
         <v>12</v>
       </c>
-      <c r="D20" s="67">
-        <v>7</v>
-      </c>
-      <c r="E20" s="67"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="1">
-        <v>3888.32</v>
-      </c>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="69"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="69"/>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="69"/>
-      <c r="R20" s="69"/>
-      <c r="S20" s="69"/>
-      <c r="T20" s="69"/>
-      <c r="U20" s="69"/>
-      <c r="V20" s="69"/>
-      <c r="W20" s="69"/>
-      <c r="X20" s="69"/>
-      <c r="Y20" s="69"/>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="69"/>
-      <c r="AB20" s="69"/>
-      <c r="AC20" s="69"/>
-      <c r="AD20" s="17"/>
-      <c r="AE20" s="41"/>
-      <c r="AF20" s="69"/>
-      <c r="AG20" s="69"/>
-      <c r="AH20" s="70">
+      <c r="D22" s="65">
+        <v>9</v>
+      </c>
+      <c r="E22" s="65"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="64">
+        <v>4805.7299999999996</v>
+      </c>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="67"/>
+      <c r="X22" s="67"/>
+      <c r="Y22" s="67"/>
+      <c r="Z22" s="67"/>
+      <c r="AA22" s="67"/>
+      <c r="AB22" s="67"/>
+      <c r="AC22" s="67"/>
+      <c r="AD22" s="96"/>
+      <c r="AE22" s="91"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="68">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AI20" s="69"/>
-      <c r="AJ20" s="69"/>
-      <c r="AK20" s="69"/>
-      <c r="AL20" s="69"/>
-      <c r="AM20" s="70">
+      <c r="AI22" s="67"/>
+      <c r="AJ22" s="67"/>
+      <c r="AK22" s="67"/>
+      <c r="AL22" s="67"/>
+      <c r="AM22" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN20" s="69"/>
-      <c r="AO20" s="69"/>
-      <c r="AP20" s="69"/>
-      <c r="AQ20" s="70">
-        <f>AN20-AN19</f>
-        <v>0</v>
-      </c>
-      <c r="AR20" s="70">
-        <f>AO20-AO19</f>
-        <v>0</v>
-      </c>
-      <c r="AS20" s="70">
-        <f>AP19-AP20</f>
-        <v>0</v>
-      </c>
-      <c r="AT20" s="25">
+      <c r="AN22" s="67"/>
+      <c r="AO22" s="67"/>
+      <c r="AP22" s="67"/>
+      <c r="AQ22" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AR22" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AS22" s="68">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AT22" s="92">
         <v>15</v>
       </c>
-      <c r="AU20" s="106">
+      <c r="AU22" s="64">
         <v>1700</v>
       </c>
-      <c r="AV20" s="69">
+      <c r="AV22" s="67">
         <v>34</v>
       </c>
-      <c r="AW20" s="69">
+      <c r="AW22" s="67">
         <v>7.2</v>
       </c>
-      <c r="AX20" s="69">
+      <c r="AX22" s="67">
         <v>50</v>
       </c>
-      <c r="AY20" s="22">
+      <c r="AY22" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ20" s="11"/>
-      <c r="BA20" s="71"/>
-      <c r="BB20" s="22"/>
-      <c r="BC20" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BD20" s="71">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BE20" s="71">
-        <f t="shared" si="17"/>
-        <v>1580</v>
-      </c>
-      <c r="BF20" s="72" t="e">
-        <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BG20" s="72" t="e">
-        <f t="shared" si="4"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BH20" s="72">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BI20" s="72">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BJ20" s="72" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="BK20" s="73" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="BL20" s="72">
-        <f t="shared" si="19"/>
-        <v>11.85</v>
-      </c>
-      <c r="BM20" s="93" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="BN20" s="28">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BO20" s="74">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BP20" s="30">
-        <f t="shared" si="7"/>
-        <v>11.85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="77" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="78" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="78">
-        <v>12</v>
-      </c>
-      <c r="D21" s="78">
-        <v>8</v>
-      </c>
-      <c r="E21" s="78"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="77">
-        <v>4309.7</v>
-      </c>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="80"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="80"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="80"/>
-      <c r="S21" s="80"/>
-      <c r="T21" s="80"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="80"/>
-      <c r="W21" s="80"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="80"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="80"/>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="115"/>
-      <c r="AE21" s="110"/>
-      <c r="AF21" s="80"/>
-      <c r="AG21" s="80"/>
-      <c r="AH21" s="81">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI21" s="80"/>
-      <c r="AJ21" s="80"/>
-      <c r="AK21" s="80"/>
-      <c r="AL21" s="80"/>
-      <c r="AM21" s="81">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AN21" s="80"/>
-      <c r="AO21" s="80"/>
-      <c r="AP21" s="80"/>
-      <c r="AQ21" s="81">
-        <f>AN21-AN20</f>
-        <v>0</v>
-      </c>
-      <c r="AR21" s="81">
-        <f>AO21-AO20</f>
-        <v>0</v>
-      </c>
-      <c r="AS21" s="81">
-        <f>AP20-AP21</f>
-        <v>0</v>
-      </c>
-      <c r="AT21" s="111">
-        <v>15</v>
-      </c>
-      <c r="AU21" s="77">
-        <v>1700</v>
-      </c>
-      <c r="AV21" s="80">
-        <v>34</v>
-      </c>
-      <c r="AW21" s="80">
-        <v>7.2</v>
-      </c>
-      <c r="AX21" s="80">
-        <v>50</v>
-      </c>
-      <c r="AY21" s="100">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="AZ21" s="97"/>
-      <c r="BA21" s="82"/>
-      <c r="BB21" s="100"/>
-      <c r="BC21" s="97">
-        <f t="shared" ref="BC21:BC25" si="23">AY21*K21*BE21/1000</f>
-        <v>0</v>
-      </c>
-      <c r="BD21" s="82">
-        <f t="shared" ref="BD21:BD25" si="24">BC21*24*60</f>
-        <v>0</v>
-      </c>
-      <c r="BE21" s="82">
-        <f t="shared" si="17"/>
-        <v>1565</v>
-      </c>
-      <c r="BF21" s="83" t="e">
-        <f t="shared" ref="BF21:BF25" si="25">IF(ISBLANK(AN21),NA(),IFERROR(AN21/BE21,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="BG21" s="83" t="e">
-        <f t="shared" ref="BG21:BG25" si="26">IF(ISBLANK(AN21),NA(),AN21/AU21)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="BH21" s="83">
-        <f t="shared" ref="BH21:BH25" si="27">AM21*24*60</f>
-        <v>0</v>
-      </c>
-      <c r="BI21" s="83">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BJ21" s="83" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="BK21" s="84" t="str">
-        <f t="shared" ref="BK21:BK25" si="28">IF(B21="No MPC", AY21*K21*BE21/1000,"")</f>
-        <v/>
-      </c>
-      <c r="BL21" s="83">
-        <f t="shared" si="19"/>
-        <v>11.737500000000001</v>
-      </c>
-      <c r="BM21" s="98" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="BN21" s="88">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BO21" s="85">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BP21" s="86">
-        <f t="shared" ref="BP21:BP25" si="29">IF(BL21&lt;&gt;"",BL21,BM21)</f>
-        <v>11.737500000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="67" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="67">
-        <v>12</v>
-      </c>
-      <c r="D22" s="67">
-        <v>9</v>
-      </c>
-      <c r="E22" s="67"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="1">
-        <v>4805.7299999999996</v>
-      </c>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="69"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="69"/>
-      <c r="S22" s="69"/>
-      <c r="T22" s="69"/>
-      <c r="U22" s="69"/>
-      <c r="V22" s="69"/>
-      <c r="W22" s="69"/>
-      <c r="X22" s="69"/>
-      <c r="Y22" s="69"/>
-      <c r="Z22" s="69"/>
-      <c r="AA22" s="69"/>
-      <c r="AB22" s="69"/>
-      <c r="AC22" s="69"/>
-      <c r="AD22" s="17"/>
-      <c r="AE22" s="41"/>
-      <c r="AF22" s="69"/>
-      <c r="AG22" s="69"/>
-      <c r="AH22" s="70">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI22" s="69"/>
-      <c r="AJ22" s="69"/>
-      <c r="AK22" s="69"/>
-      <c r="AL22" s="69"/>
-      <c r="AM22" s="70">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AN22" s="69"/>
-      <c r="AO22" s="69"/>
-      <c r="AP22" s="69"/>
-      <c r="AQ22" s="70">
-        <f>AN22-AN21</f>
-        <v>0</v>
-      </c>
-      <c r="AR22" s="70">
-        <f>AO22-AO21</f>
-        <v>0</v>
-      </c>
-      <c r="AS22" s="70">
-        <f>AP21-AP22</f>
-        <v>0</v>
-      </c>
-      <c r="AT22" s="25">
-        <v>15</v>
-      </c>
-      <c r="AU22" s="1">
-        <v>1700</v>
-      </c>
-      <c r="AV22" s="69">
-        <v>34</v>
-      </c>
-      <c r="AW22" s="69">
-        <v>7.2</v>
-      </c>
-      <c r="AX22" s="69">
-        <v>50</v>
-      </c>
-      <c r="AY22" s="22">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="AZ22" s="11"/>
-      <c r="BA22" s="71"/>
-      <c r="BB22" s="22"/>
-      <c r="BC22" s="11">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="BD22" s="71">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BE22" s="71">
+      <c r="AZ22" s="81"/>
+      <c r="BA22" s="69"/>
+      <c r="BB22" s="84"/>
+      <c r="BC22" s="81">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BD22" s="69">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BE22" s="69">
         <f t="shared" si="17"/>
         <v>1550</v>
       </c>
-      <c r="BF22" s="72" t="e">
-        <f t="shared" si="25"/>
+      <c r="BF22" s="70" t="e">
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="BG22" s="72" t="e">
-        <f t="shared" si="26"/>
+      <c r="BG22" s="70" t="e">
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
-      <c r="BH22" s="72">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI22" s="72">
-        <f t="shared" ref="BI22:BI25" si="30">IF(B22="Python",AZ22*BE22/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BJ22" s="72" t="str">
-        <f t="shared" ref="BJ22:BJ25" si="31">IF(B22="Julia",BA22*BE22/24/60,"")</f>
+      <c r="BH22" s="70">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BI22" s="70">
+        <f t="shared" ref="BI22:BI25" si="33">IF(B22="Python",AZ22*BE22/24/60,"")</f>
+        <v>0</v>
+      </c>
+      <c r="BJ22" s="70" t="str">
+        <f t="shared" ref="BJ22:BJ25" si="34">IF(B22="Julia",BA22*BE22/24/60,"")</f>
         <v/>
       </c>
-      <c r="BK22" s="73" t="str">
-        <f t="shared" si="28"/>
+      <c r="BK22" s="71" t="str">
+        <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="BL22" s="72">
+      <c r="BL22" s="70">
         <f t="shared" si="19"/>
         <v>11.625</v>
       </c>
-      <c r="BM22" s="93" t="str">
-        <f t="shared" ref="BM22:BM25" si="32">IF(B22="Julia",BB22*BE22,"")</f>
+      <c r="BM22" s="82" t="str">
+        <f t="shared" ref="BM22:BM25" si="35">IF(B22="Julia",BB22*BE22,"")</f>
         <v/>
       </c>
-      <c r="BN22" s="28">
+      <c r="BN22" s="75">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BO22" s="74">
+      <c r="BO22" s="72">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BP22" s="30">
-        <f t="shared" si="29"/>
+      <c r="BP22" s="73">
+        <f t="shared" si="32"/>
         <v>11.625</v>
       </c>
     </row>
-    <row r="23" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="65">
         <v>12</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="65">
         <v>10</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="116">
+      <c r="E23" s="65"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="97">
         <v>5497.99</v>
       </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="6"/>
-      <c r="AB23" s="6"/>
-      <c r="AC23" s="6"/>
-      <c r="AD23" s="16"/>
-      <c r="AE23" s="40"/>
-      <c r="AF23" s="6"/>
-      <c r="AG23" s="6"/>
-      <c r="AH23" s="43">
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="67"/>
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67"/>
+      <c r="Z23" s="67"/>
+      <c r="AA23" s="67"/>
+      <c r="AB23" s="67"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="96"/>
+      <c r="AE23" s="91"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="67"/>
+      <c r="AH23" s="68">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AI23" s="6"/>
-      <c r="AJ23" s="6"/>
-      <c r="AK23" s="6"/>
-      <c r="AL23" s="6"/>
-      <c r="AM23" s="43">
+      <c r="AI23" s="67"/>
+      <c r="AJ23" s="67"/>
+      <c r="AK23" s="67"/>
+      <c r="AL23" s="67"/>
+      <c r="AM23" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="6"/>
-      <c r="AO23" s="6"/>
-      <c r="AP23" s="6"/>
-      <c r="AQ23" s="43">
-        <f>AN23-AN22</f>
-        <v>0</v>
-      </c>
-      <c r="AR23" s="43">
-        <f>AO23-AO22</f>
-        <v>0</v>
-      </c>
-      <c r="AS23" s="43">
-        <f>AP22-AP23</f>
-        <v>0</v>
-      </c>
-      <c r="AT23" s="24">
+      <c r="AN23" s="67"/>
+      <c r="AO23" s="67"/>
+      <c r="AP23" s="67"/>
+      <c r="AQ23" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AR23" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AS23" s="68">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AT23" s="92">
         <v>15</v>
       </c>
-      <c r="AU23" s="2">
+      <c r="AU23" s="64">
         <v>1700</v>
       </c>
-      <c r="AV23" s="6">
+      <c r="AV23" s="67">
         <v>34</v>
       </c>
-      <c r="AW23" s="6">
+      <c r="AW23" s="67">
         <v>7.2</v>
       </c>
-      <c r="AX23" s="6">
+      <c r="AX23" s="67">
         <v>50</v>
       </c>
-      <c r="AY23" s="21">
+      <c r="AY23" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ23" s="8"/>
-      <c r="BA23" s="9"/>
-      <c r="BB23" s="21"/>
-      <c r="BC23" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="BD23" s="9">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BE23" s="9">
+      <c r="AZ23" s="81"/>
+      <c r="BA23" s="69"/>
+      <c r="BB23" s="84"/>
+      <c r="BC23" s="81">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BD23" s="69">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BE23" s="69">
         <f t="shared" si="17"/>
         <v>1535</v>
       </c>
-      <c r="BF23" s="10" t="e">
-        <f t="shared" si="25"/>
+      <c r="BF23" s="70" t="e">
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="BG23" s="10" t="e">
-        <f t="shared" si="26"/>
+      <c r="BG23" s="70" t="e">
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
-      <c r="BH23" s="10">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI23" s="10">
+      <c r="BH23" s="70">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="BJ23" s="10" t="str">
+      <c r="BI23" s="70">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BJ23" s="70" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="BK23" s="71" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="BK23" s="35" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BL23" s="10">
+      <c r="BL23" s="70">
         <f t="shared" si="19"/>
         <v>11.512499999999999</v>
       </c>
-      <c r="BM23" s="92" t="str">
+      <c r="BM23" s="82" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BN23" s="75">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BO23" s="72">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BP23" s="73">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="BN23" s="27">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="BO23" s="37">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="BP23" s="32">
-        <f t="shared" si="29"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="65">
         <v>12</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="65">
         <v>11</v>
       </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="116">
+      <c r="E24" s="65"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="97">
         <v>6057.48</v>
       </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6"/>
-      <c r="AB24" s="6"/>
-      <c r="AC24" s="6"/>
-      <c r="AD24" s="16"/>
-      <c r="AE24" s="40"/>
-      <c r="AF24" s="6"/>
-      <c r="AG24" s="6"/>
-      <c r="AH24" s="43">
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67"/>
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="67"/>
+      <c r="AA24" s="67"/>
+      <c r="AB24" s="67"/>
+      <c r="AC24" s="67"/>
+      <c r="AD24" s="96"/>
+      <c r="AE24" s="91"/>
+      <c r="AF24" s="67"/>
+      <c r="AG24" s="67"/>
+      <c r="AH24" s="68">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AI24" s="6"/>
-      <c r="AJ24" s="6"/>
-      <c r="AK24" s="6"/>
-      <c r="AL24" s="6"/>
-      <c r="AM24" s="43">
+      <c r="AI24" s="67"/>
+      <c r="AJ24" s="67"/>
+      <c r="AK24" s="67"/>
+      <c r="AL24" s="67"/>
+      <c r="AM24" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN24" s="6"/>
-      <c r="AO24" s="6"/>
-      <c r="AP24" s="6"/>
-      <c r="AQ24" s="43">
-        <f>AN24-AN23</f>
-        <v>0</v>
-      </c>
-      <c r="AR24" s="43">
-        <f>AO24-AO23</f>
-        <v>0</v>
-      </c>
-      <c r="AS24" s="43">
-        <f>AP23-AP24</f>
-        <v>0</v>
-      </c>
-      <c r="AT24" s="24">
+      <c r="AN24" s="67"/>
+      <c r="AO24" s="67"/>
+      <c r="AP24" s="67"/>
+      <c r="AQ24" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AR24" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AS24" s="68">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AT24" s="92">
         <v>15</v>
       </c>
-      <c r="AU24" s="2">
+      <c r="AU24" s="64">
         <v>1700</v>
       </c>
-      <c r="AV24" s="6">
+      <c r="AV24" s="67">
         <v>34</v>
       </c>
-      <c r="AW24" s="6">
+      <c r="AW24" s="67">
         <v>7.2</v>
       </c>
-      <c r="AX24" s="6">
+      <c r="AX24" s="67">
         <v>50</v>
       </c>
-      <c r="AY24" s="21">
+      <c r="AY24" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ24" s="8"/>
-      <c r="BA24" s="9"/>
-      <c r="BB24" s="21"/>
-      <c r="BC24" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="BD24" s="9">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BE24" s="9">
+      <c r="AZ24" s="81"/>
+      <c r="BA24" s="69"/>
+      <c r="BB24" s="84"/>
+      <c r="BC24" s="81">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BD24" s="69">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BE24" s="69">
         <f t="shared" si="17"/>
         <v>1520</v>
       </c>
-      <c r="BF24" s="10" t="e">
-        <f t="shared" si="25"/>
+      <c r="BF24" s="70" t="e">
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="BG24" s="10" t="e">
-        <f t="shared" si="26"/>
+      <c r="BG24" s="70" t="e">
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
-      <c r="BH24" s="10">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI24" s="10">
+      <c r="BH24" s="70">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="BJ24" s="10" t="str">
+      <c r="BI24" s="70">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BJ24" s="70" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="BK24" s="71" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="BK24" s="35" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BL24" s="10">
+      <c r="BL24" s="70">
         <f t="shared" si="19"/>
         <v>11.4</v>
       </c>
-      <c r="BM24" s="92" t="str">
+      <c r="BM24" s="82" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BN24" s="75">
+        <f t="shared" ref="BN24:BN25" si="36">IF(BI24&lt;&gt;"",BI24/0.000385,IF(BJ24&lt;&gt;"",BJ24/0.000385,BK24/0.000385))</f>
+        <v>0</v>
+      </c>
+      <c r="BO24" s="72">
+        <f t="shared" ref="BO24" si="37">IF(BI24&lt;&gt;"",BI24,IF(BJ24&lt;&gt;"",BJ24,BK24))</f>
+        <v>0</v>
+      </c>
+      <c r="BP24" s="73">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="BN24" s="27">
-        <f t="shared" ref="BN24:BN25" si="33">IF(BI24&lt;&gt;"",BI24/0.000385,IF(BJ24&lt;&gt;"",BJ24/0.000385,BK24/0.000385))</f>
-        <v>0</v>
-      </c>
-      <c r="BO24" s="37">
-        <f t="shared" ref="BO24" si="34">IF(BI24&lt;&gt;"",BI24,IF(BJ24&lt;&gt;"",BJ24,BK24))</f>
-        <v>0</v>
-      </c>
-      <c r="BP24" s="32">
-        <f t="shared" si="29"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="25" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="77" t="s">
+    <row r="25" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="78" t="s">
+      <c r="B25" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="78">
+      <c r="C25" s="65">
         <v>12</v>
       </c>
-      <c r="D25" s="78">
+      <c r="D25" s="65">
         <v>12</v>
       </c>
-      <c r="E25" s="78"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="117">
+      <c r="E25" s="65"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="97">
         <v>6478.05</v>
       </c>
-      <c r="H25" s="78"/>
-      <c r="I25" s="80"/>
-      <c r="J25" s="80"/>
-      <c r="K25" s="80"/>
-      <c r="L25" s="80"/>
-      <c r="M25" s="80"/>
-      <c r="N25" s="80"/>
-      <c r="O25" s="80"/>
-      <c r="P25" s="80"/>
-      <c r="Q25" s="80"/>
-      <c r="R25" s="80"/>
-      <c r="S25" s="80"/>
-      <c r="T25" s="80"/>
-      <c r="U25" s="80"/>
-      <c r="V25" s="80"/>
-      <c r="W25" s="80"/>
-      <c r="X25" s="80"/>
-      <c r="Y25" s="80"/>
-      <c r="Z25" s="80"/>
-      <c r="AA25" s="80"/>
-      <c r="AB25" s="80"/>
-      <c r="AC25" s="80"/>
-      <c r="AD25" s="115"/>
-      <c r="AE25" s="110"/>
-      <c r="AF25" s="80"/>
-      <c r="AG25" s="80"/>
-      <c r="AH25" s="81">
+      <c r="H25" s="65"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="67"/>
+      <c r="X25" s="67"/>
+      <c r="Y25" s="67"/>
+      <c r="Z25" s="67"/>
+      <c r="AA25" s="67"/>
+      <c r="AB25" s="67"/>
+      <c r="AC25" s="67"/>
+      <c r="AD25" s="96"/>
+      <c r="AE25" s="91"/>
+      <c r="AF25" s="67"/>
+      <c r="AG25" s="67"/>
+      <c r="AH25" s="68">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AI25" s="80"/>
-      <c r="AJ25" s="80"/>
-      <c r="AK25" s="80"/>
-      <c r="AL25" s="80"/>
-      <c r="AM25" s="81">
+      <c r="AI25" s="67"/>
+      <c r="AJ25" s="67"/>
+      <c r="AK25" s="67"/>
+      <c r="AL25" s="67"/>
+      <c r="AM25" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="80"/>
-      <c r="AO25" s="80"/>
-      <c r="AP25" s="80"/>
-      <c r="AQ25" s="81">
-        <f>AN25-AN24</f>
-        <v>0</v>
-      </c>
-      <c r="AR25" s="81">
-        <f>AO25-AO24</f>
-        <v>0</v>
-      </c>
-      <c r="AS25" s="81">
-        <f>AP24-AP25</f>
-        <v>0</v>
-      </c>
-      <c r="AT25" s="111">
+      <c r="AN25" s="67"/>
+      <c r="AO25" s="67"/>
+      <c r="AP25" s="67"/>
+      <c r="AQ25" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AR25" s="68">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AS25" s="68">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AT25" s="92">
         <v>15</v>
       </c>
-      <c r="AU25" s="77">
+      <c r="AU25" s="64">
         <v>1700</v>
       </c>
-      <c r="AV25" s="80">
+      <c r="AV25" s="67">
         <v>34</v>
       </c>
-      <c r="AW25" s="80">
+      <c r="AW25" s="67">
         <v>7.2</v>
       </c>
-      <c r="AX25" s="80">
+      <c r="AX25" s="67">
         <v>50</v>
       </c>
-      <c r="AY25" s="100">
+      <c r="AY25" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ25" s="97"/>
-      <c r="BA25" s="78"/>
-      <c r="BB25" s="101"/>
-      <c r="BC25" s="97">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="BD25" s="82">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="BE25" s="82">
+      <c r="AZ25" s="81"/>
+      <c r="BA25" s="65"/>
+      <c r="BB25" s="85"/>
+      <c r="BC25" s="81">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BD25" s="69">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="BE25" s="69">
         <f t="shared" si="17"/>
         <v>1505</v>
       </c>
-      <c r="BF25" s="83" t="e">
-        <f t="shared" si="25"/>
+      <c r="BF25" s="70" t="e">
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="BG25" s="83" t="e">
-        <f t="shared" si="26"/>
+      <c r="BG25" s="70" t="e">
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
-      <c r="BH25" s="83">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="BI25" s="83">
+      <c r="BH25" s="70">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="BJ25" s="83" t="str">
+      <c r="BI25" s="70">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BJ25" s="70" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="BK25" s="71" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="BK25" s="84" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="BL25" s="83">
+      <c r="BL25" s="70">
         <f t="shared" si="19"/>
         <v>11.2875</v>
       </c>
-      <c r="BM25" s="98" t="str">
+      <c r="BM25" s="82" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="BN25" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="BO25" s="72">
+        <f>IF(BI25&lt;&gt;"",BI25,IF(BJ25&lt;&gt;"",BJ25,BK25))</f>
+        <v>0</v>
+      </c>
+      <c r="BP25" s="73">
         <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="BN25" s="88">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BO25" s="85">
-        <f>IF(BI25&lt;&gt;"",BI25,IF(BJ25&lt;&gt;"",BJ25,BK25))</f>
-        <v>0</v>
-      </c>
-      <c r="BP25" s="86">
-        <f t="shared" si="29"/>
         <v>11.2875</v>
       </c>
     </row>
-    <row r="28" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:68" x14ac:dyDescent="0.3">
       <c r="S28" s="39"/>
     </row>
   </sheetData>
@@ -6358,13 +6520,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A841E7D6-1405-4AC8-A599-0CE4601ECD66}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -6587,34 +6776,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6631,29 +6818,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
+++ b/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-038-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="537" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{297C3AE4-042B-4D04-A2F8-688BF6A89B74}"/>
+  <xr:revisionPtr revIDLastSave="559" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{123E69FD-5553-4086-AA0E-C4845C436807}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -5047,7 +5047,7 @@
       <c r="AL17" s="44"/>
       <c r="AM17" s="44">
         <f t="shared" si="9"/>
-        <v>4.2769097222222226E-2</v>
+        <v>0</v>
       </c>
       <c r="AN17" s="44"/>
       <c r="AO17" s="44"/>
@@ -5082,9 +5082,7 @@
       <c r="AY17" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="AZ17" s="12">
-        <v>3.7900000000000003E-2</v>
-      </c>
+      <c r="AZ17" s="12"/>
       <c r="BA17" s="13"/>
       <c r="BB17" s="23"/>
       <c r="BC17" s="12">
@@ -5109,11 +5107,11 @@
       </c>
       <c r="BH17" s="14">
         <f t="shared" si="5"/>
-        <v>61.587500000000006</v>
+        <v>0</v>
       </c>
       <c r="BI17" s="14">
         <f t="shared" si="10"/>
-        <v>4.2769097222222226E-2</v>
+        <v>0</v>
       </c>
       <c r="BJ17" s="14" t="str">
         <f t="shared" si="13"/>
@@ -5133,11 +5131,11 @@
       </c>
       <c r="BN17" s="29">
         <f t="shared" si="11"/>
-        <v>111.08856421356423</v>
+        <v>0</v>
       </c>
       <c r="BO17" s="38">
         <f t="shared" si="12"/>
-        <v>4.2769097222222226E-2</v>
+        <v>0</v>
       </c>
       <c r="BP17" s="31">
         <f t="shared" si="7"/>
@@ -5301,11 +5299,11 @@
         <v>3.7932984327519299E-2</v>
       </c>
       <c r="BA18" s="99">
-        <f>0.0180279302940535/BE18*24*60</f>
-        <v>1.4359799331487878E-2</v>
-      </c>
-      <c r="BB18">
-        <f>0.000180183999999999/BE18</f>
+        <f>BJ18*24*60/BE18</f>
+        <v>1.4359799331487877E-2</v>
+      </c>
+      <c r="BB18" s="99">
+        <f>BM18/BE18</f>
         <v>9.9668112222320009E-8</v>
       </c>
       <c r="BC18" s="81">
@@ -5336,9 +5334,8 @@
         <f t="shared" si="10"/>
         <v>4.7622754435182282E-2</v>
       </c>
-      <c r="BJ18" s="70" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+      <c r="BJ18" s="70">
+        <v>1.8027930294053501E-2</v>
       </c>
       <c r="BK18" s="71" t="str">
         <f t="shared" si="6"/>
@@ -5348,9 +5345,8 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BM18" s="82" t="str">
-        <f t="shared" si="14"/>
-        <v/>
+      <c r="BM18" s="82">
+        <v>1.8018399999999901E-4</v>
       </c>
       <c r="BN18" s="75">
         <f t="shared" si="11"/>
@@ -5477,7 +5473,7 @@
       </c>
       <c r="AM19" s="68">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4.0639629441766648E-2</v>
       </c>
       <c r="AN19" s="67">
         <v>184</v>
@@ -5518,9 +5514,17 @@
       <c r="AY19" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ19" s="81"/>
-      <c r="BA19" s="69"/>
-      <c r="BB19" s="84"/>
+      <c r="AZ19" s="81">
+        <v>3.1398117003682703E-2</v>
+      </c>
+      <c r="BA19" s="99">
+        <f>BJ19*24*60/BE19</f>
+        <v>5.8037926537741662E-3</v>
+      </c>
+      <c r="BB19" s="99">
+        <f>BM19/BE19</f>
+        <v>9.9999999999999995E-8</v>
+      </c>
       <c r="BC19" s="81">
         <f t="shared" si="0"/>
         <v>1.6401792000000005E-2</v>
@@ -5543,15 +5547,14 @@
       </c>
       <c r="BH19" s="70">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>58.521066396143972</v>
       </c>
       <c r="BI19" s="70">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BJ19" s="70" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <v>4.0639629441766648E-2</v>
+      </c>
+      <c r="BJ19" s="70">
+        <v>7.5120422915350296E-3</v>
       </c>
       <c r="BK19" s="71" t="str">
         <f t="shared" si="6"/>
@@ -5561,17 +5564,16 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BM19" s="82" t="str">
-        <f t="shared" si="14"/>
-        <v/>
+      <c r="BM19" s="82">
+        <v>1.86384E-4</v>
       </c>
       <c r="BN19" s="75">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>105.55747906952377</v>
       </c>
       <c r="BO19" s="72">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4.0639629441766648E-2</v>
       </c>
       <c r="BP19" s="73">
         <f t="shared" si="7"/>
@@ -5592,62 +5594,126 @@
         <v>7</v>
       </c>
       <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
+      <c r="F20" s="66">
+        <v>45498.335474537002</v>
+      </c>
       <c r="G20" s="64">
         <v>3888.32</v>
       </c>
       <c r="H20" s="67"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="67"/>
-      <c r="K20" s="67"/>
-      <c r="L20" s="67"/>
-      <c r="M20" s="67"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="67"/>
-      <c r="Q20" s="67"/>
+      <c r="I20" s="67">
+        <v>3528.9749999999999</v>
+      </c>
+      <c r="J20" s="67">
+        <v>24.7</v>
+      </c>
+      <c r="K20" s="67">
+        <v>23.6</v>
+      </c>
+      <c r="L20" s="67">
+        <v>95.7</v>
+      </c>
+      <c r="M20" s="67">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="N20" s="67">
+        <v>438</v>
+      </c>
+      <c r="O20" s="67">
+        <v>2.58</v>
+      </c>
+      <c r="P20" s="67">
+        <v>0.27</v>
+      </c>
+      <c r="Q20" s="67">
+        <v>7.81</v>
+      </c>
       <c r="R20" s="67"/>
-      <c r="S20" s="67"/>
-      <c r="T20" s="67"/>
-      <c r="U20" s="67"/>
-      <c r="V20" s="67"/>
-      <c r="W20" s="67"/>
-      <c r="X20" s="67"/>
-      <c r="Y20" s="67"/>
-      <c r="Z20" s="67"/>
-      <c r="AA20" s="67"/>
-      <c r="AB20" s="67"/>
-      <c r="AC20" s="67"/>
-      <c r="AD20" s="96"/>
-      <c r="AE20" s="91"/>
-      <c r="AF20" s="67"/>
-      <c r="AG20" s="67"/>
+      <c r="S20" s="67">
+        <v>0.89</v>
+      </c>
+      <c r="T20" s="67">
+        <v>3.24</v>
+      </c>
+      <c r="U20" s="67">
+        <v>1.87</v>
+      </c>
+      <c r="V20" s="67">
+        <v>7.0670000000000002</v>
+      </c>
+      <c r="W20" s="67">
+        <v>174.1</v>
+      </c>
+      <c r="X20" s="67">
+        <v>5.5</v>
+      </c>
+      <c r="Y20" s="67">
+        <v>1.78</v>
+      </c>
+      <c r="Z20" s="67">
+        <v>162.80000000000001</v>
+      </c>
+      <c r="AA20" s="67">
+        <v>48.4</v>
+      </c>
+      <c r="AB20" s="67">
+        <v>152.6</v>
+      </c>
+      <c r="AC20" s="67">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AD20" s="96">
+        <v>7.1050000000000004</v>
+      </c>
+      <c r="AE20" s="91">
+        <v>300</v>
+      </c>
+      <c r="AF20" s="67">
+        <v>54.4</v>
+      </c>
+      <c r="AG20" s="67">
+        <v>7.1</v>
+      </c>
       <c r="AH20" s="68">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI20" s="67"/>
-      <c r="AJ20" s="67"/>
-      <c r="AK20" s="67"/>
-      <c r="AL20" s="67"/>
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="AI20" s="67">
+        <v>34</v>
+      </c>
+      <c r="AJ20" s="67">
+        <v>30.1</v>
+      </c>
+      <c r="AK20" s="67">
+        <v>8.17</v>
+      </c>
+      <c r="AL20" s="67">
+        <v>6</v>
+      </c>
       <c r="AM20" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN20" s="67"/>
-      <c r="AO20" s="67"/>
-      <c r="AP20" s="67"/>
+      <c r="AN20" s="67">
+        <v>244</v>
+      </c>
+      <c r="AO20" s="67">
+        <v>43</v>
+      </c>
+      <c r="AP20" s="67">
+        <v>450</v>
+      </c>
       <c r="AQ20" s="68">
         <f t="shared" si="24"/>
-        <v>-184</v>
+        <v>60</v>
       </c>
       <c r="AR20" s="68">
         <f t="shared" si="24"/>
-        <v>-43</v>
+        <v>0</v>
       </c>
       <c r="AS20" s="68">
         <f t="shared" ref="AS20:AS25" si="25">AP19-AP20</f>
-        <v>515</v>
+        <v>65</v>
       </c>
       <c r="AT20" s="92">
         <v>15</v>
@@ -5672,23 +5738,23 @@
       <c r="BB20" s="84"/>
       <c r="BC20" s="81">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.80423888E-2</v>
       </c>
       <c r="BD20" s="69">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25.981039871999997</v>
       </c>
       <c r="BE20" s="69">
         <f t="shared" si="17"/>
-        <v>1580</v>
-      </c>
-      <c r="BF20" s="70" t="e">
+        <v>1911.27</v>
+      </c>
+      <c r="BF20" s="70">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BG20" s="70" t="e">
+        <v>0.1276638046953073</v>
+      </c>
+      <c r="BG20" s="70">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>0.14352941176470588</v>
       </c>
       <c r="BH20" s="70">
         <f t="shared" si="5"/>
@@ -5708,7 +5774,7 @@
       </c>
       <c r="BL20" s="70">
         <f t="shared" si="19"/>
-        <v>11.85</v>
+        <v>0</v>
       </c>
       <c r="BM20" s="82" t="str">
         <f t="shared" si="14"/>
@@ -5724,7 +5790,7 @@
       </c>
       <c r="BP20" s="73">
         <f t="shared" si="7"/>
-        <v>11.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5788,15 +5854,15 @@
       <c r="AP21" s="67"/>
       <c r="AQ21" s="68">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>-244</v>
       </c>
       <c r="AR21" s="68">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>-43</v>
       </c>
       <c r="AS21" s="68">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="AT21" s="92">
         <v>15</v>
@@ -6527,15 +6593,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
@@ -6551,6 +6608,15 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6777,26 +6843,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
+++ b/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-038-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="559" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{123E69FD-5553-4086-AA0E-C4845C436807}"/>
+  <xr:revisionPtr revIDLastSave="582" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A92E14B7-5C28-4C96-B3B1-B1EE03567F49}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AM20" s="68">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3.9685397916666663E-2</v>
       </c>
       <c r="AN20" s="67">
         <v>244</v>
@@ -5733,9 +5733,17 @@
       <c r="AY20" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ20" s="81"/>
-      <c r="BA20" s="69"/>
-      <c r="BB20" s="84"/>
+      <c r="AZ20" s="81">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="BA20" s="99">
+        <f>BJ20*24*60/BE20</f>
+        <v>8.8711852715143927E-3</v>
+      </c>
+      <c r="BB20" s="99">
+        <f>BM20/BE20</f>
+        <v>9.9999999999999995E-8</v>
+      </c>
       <c r="BC20" s="81">
         <f t="shared" si="0"/>
         <v>1.80423888E-2</v>
@@ -5758,15 +5766,14 @@
       </c>
       <c r="BH20" s="70">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57.146972999999988</v>
       </c>
       <c r="BI20" s="70">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BJ20" s="70" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <v>3.9685397916666663E-2</v>
+      </c>
+      <c r="BJ20" s="70">
+        <v>1.1774465467977301E-2</v>
       </c>
       <c r="BK20" s="71" t="str">
         <f t="shared" si="6"/>
@@ -5776,17 +5783,16 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BM20" s="82" t="str">
-        <f t="shared" si="14"/>
-        <v/>
+      <c r="BM20" s="82">
+        <v>1.91127E-4</v>
       </c>
       <c r="BN20" s="75">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>103.07895562770562</v>
       </c>
       <c r="BO20" s="72">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3.9685397916666663E-2</v>
       </c>
       <c r="BP20" s="73">
         <f t="shared" si="7"/>
@@ -5812,57 +5818,119 @@
         <v>4309.7</v>
       </c>
       <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="67"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="67"/>
-      <c r="Q21" s="67"/>
+      <c r="I21" s="67">
+        <v>4097.625</v>
+      </c>
+      <c r="J21" s="67">
+        <v>25.3</v>
+      </c>
+      <c r="K21" s="67">
+        <v>24</v>
+      </c>
+      <c r="L21" s="67">
+        <v>94.8</v>
+      </c>
+      <c r="M21" s="67">
+        <v>18.8</v>
+      </c>
+      <c r="N21" s="67">
+        <v>458</v>
+      </c>
+      <c r="O21" s="67">
+        <v>3</v>
+      </c>
+      <c r="P21" s="67">
+        <v>0.25</v>
+      </c>
+      <c r="Q21" s="67">
+        <v>7.34</v>
+      </c>
       <c r="R21" s="67"/>
-      <c r="S21" s="67"/>
-      <c r="T21" s="67"/>
-      <c r="U21" s="67"/>
-      <c r="V21" s="67"/>
-      <c r="W21" s="67"/>
-      <c r="X21" s="67"/>
-      <c r="Y21" s="67"/>
-      <c r="Z21" s="67"/>
-      <c r="AA21" s="67"/>
-      <c r="AB21" s="67"/>
-      <c r="AC21" s="67"/>
-      <c r="AD21" s="96"/>
-      <c r="AE21" s="91"/>
-      <c r="AF21" s="67"/>
-      <c r="AG21" s="67"/>
+      <c r="S21" s="67">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="T21" s="67">
+        <v>3.94</v>
+      </c>
+      <c r="U21" s="67">
+        <v>1.89</v>
+      </c>
+      <c r="V21" s="67">
+        <v>7.0620000000000003</v>
+      </c>
+      <c r="W21" s="67">
+        <v>165.6</v>
+      </c>
+      <c r="X21" s="67">
+        <v>9</v>
+      </c>
+      <c r="Y21" s="67">
+        <v>1.51</v>
+      </c>
+      <c r="Z21" s="67">
+        <v>165.7</v>
+      </c>
+      <c r="AA21" s="67">
+        <v>45.5</v>
+      </c>
+      <c r="AB21" s="67">
+        <v>145.19999999999999</v>
+      </c>
+      <c r="AC21" s="67">
+        <v>7.3</v>
+      </c>
+      <c r="AD21" s="96">
+        <v>7.1</v>
+      </c>
+      <c r="AE21" s="91">
+        <v>300</v>
+      </c>
+      <c r="AF21" s="67">
+        <v>49.9</v>
+      </c>
+      <c r="AG21" s="67">
+        <v>7.1</v>
+      </c>
       <c r="AH21" s="68">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI21" s="67"/>
-      <c r="AJ21" s="67"/>
-      <c r="AK21" s="67"/>
-      <c r="AL21" s="67"/>
+        <v>0.499</v>
+      </c>
+      <c r="AI21" s="67">
+        <v>34</v>
+      </c>
+      <c r="AJ21" s="67">
+        <v>32.640999999999998</v>
+      </c>
+      <c r="AK21" s="67">
+        <v>8.1745999999999999</v>
+      </c>
+      <c r="AL21" s="67">
+        <v>7</v>
+      </c>
       <c r="AM21" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="67"/>
-      <c r="AO21" s="67"/>
-      <c r="AP21" s="67"/>
+      <c r="AN21" s="67">
+        <v>303</v>
+      </c>
+      <c r="AO21" s="67">
+        <v>43</v>
+      </c>
+      <c r="AP21" s="67">
+        <v>387</v>
+      </c>
       <c r="AQ21" s="68">
         <f t="shared" si="24"/>
-        <v>-244</v>
+        <v>59</v>
       </c>
       <c r="AR21" s="68">
         <f t="shared" si="24"/>
-        <v>-43</v>
+        <v>0</v>
       </c>
       <c r="AS21" s="68">
         <f t="shared" si="25"/>
-        <v>450</v>
+        <v>63</v>
       </c>
       <c r="AT21" s="92">
         <v>15</v>
@@ -5887,23 +5955,23 @@
       <c r="BB21" s="84"/>
       <c r="BC21" s="81">
         <f t="shared" ref="BC21:BC25" si="26">AY21*K21*BE21/1000</f>
-        <v>0</v>
+        <v>1.880462976E-2</v>
       </c>
       <c r="BD21" s="69">
         <f t="shared" ref="BD21:BD25" si="27">BC21*24*60</f>
-        <v>0</v>
+        <v>27.078666854400002</v>
       </c>
       <c r="BE21" s="69">
         <f t="shared" si="17"/>
-        <v>1565</v>
-      </c>
-      <c r="BF21" s="70" t="e">
+        <v>1958.8155999999999</v>
+      </c>
+      <c r="BF21" s="70">
         <f t="shared" ref="BF21:BF25" si="28">IF(ISBLANK(AN21),NA(),IFERROR(AN21/BE21,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="BG21" s="70" t="e">
+        <v>0.15468531085825538</v>
+      </c>
+      <c r="BG21" s="70">
         <f t="shared" ref="BG21:BG25" si="29">IF(ISBLANK(AN21),NA(),AN21/AU21)</f>
-        <v>#N/A</v>
+        <v>0.17823529411764705</v>
       </c>
       <c r="BH21" s="70">
         <f t="shared" ref="BH21:BH25" si="30">AM21*24*60</f>
@@ -5923,7 +5991,7 @@
       </c>
       <c r="BL21" s="70">
         <f t="shared" si="19"/>
-        <v>11.737500000000001</v>
+        <v>0</v>
       </c>
       <c r="BM21" s="82" t="str">
         <f t="shared" si="14"/>
@@ -5939,7 +6007,7 @@
       </c>
       <c r="BP21" s="73">
         <f t="shared" ref="BP21:BP25" si="32">IF(BL21&lt;&gt;"",BL21,BM21)</f>
-        <v>11.737500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6003,15 +6071,15 @@
       <c r="AP22" s="67"/>
       <c r="AQ22" s="68">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>-303</v>
       </c>
       <c r="AR22" s="68">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>-43</v>
       </c>
       <c r="AS22" s="68">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="AT22" s="92">
         <v>15</v>
@@ -6847,14 +6915,14 @@
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
+++ b/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-038-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="582" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A92E14B7-5C28-4C96-B3B1-B1EE03567F49}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1717BD6-BA1F-44AB-8241-E5407EB9F307}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2359,7 +2359,7 @@
         <v>1.685E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>77</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>6.9716747687283455E-3</v>
       </c>
       <c r="BJ5" s="60" t="str">
-        <f t="shared" ref="BJ5:BJ21" si="13">IF(B5="Julia",BA5*BE5/24/60,"")</f>
+        <f t="shared" ref="BJ5:BJ17" si="13">IF(B5="Julia",BA5*BE5/24/60,"")</f>
         <v/>
       </c>
       <c r="BK5" s="60" t="str">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="BM5" s="77" t="str">
-        <f t="shared" ref="BM5:BM21" si="14">IF(B5="Julia",BB5*BE5,"")</f>
+        <f t="shared" ref="BM5:BM17" si="14">IF(B5="Julia",BB5*BE5,"")</f>
         <v/>
       </c>
       <c r="BN5" s="28">
@@ -2645,14 +2645,14 @@
       <c r="AA6" s="7">
         <v>24.5</v>
       </c>
-      <c r="AB6" s="7">
-        <v>81.3</v>
-      </c>
-      <c r="AC6" s="7">
-        <v>47.7</v>
-      </c>
-      <c r="AD6" s="18">
-        <v>7.0839999999999996</v>
+      <c r="AB6" s="40">
+        <v>300</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>51.2</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>7.11</v>
       </c>
       <c r="AE6" s="42">
         <v>300</v>
@@ -5813,7 +5813,9 @@
         <v>8</v>
       </c>
       <c r="E21" s="65"/>
-      <c r="F21" s="66"/>
+      <c r="F21" s="66">
+        <v>45499.369444444397</v>
+      </c>
       <c r="G21" s="64">
         <v>4309.7</v>
       </c>
@@ -5909,7 +5911,7 @@
       </c>
       <c r="AM21" s="68">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4.1624831499999994E-2</v>
       </c>
       <c r="AN21" s="67">
         <v>303</v>
@@ -5950,9 +5952,17 @@
       <c r="AY21" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ21" s="81"/>
-      <c r="BA21" s="69"/>
-      <c r="BB21" s="84"/>
+      <c r="AZ21" s="81">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="BA21" s="99">
+        <f>BJ21*24*60/BE21</f>
+        <v>1.1338377715141717E-2</v>
+      </c>
+      <c r="BB21" s="99">
+        <f>BM21/BE21</f>
+        <v>1.0000000000000001E-7</v>
+      </c>
       <c r="BC21" s="81">
         <f t="shared" ref="BC21:BC25" si="26">AY21*K21*BE21/1000</f>
         <v>1.880462976E-2</v>
@@ -5975,15 +5985,14 @@
       </c>
       <c r="BH21" s="70">
         <f t="shared" ref="BH21:BH25" si="30">AM21*24*60</f>
-        <v>0</v>
+        <v>59.939757359999994</v>
       </c>
       <c r="BI21" s="70">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="BJ21" s="70" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <v>4.1624831499999994E-2</v>
+      </c>
+      <c r="BJ21" s="70">
+        <v>1.54234660743833E-2</v>
       </c>
       <c r="BK21" s="71" t="str">
         <f t="shared" ref="BK21:BK25" si="31">IF(B21="No MPC", AY21*K21*BE21/1000,"")</f>
@@ -5993,17 +6002,16 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BM21" s="82" t="str">
-        <f t="shared" si="14"/>
-        <v/>
+      <c r="BM21" s="82">
+        <v>1.9588156E-4</v>
       </c>
       <c r="BN21" s="75">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>108.11644545454544</v>
       </c>
       <c r="BO21" s="72">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4.1624831499999994E-2</v>
       </c>
       <c r="BP21" s="73">
         <f t="shared" ref="BP21:BP25" si="32">IF(BL21&lt;&gt;"",BL21,BM21)</f>
@@ -6024,62 +6032,126 @@
         <v>9</v>
       </c>
       <c r="E22" s="65"/>
-      <c r="F22" s="66"/>
+      <c r="F22" s="66">
+        <v>45500.443576388898</v>
+      </c>
       <c r="G22" s="64">
         <v>4805.7299999999996</v>
       </c>
       <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="67"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="67"/>
-      <c r="Q22" s="67"/>
+      <c r="I22" s="67">
+        <v>4453.3999999999996</v>
+      </c>
+      <c r="J22" s="67">
+        <v>25.2</v>
+      </c>
+      <c r="K22" s="67">
+        <v>23.6</v>
+      </c>
+      <c r="L22" s="67">
+        <v>93.6</v>
+      </c>
+      <c r="M22" s="67">
+        <v>18.8</v>
+      </c>
+      <c r="N22" s="67">
+        <v>486</v>
+      </c>
+      <c r="O22" s="67">
+        <v>3.91</v>
+      </c>
+      <c r="P22" s="67">
+        <v>0.23</v>
+      </c>
+      <c r="Q22" s="67">
+        <v>6.91</v>
+      </c>
       <c r="R22" s="67"/>
-      <c r="S22" s="67"/>
-      <c r="T22" s="67"/>
-      <c r="U22" s="67"/>
-      <c r="V22" s="67"/>
-      <c r="W22" s="67"/>
-      <c r="X22" s="67"/>
-      <c r="Y22" s="67"/>
-      <c r="Z22" s="67"/>
-      <c r="AA22" s="67"/>
-      <c r="AB22" s="67"/>
-      <c r="AC22" s="67"/>
-      <c r="AD22" s="96"/>
-      <c r="AE22" s="91"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="67"/>
+      <c r="S22" s="67">
+        <v>1.72</v>
+      </c>
+      <c r="T22" s="67">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="U22" s="67">
+        <v>2.09</v>
+      </c>
+      <c r="V22" s="67">
+        <v>7.0579999999999998</v>
+      </c>
+      <c r="W22" s="67">
+        <v>164.4</v>
+      </c>
+      <c r="X22" s="67">
+        <v>1.7</v>
+      </c>
+      <c r="Y22" s="67">
+        <v>1.52</v>
+      </c>
+      <c r="Z22" s="67">
+        <v>174.3</v>
+      </c>
+      <c r="AA22" s="67">
+        <v>44.7</v>
+      </c>
+      <c r="AB22" s="67">
+        <v>144.19999999999999</v>
+      </c>
+      <c r="AC22" s="67">
+        <v>1.4</v>
+      </c>
+      <c r="AD22" s="96">
+        <v>7.0960000000000001</v>
+      </c>
+      <c r="AE22" s="91">
+        <v>300</v>
+      </c>
+      <c r="AF22" s="67">
+        <v>51.3</v>
+      </c>
+      <c r="AG22" s="67">
+        <v>7.1</v>
+      </c>
       <c r="AH22" s="68">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI22" s="67"/>
-      <c r="AJ22" s="67"/>
-      <c r="AK22" s="67"/>
-      <c r="AL22" s="67"/>
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="AI22" s="67">
+        <v>34</v>
+      </c>
+      <c r="AJ22" s="67">
+        <v>35.975999999999999</v>
+      </c>
+      <c r="AK22" s="67">
+        <v>8.1745999999999999</v>
+      </c>
+      <c r="AL22" s="67">
+        <v>8</v>
+      </c>
       <c r="AM22" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN22" s="67"/>
-      <c r="AO22" s="67"/>
-      <c r="AP22" s="67"/>
+      <c r="AN22" s="67">
+        <v>367</v>
+      </c>
+      <c r="AO22" s="67">
+        <v>43</v>
+      </c>
+      <c r="AP22" s="67">
+        <v>316</v>
+      </c>
       <c r="AQ22" s="68">
         <f t="shared" si="24"/>
-        <v>-303</v>
+        <v>64</v>
       </c>
       <c r="AR22" s="68">
         <f t="shared" si="24"/>
-        <v>-43</v>
+        <v>0</v>
       </c>
       <c r="AS22" s="68">
         <f t="shared" si="25"/>
-        <v>387</v>
+        <v>71</v>
       </c>
       <c r="AT22" s="92">
         <v>15</v>
@@ -6100,27 +6172,33 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AZ22" s="81"/>
-      <c r="BA22" s="69"/>
-      <c r="BB22" s="84"/>
+      <c r="BA22" s="99">
+        <f>BJ22*24*60/BE22</f>
+        <v>1.3595595557568218E-2</v>
+      </c>
+      <c r="BB22" s="99">
+        <f>BM22/BE22</f>
+        <v>1.0000000000000001E-7</v>
+      </c>
       <c r="BC22" s="81">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1.8994701664E-2</v>
       </c>
       <c r="BD22" s="69">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>27.352370396160001</v>
       </c>
       <c r="BE22" s="69">
         <f t="shared" si="17"/>
-        <v>1550</v>
-      </c>
-      <c r="BF22" s="70" t="e">
+        <v>2012.1505999999999</v>
+      </c>
+      <c r="BF22" s="70">
         <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BG22" s="70" t="e">
+        <v>0.18239191440243091</v>
+      </c>
+      <c r="BG22" s="70">
         <f t="shared" si="29"/>
-        <v>#N/A</v>
+        <v>0.21588235294117647</v>
       </c>
       <c r="BH22" s="70">
         <f t="shared" si="30"/>
@@ -6130,9 +6208,8 @@
         <f t="shared" ref="BI22:BI25" si="33">IF(B22="Python",AZ22*BE22/24/60,"")</f>
         <v>0</v>
       </c>
-      <c r="BJ22" s="70" t="str">
-        <f t="shared" ref="BJ22:BJ25" si="34">IF(B22="Julia",BA22*BE22/24/60,"")</f>
-        <v/>
+      <c r="BJ22" s="70">
+        <v>1.8997490110082099E-2</v>
       </c>
       <c r="BK22" s="71" t="str">
         <f t="shared" si="31"/>
@@ -6140,11 +6217,10 @@
       </c>
       <c r="BL22" s="70">
         <f t="shared" si="19"/>
-        <v>11.625</v>
-      </c>
-      <c r="BM22" s="82" t="str">
-        <f t="shared" ref="BM22:BM25" si="35">IF(B22="Julia",BB22*BE22,"")</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="BM22" s="82">
+        <v>2.0121506000000001E-4</v>
       </c>
       <c r="BN22" s="75">
         <f t="shared" si="11"/>
@@ -6156,7 +6232,7 @@
       </c>
       <c r="BP22" s="73">
         <f t="shared" si="32"/>
-        <v>11.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6173,54 +6249,118 @@
         <v>10</v>
       </c>
       <c r="E23" s="65"/>
-      <c r="F23" s="66"/>
+      <c r="F23" s="66">
+        <v>45501.511122685202</v>
+      </c>
       <c r="G23" s="97">
         <v>5497.99</v>
       </c>
       <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="67"/>
-      <c r="L23" s="67"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="67"/>
-      <c r="Q23" s="67"/>
+      <c r="I23" s="67">
+        <v>4845.16</v>
+      </c>
+      <c r="J23" s="67">
+        <v>26.5</v>
+      </c>
+      <c r="K23" s="67">
+        <v>24.4</v>
+      </c>
+      <c r="L23" s="67">
+        <v>92.1</v>
+      </c>
+      <c r="M23" s="67">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="N23" s="67">
+        <v>483</v>
+      </c>
+      <c r="O23" s="67">
+        <v>4.24</v>
+      </c>
+      <c r="P23" s="67">
+        <v>0.2</v>
+      </c>
+      <c r="Q23" s="67">
+        <v>3.09</v>
+      </c>
       <c r="R23" s="67"/>
-      <c r="S23" s="67"/>
-      <c r="T23" s="67"/>
-      <c r="U23" s="67"/>
-      <c r="V23" s="67"/>
-      <c r="W23" s="67"/>
-      <c r="X23" s="67"/>
-      <c r="Y23" s="67"/>
-      <c r="Z23" s="67"/>
-      <c r="AA23" s="67"/>
-      <c r="AB23" s="67"/>
-      <c r="AC23" s="67"/>
-      <c r="AD23" s="96"/>
-      <c r="AE23" s="91"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="67"/>
+      <c r="S23" s="67">
+        <v>1.59</v>
+      </c>
+      <c r="T23" s="67">
+        <v>4.58</v>
+      </c>
+      <c r="U23" s="67">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="V23" s="67">
+        <v>7.0579999999999998</v>
+      </c>
+      <c r="W23" s="67">
+        <v>163.80000000000001</v>
+      </c>
+      <c r="X23" s="67">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="67">
+        <v>1.49</v>
+      </c>
+      <c r="Z23" s="67">
+        <v>182.7</v>
+      </c>
+      <c r="AA23" s="67">
+        <v>44.6</v>
+      </c>
+      <c r="AB23" s="67">
+        <v>143.6</v>
+      </c>
+      <c r="AC23" s="67">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="96">
+        <v>7.0960000000000001</v>
+      </c>
+      <c r="AE23" s="91">
+        <v>300</v>
+      </c>
+      <c r="AF23" s="67">
+        <v>48.9</v>
+      </c>
+      <c r="AG23" s="67">
+        <v>7.1</v>
+      </c>
       <c r="AH23" s="68">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="67"/>
-      <c r="AK23" s="67"/>
-      <c r="AL23" s="67"/>
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="AI23" s="67">
+        <v>34</v>
+      </c>
+      <c r="AJ23" s="67">
+        <v>40.124000000000002</v>
+      </c>
+      <c r="AK23" s="67">
+        <v>8.1745999999999999</v>
+      </c>
+      <c r="AL23" s="67">
+        <v>10</v>
+      </c>
       <c r="AM23" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN23" s="67"/>
-      <c r="AO23" s="67"/>
-      <c r="AP23" s="67"/>
+      <c r="AN23" s="67">
+        <v>397</v>
+      </c>
+      <c r="AO23" s="67">
+        <v>43</v>
+      </c>
+      <c r="AP23" s="67">
+        <v>284</v>
+      </c>
       <c r="AQ23" s="68">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AR23" s="68">
         <f t="shared" si="24"/>
@@ -6228,7 +6368,7 @@
       </c>
       <c r="AS23" s="68">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT23" s="92">
         <v>15</v>
@@ -6253,23 +6393,23 @@
       <c r="BB23" s="84"/>
       <c r="BC23" s="81">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1.9844994336E-2</v>
       </c>
       <c r="BD23" s="69">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>28.576791843840002</v>
       </c>
       <c r="BE23" s="69">
         <f t="shared" si="17"/>
-        <v>1535</v>
-      </c>
-      <c r="BF23" s="70" t="e">
+        <v>2033.2986000000001</v>
+      </c>
+      <c r="BF23" s="70">
         <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BG23" s="70" t="e">
+        <v>0.19524923688040702</v>
+      </c>
+      <c r="BG23" s="70">
         <f t="shared" si="29"/>
-        <v>#N/A</v>
+        <v>0.23352941176470587</v>
       </c>
       <c r="BH23" s="70">
         <f t="shared" si="30"/>
@@ -6280,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="BJ23" s="70" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="BJ23:BJ25" si="34">IF(B23="Julia",BA23*BE23/24/60,"")</f>
         <v/>
       </c>
       <c r="BK23" s="71" t="str">
@@ -6289,10 +6429,10 @@
       </c>
       <c r="BL23" s="70">
         <f t="shared" si="19"/>
-        <v>11.512499999999999</v>
+        <v>0</v>
       </c>
       <c r="BM23" s="82" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="BM23:BM25" si="35">IF(B23="Julia",BB23*BE23,"")</f>
         <v/>
       </c>
       <c r="BN23" s="75">
@@ -6305,7 +6445,7 @@
       </c>
       <c r="BP23" s="73">
         <f t="shared" si="32"/>
-        <v>11.512499999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6369,15 +6509,15 @@
       <c r="AP24" s="67"/>
       <c r="AQ24" s="68">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>-397</v>
       </c>
       <c r="AR24" s="68">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>-43</v>
       </c>
       <c r="AS24" s="68">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="AT24" s="92">
         <v>15</v>
@@ -6661,6 +6801,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
@@ -6676,15 +6825,6 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6911,26 +7051,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
+++ b/data/mr24-038-experiment/MR24-038-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-038-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="613" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1717BD6-BA1F-44AB-8241-E5407EB9F307}"/>
+  <xr:revisionPtr revIDLastSave="657" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31AA43A5-876B-43DE-A611-C88ACE7FB4D7}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -1049,7 +1049,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1171,6 +1171,7 @@
     <xf numFmtId="0" fontId="26" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="41" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1635,104 +1636,104 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BP28"/>
-  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="10.6640625" customWidth="1"/>
+    <col min="2" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="5" width="49" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" customWidth="1"/>
-    <col min="7" max="18" width="12.6640625" customWidth="1"/>
-    <col min="19" max="19" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="65" width="12.6640625" customWidth="1"/>
-    <col min="66" max="66" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="18" width="12.7109375" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="65" width="12.7109375" customWidth="1"/>
+    <col min="66" max="66" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="102" t="s">
+    <row r="1" spans="1:68" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="102" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="103"/>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="103"/>
-      <c r="AA1" s="103"/>
-      <c r="AB1" s="103"/>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="104"/>
-      <c r="AE1" s="117" t="s">
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="104"/>
+      <c r="T1" s="104"/>
+      <c r="U1" s="104"/>
+      <c r="V1" s="104"/>
+      <c r="W1" s="104"/>
+      <c r="X1" s="104"/>
+      <c r="Y1" s="104"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="104"/>
+      <c r="AB1" s="104"/>
+      <c r="AC1" s="104"/>
+      <c r="AD1" s="105"/>
+      <c r="AE1" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="118"/>
-      <c r="AG1" s="118"/>
-      <c r="AH1" s="118"/>
-      <c r="AI1" s="118"/>
-      <c r="AJ1" s="118"/>
-      <c r="AK1" s="118"/>
-      <c r="AL1" s="118"/>
-      <c r="AM1" s="118"/>
-      <c r="AN1" s="118"/>
-      <c r="AO1" s="118"/>
-      <c r="AP1" s="118"/>
-      <c r="AQ1" s="118"/>
-      <c r="AR1" s="118"/>
-      <c r="AS1" s="118"/>
-      <c r="AT1" s="119"/>
-      <c r="AU1" s="111" t="s">
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
+      <c r="AI1" s="119"/>
+      <c r="AJ1" s="119"/>
+      <c r="AK1" s="119"/>
+      <c r="AL1" s="119"/>
+      <c r="AM1" s="119"/>
+      <c r="AN1" s="119"/>
+      <c r="AO1" s="119"/>
+      <c r="AP1" s="119"/>
+      <c r="AQ1" s="119"/>
+      <c r="AR1" s="119"/>
+      <c r="AS1" s="119"/>
+      <c r="AT1" s="120"/>
+      <c r="AU1" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="AV1" s="112"/>
-      <c r="AW1" s="112"/>
-      <c r="AX1" s="112"/>
-      <c r="AY1" s="113"/>
-      <c r="AZ1" s="114" t="s">
+      <c r="AV1" s="113"/>
+      <c r="AW1" s="113"/>
+      <c r="AX1" s="113"/>
+      <c r="AY1" s="114"/>
+      <c r="AZ1" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="BA1" s="115"/>
-      <c r="BB1" s="116"/>
-      <c r="BC1" s="108" t="s">
+      <c r="BA1" s="116"/>
+      <c r="BB1" s="117"/>
+      <c r="BC1" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="BD1" s="109"/>
-      <c r="BE1" s="109"/>
-      <c r="BF1" s="109"/>
-      <c r="BG1" s="109"/>
-      <c r="BH1" s="109"/>
-      <c r="BI1" s="109"/>
-      <c r="BJ1" s="109"/>
-      <c r="BK1" s="109"/>
-      <c r="BL1" s="109"/>
-      <c r="BM1" s="110"/>
-      <c r="BN1" s="105" t="s">
+      <c r="BD1" s="110"/>
+      <c r="BE1" s="110"/>
+      <c r="BF1" s="110"/>
+      <c r="BG1" s="110"/>
+      <c r="BH1" s="110"/>
+      <c r="BI1" s="110"/>
+      <c r="BJ1" s="110"/>
+      <c r="BK1" s="110"/>
+      <c r="BL1" s="110"/>
+      <c r="BM1" s="111"/>
+      <c r="BN1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="BO1" s="106"/>
-      <c r="BP1" s="107"/>
+      <c r="BO1" s="107"/>
+      <c r="BP1" s="108"/>
     </row>
-    <row r="2" spans="1:68" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:68" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>7</v>
       </c>
@@ -1938,7 +1939,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>74</v>
       </c>
@@ -2149,7 +2150,7 @@
         <v>1.685E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>76</v>
       </c>
@@ -2359,7 +2360,7 @@
         <v>1.685E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>77</v>
       </c>
@@ -2569,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>79</v>
       </c>
@@ -2780,7 +2781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>74</v>
       </c>
@@ -2997,7 +2998,7 @@
         <v>16.832071720300799</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>76</v>
       </c>
@@ -3216,7 +3217,7 @@
         <v>18.617318338672099</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
@@ -3430,7 +3431,7 @@
         <v>16.512855499999997</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>79</v>
       </c>
@@ -3644,7 +3645,7 @@
         <v>17.037286999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>74</v>
       </c>
@@ -3863,7 +3864,7 @@
         <v>12.1026345792793</v>
       </c>
     </row>
-    <row r="12" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>77</v>
       </c>
@@ -4079,7 +4080,7 @@
         <v>12.887707500000001</v>
       </c>
     </row>
-    <row r="13" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>79</v>
       </c>
@@ -4295,7 +4296,7 @@
         <v>10.962813374999998</v>
       </c>
     </row>
-    <row r="14" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>74</v>
       </c>
@@ -4512,7 +4513,7 @@
         <v>11.3869050015914</v>
       </c>
     </row>
-    <row r="15" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>77</v>
       </c>
@@ -4726,7 +4727,7 @@
         <v>13.070538324999999</v>
       </c>
     </row>
-    <row r="16" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:68" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>74</v>
       </c>
@@ -4949,7 +4950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>77</v>
       </c>
@@ -5142,7 +5143,7 @@
         <v>7.4749999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="64" t="s">
         <v>74</v>
       </c>
@@ -5299,11 +5300,11 @@
         <v>3.7932984327519299E-2</v>
       </c>
       <c r="BA18" s="99">
-        <f>BJ18*24*60/BE18</f>
+        <f t="shared" ref="BA18:BA24" si="24">BJ18*24*60/BE18</f>
         <v>1.4359799331487877E-2</v>
       </c>
       <c r="BB18" s="99">
-        <f>BM18/BE18</f>
+        <f t="shared" ref="BB18:BB24" si="25">BM18/BE18</f>
         <v>9.9668112222320009E-8</v>
       </c>
       <c r="BC18" s="81">
@@ -5361,7 +5362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="64" t="s">
         <v>74</v>
       </c>
@@ -5485,11 +5486,11 @@
         <v>515</v>
       </c>
       <c r="AQ19" s="68">
-        <f t="shared" ref="AQ19:AR25" si="24">AN19-AN18</f>
+        <f t="shared" ref="AQ19:AR25" si="26">AN19-AN18</f>
         <v>71</v>
       </c>
       <c r="AR19" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AS19" s="68">
@@ -5518,11 +5519,11 @@
         <v>3.1398117003682703E-2</v>
       </c>
       <c r="BA19" s="99">
-        <f>BJ19*24*60/BE19</f>
+        <f t="shared" si="24"/>
         <v>5.8037926537741662E-3</v>
       </c>
       <c r="BB19" s="99">
-        <f>BM19/BE19</f>
+        <f t="shared" si="25"/>
         <v>9.9999999999999995E-8</v>
       </c>
       <c r="BC19" s="81">
@@ -5580,7 +5581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="64" t="s">
         <v>74</v>
       </c>
@@ -5704,15 +5705,15 @@
         <v>450</v>
       </c>
       <c r="AQ20" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>60</v>
       </c>
       <c r="AR20" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AS20" s="68">
-        <f t="shared" ref="AS20:AS25" si="25">AP19-AP20</f>
+        <f t="shared" ref="AS20:AS25" si="27">AP19-AP20</f>
         <v>65</v>
       </c>
       <c r="AT20" s="92">
@@ -5737,11 +5738,11 @@
         <v>2.9899999999999999E-2</v>
       </c>
       <c r="BA20" s="99">
-        <f>BJ20*24*60/BE20</f>
+        <f t="shared" si="24"/>
         <v>8.8711852715143927E-3</v>
       </c>
       <c r="BB20" s="99">
-        <f>BM20/BE20</f>
+        <f t="shared" si="25"/>
         <v>9.9999999999999995E-8</v>
       </c>
       <c r="BC20" s="81">
@@ -5799,7 +5800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="64" t="s">
         <v>74</v>
       </c>
@@ -5923,15 +5924,15 @@
         <v>387</v>
       </c>
       <c r="AQ21" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>59</v>
       </c>
       <c r="AR21" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AS21" s="68">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>63</v>
       </c>
       <c r="AT21" s="92">
@@ -5956,19 +5957,19 @@
         <v>3.0599999999999999E-2</v>
       </c>
       <c r="BA21" s="99">
-        <f>BJ21*24*60/BE21</f>
+        <f t="shared" si="24"/>
         <v>1.1338377715141717E-2</v>
       </c>
       <c r="BB21" s="99">
-        <f>BM21/BE21</f>
+        <f t="shared" si="25"/>
         <v>1.0000000000000001E-7</v>
       </c>
       <c r="BC21" s="81">
-        <f t="shared" ref="BC21:BC25" si="26">AY21*K21*BE21/1000</f>
+        <f t="shared" ref="BC21:BC25" si="28">AY21*K21*BE21/1000</f>
         <v>1.880462976E-2</v>
       </c>
       <c r="BD21" s="69">
-        <f t="shared" ref="BD21:BD25" si="27">BC21*24*60</f>
+        <f t="shared" ref="BD21:BD25" si="29">BC21*24*60</f>
         <v>27.078666854400002</v>
       </c>
       <c r="BE21" s="69">
@@ -5976,15 +5977,15 @@
         <v>1958.8155999999999</v>
       </c>
       <c r="BF21" s="70">
-        <f t="shared" ref="BF21:BF25" si="28">IF(ISBLANK(AN21),NA(),IFERROR(AN21/BE21,0))</f>
+        <f t="shared" ref="BF21:BF25" si="30">IF(ISBLANK(AN21),NA(),IFERROR(AN21/BE21,0))</f>
         <v>0.15468531085825538</v>
       </c>
       <c r="BG21" s="70">
-        <f t="shared" ref="BG21:BG25" si="29">IF(ISBLANK(AN21),NA(),AN21/AU21)</f>
+        <f t="shared" ref="BG21:BG25" si="31">IF(ISBLANK(AN21),NA(),AN21/AU21)</f>
         <v>0.17823529411764705</v>
       </c>
       <c r="BH21" s="70">
-        <f t="shared" ref="BH21:BH25" si="30">AM21*24*60</f>
+        <f t="shared" ref="BH21:BH25" si="32">AM21*24*60</f>
         <v>59.939757359999994</v>
       </c>
       <c r="BI21" s="70">
@@ -5995,7 +5996,7 @@
         <v>1.54234660743833E-2</v>
       </c>
       <c r="BK21" s="71" t="str">
-        <f t="shared" ref="BK21:BK25" si="31">IF(B21="No MPC", AY21*K21*BE21/1000,"")</f>
+        <f t="shared" ref="BK21:BK25" si="33">IF(B21="No MPC", AY21*K21*BE21/1000,"")</f>
         <v/>
       </c>
       <c r="BL21" s="70">
@@ -6014,11 +6015,11 @@
         <v>4.1624831499999994E-2</v>
       </c>
       <c r="BP21" s="73">
-        <f t="shared" ref="BP21:BP25" si="32">IF(BL21&lt;&gt;"",BL21,BM21)</f>
+        <f t="shared" ref="BP21:BP25" si="34">IF(BL21&lt;&gt;"",BL21,BM21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="64" t="s">
         <v>74</v>
       </c>
@@ -6142,15 +6143,15 @@
         <v>316</v>
       </c>
       <c r="AQ22" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>64</v>
       </c>
       <c r="AR22" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AS22" s="68">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>71</v>
       </c>
       <c r="AT22" s="92">
@@ -6173,19 +6174,19 @@
       </c>
       <c r="AZ22" s="81"/>
       <c r="BA22" s="99">
-        <f>BJ22*24*60/BE22</f>
+        <f t="shared" si="24"/>
         <v>1.3595595557568218E-2</v>
       </c>
       <c r="BB22" s="99">
-        <f>BM22/BE22</f>
+        <f t="shared" si="25"/>
         <v>1.0000000000000001E-7</v>
       </c>
-      <c r="BC22" s="81">
-        <f t="shared" si="26"/>
+      <c r="BC22" s="101">
+        <f t="shared" si="28"/>
         <v>1.8994701664E-2</v>
       </c>
       <c r="BD22" s="69">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>27.352370396160001</v>
       </c>
       <c r="BE22" s="69">
@@ -6193,26 +6194,26 @@
         <v>2012.1505999999999</v>
       </c>
       <c r="BF22" s="70">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.18239191440243091</v>
       </c>
       <c r="BG22" s="70">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.21588235294117647</v>
       </c>
       <c r="BH22" s="70">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BI22" s="70">
-        <f t="shared" ref="BI22:BI25" si="33">IF(B22="Python",AZ22*BE22/24/60,"")</f>
+        <f t="shared" ref="BI22:BI25" si="35">IF(B22="Python",AZ22*BE22/24/60,"")</f>
         <v>0</v>
       </c>
       <c r="BJ22" s="70">
         <v>1.8997490110082099E-2</v>
       </c>
       <c r="BK22" s="71" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="BL22" s="70">
@@ -6231,11 +6232,11 @@
         <v>0</v>
       </c>
       <c r="BP22" s="73">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="64" t="s">
         <v>74</v>
       </c>
@@ -6347,7 +6348,7 @@
       </c>
       <c r="AM23" s="68">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4.6455224958333333E-2</v>
       </c>
       <c r="AN23" s="67">
         <v>397</v>
@@ -6359,15 +6360,15 @@
         <v>284</v>
       </c>
       <c r="AQ23" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>30</v>
       </c>
       <c r="AR23" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AS23" s="68">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32</v>
       </c>
       <c r="AT23" s="92">
@@ -6388,15 +6389,23 @@
       <c r="AY23" s="84">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="AZ23" s="81"/>
-      <c r="BA23" s="69"/>
-      <c r="BB23" s="84"/>
+      <c r="AZ23" s="81">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="BA23" s="99">
+        <f t="shared" si="24"/>
+        <v>2.3999999999999994E-2</v>
+      </c>
+      <c r="BB23" s="99">
+        <f t="shared" si="25"/>
+        <v>4.7067865967358406E-3</v>
+      </c>
       <c r="BC23" s="81">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.9844994336E-2</v>
       </c>
       <c r="BD23" s="69">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>28.576791843840002</v>
       </c>
       <c r="BE23" s="69">
@@ -6404,51 +6413,49 @@
         <v>2033.2986000000001</v>
       </c>
       <c r="BF23" s="70">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.19524923688040702</v>
       </c>
       <c r="BG23" s="70">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.23352941176470587</v>
       </c>
       <c r="BH23" s="70">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="32"/>
+        <v>66.895523940000004</v>
       </c>
       <c r="BI23" s="70">
+        <f t="shared" si="35"/>
+        <v>4.6455224958333333E-2</v>
+      </c>
+      <c r="BJ23" s="70">
+        <v>3.3888309999999998E-2</v>
+      </c>
+      <c r="BK23" s="71" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BJ23" s="70" t="str">
-        <f t="shared" ref="BJ23:BJ25" si="34">IF(B23="Julia",BA23*BE23/24/60,"")</f>
-        <v/>
-      </c>
-      <c r="BK23" s="71" t="str">
-        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BL23" s="70">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="BM23" s="82" t="str">
-        <f t="shared" ref="BM23:BM25" si="35">IF(B23="Julia",BB23*BE23,"")</f>
-        <v/>
+      <c r="BM23" s="82">
+        <v>9.5703025976417493</v>
       </c>
       <c r="BN23" s="75">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>120.66292196969698</v>
       </c>
       <c r="BO23" s="72">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4.6455224958333333E-2</v>
       </c>
       <c r="BP23" s="73">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="64" t="s">
         <v>74</v>
       </c>
@@ -6462,62 +6469,126 @@
         <v>11</v>
       </c>
       <c r="E24" s="65"/>
-      <c r="F24" s="66"/>
+      <c r="F24" s="66">
+        <v>45502.407256944403</v>
+      </c>
       <c r="G24" s="97">
         <v>6057.48</v>
       </c>
       <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="67"/>
-      <c r="K24" s="67"/>
-      <c r="L24" s="67"/>
-      <c r="M24" s="67"/>
-      <c r="N24" s="67"/>
-      <c r="O24" s="67"/>
-      <c r="P24" s="67"/>
-      <c r="Q24" s="67"/>
+      <c r="I24" s="67">
+        <v>5027.07</v>
+      </c>
+      <c r="J24" s="67">
+        <v>28.2</v>
+      </c>
+      <c r="K24" s="67">
+        <v>25.5</v>
+      </c>
+      <c r="L24" s="67">
+        <v>90.3</v>
+      </c>
+      <c r="M24" s="67">
+        <v>18.3</v>
+      </c>
+      <c r="N24" s="67">
+        <v>529</v>
+      </c>
+      <c r="O24" s="67">
+        <v>5</v>
+      </c>
+      <c r="P24" s="67">
+        <v>0.2</v>
+      </c>
+      <c r="Q24" s="67">
+        <v>3.34</v>
+      </c>
       <c r="R24" s="67"/>
-      <c r="S24" s="67"/>
-      <c r="T24" s="67"/>
-      <c r="U24" s="67"/>
-      <c r="V24" s="67"/>
-      <c r="W24" s="67"/>
-      <c r="X24" s="67"/>
-      <c r="Y24" s="67"/>
-      <c r="Z24" s="67"/>
-      <c r="AA24" s="67"/>
-      <c r="AB24" s="67"/>
-      <c r="AC24" s="67"/>
-      <c r="AD24" s="96"/>
-      <c r="AE24" s="91"/>
-      <c r="AF24" s="67"/>
-      <c r="AG24" s="67"/>
+      <c r="S24" s="67">
+        <v>2</v>
+      </c>
+      <c r="T24" s="67">
+        <v>5.05</v>
+      </c>
+      <c r="U24" s="67">
+        <v>3.15</v>
+      </c>
+      <c r="V24" s="67">
+        <v>7.0510000000000002</v>
+      </c>
+      <c r="W24" s="67">
+        <v>164.4</v>
+      </c>
+      <c r="X24" s="67">
+        <v>20.2</v>
+      </c>
+      <c r="Y24" s="67">
+        <v>1.53</v>
+      </c>
+      <c r="Z24" s="67">
+        <v>196.9</v>
+      </c>
+      <c r="AA24" s="67">
+        <v>43.9</v>
+      </c>
+      <c r="AB24" s="67">
+        <v>144.1</v>
+      </c>
+      <c r="AC24" s="67">
+        <v>16.3</v>
+      </c>
+      <c r="AD24" s="96">
+        <v>7.0880000000000001</v>
+      </c>
+      <c r="AE24" s="91">
+        <v>300</v>
+      </c>
+      <c r="AF24" s="67">
+        <v>51.3</v>
+      </c>
+      <c r="AG24" s="67">
+        <v>7.1</v>
+      </c>
       <c r="AH24" s="68">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI24" s="67"/>
-      <c r="AJ24" s="67"/>
-      <c r="AK24" s="67"/>
-      <c r="AL24" s="67"/>
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="AI24" s="67">
+        <v>34</v>
+      </c>
+      <c r="AJ24" s="67">
+        <v>46.48</v>
+      </c>
+      <c r="AK24" s="67">
+        <v>8.17</v>
+      </c>
+      <c r="AL24" s="67">
+        <v>11</v>
+      </c>
       <c r="AM24" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN24" s="67"/>
-      <c r="AO24" s="67"/>
-      <c r="AP24" s="67"/>
+      <c r="AN24" s="67">
+        <v>456</v>
+      </c>
+      <c r="AO24" s="67">
+        <v>43</v>
+      </c>
+      <c r="AP24" s="67">
+        <v>221</v>
+      </c>
       <c r="AQ24" s="68">
-        <f t="shared" si="24"/>
-        <v>-397</v>
+        <f t="shared" si="26"/>
+        <v>59</v>
       </c>
       <c r="AR24" s="68">
-        <f t="shared" si="24"/>
-        <v>-43</v>
+        <f t="shared" si="26"/>
+        <v>0</v>
       </c>
       <c r="AS24" s="68">
-        <f t="shared" si="25"/>
-        <v>284</v>
+        <f t="shared" si="27"/>
+        <v>63</v>
       </c>
       <c r="AT24" s="92">
         <v>15</v>
@@ -6538,51 +6609,55 @@
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="AZ24" s="81"/>
-      <c r="BA24" s="69"/>
-      <c r="BB24" s="84"/>
+      <c r="BA24" s="99">
+        <f t="shared" si="24"/>
+        <v>4.874288693960515E-3</v>
+      </c>
+      <c r="BB24" s="99">
+        <f t="shared" si="25"/>
+        <v>2.4030259080113927E-3</v>
+      </c>
       <c r="BC24" s="81">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>2.1263430000000003E-2</v>
       </c>
       <c r="BD24" s="69">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>30.619339200000006</v>
       </c>
       <c r="BE24" s="69">
         <f t="shared" si="17"/>
-        <v>1520</v>
-      </c>
-      <c r="BF24" s="70" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BG24" s="70" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
+        <v>2084.65</v>
+      </c>
+      <c r="BF24" s="70">
+        <f t="shared" si="30"/>
+        <v>0.21874175521070682</v>
+      </c>
+      <c r="BG24" s="70">
+        <f t="shared" si="31"/>
+        <v>0.26823529411764707</v>
       </c>
       <c r="BH24" s="70">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BI24" s="70">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BJ24" s="70">
+        <v>7.0563791151838796E-3</v>
+      </c>
+      <c r="BK24" s="71" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BJ24" s="70" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="BK24" s="71" t="str">
-        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BL24" s="70">
         <f t="shared" si="19"/>
-        <v>11.4</v>
-      </c>
-      <c r="BM24" s="82" t="str">
-        <f t="shared" si="35"/>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="BM24" s="82">
+        <v>5.0094679591359501</v>
       </c>
       <c r="BN24" s="75">
         <f t="shared" ref="BN24:BN25" si="36">IF(BI24&lt;&gt;"",BI24/0.000385,IF(BJ24&lt;&gt;"",BJ24/0.000385,BK24/0.000385))</f>
@@ -6593,11 +6668,11 @@
         <v>0</v>
       </c>
       <c r="BP24" s="73">
-        <f t="shared" si="32"/>
-        <v>11.4</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="64" t="s">
         <v>74</v>
       </c>
@@ -6611,62 +6686,124 @@
         <v>12</v>
       </c>
       <c r="E25" s="65"/>
-      <c r="F25" s="66"/>
+      <c r="F25" s="66">
+        <v>45503.370902777802</v>
+      </c>
       <c r="G25" s="97">
         <v>6478.05</v>
       </c>
       <c r="H25" s="65"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="67"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="67"/>
-      <c r="M25" s="67"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="67"/>
-      <c r="Q25" s="67"/>
+      <c r="I25" s="67">
+        <v>5083.29</v>
+      </c>
+      <c r="J25" s="67">
+        <v>25.4</v>
+      </c>
+      <c r="K25" s="67">
+        <v>22.3</v>
+      </c>
+      <c r="L25" s="67">
+        <v>87.9</v>
+      </c>
+      <c r="M25" s="67">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="N25" s="67">
+        <v>588</v>
+      </c>
+      <c r="O25" s="67">
+        <v>6.42</v>
+      </c>
+      <c r="P25" s="67">
+        <v>0.24</v>
+      </c>
+      <c r="Q25" s="67">
+        <v>3.39</v>
+      </c>
       <c r="R25" s="67"/>
       <c r="S25" s="67"/>
-      <c r="T25" s="67"/>
-      <c r="U25" s="67"/>
-      <c r="V25" s="67"/>
-      <c r="W25" s="67"/>
-      <c r="X25" s="67"/>
-      <c r="Y25" s="67"/>
-      <c r="Z25" s="67"/>
-      <c r="AA25" s="67"/>
-      <c r="AB25" s="67"/>
-      <c r="AC25" s="67"/>
-      <c r="AD25" s="96"/>
-      <c r="AE25" s="91"/>
-      <c r="AF25" s="67"/>
-      <c r="AG25" s="67"/>
+      <c r="T25" s="67">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="U25" s="67">
+        <v>4.5</v>
+      </c>
+      <c r="V25" s="67">
+        <v>7.0289999999999999</v>
+      </c>
+      <c r="W25" s="67">
+        <v>163.6</v>
+      </c>
+      <c r="X25" s="67">
+        <v>31.8</v>
+      </c>
+      <c r="Y25" s="67">
+        <v>1.69</v>
+      </c>
+      <c r="Z25" s="67">
+        <v>205.5</v>
+      </c>
+      <c r="AA25" s="67">
+        <v>42.9</v>
+      </c>
+      <c r="AB25" s="67">
+        <v>156.5</v>
+      </c>
+      <c r="AC25" s="67">
+        <v>29.7</v>
+      </c>
+      <c r="AD25" s="96">
+        <v>7.0419999999999998</v>
+      </c>
+      <c r="AE25" s="91">
+        <v>300</v>
+      </c>
+      <c r="AF25" s="67">
+        <v>49.3</v>
+      </c>
+      <c r="AG25" s="67">
+        <v>7.1</v>
+      </c>
       <c r="AH25" s="68">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AI25" s="67"/>
-      <c r="AJ25" s="67"/>
-      <c r="AK25" s="67"/>
-      <c r="AL25" s="67"/>
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="AI25" s="67">
+        <v>34</v>
+      </c>
+      <c r="AJ25" s="67">
+        <v>57.96</v>
+      </c>
+      <c r="AK25" s="67">
+        <v>8.17</v>
+      </c>
+      <c r="AL25" s="67">
+        <v>12</v>
+      </c>
       <c r="AM25" s="68">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="67"/>
-      <c r="AO25" s="67"/>
-      <c r="AP25" s="67"/>
+      <c r="AN25" s="67">
+        <v>521</v>
+      </c>
+      <c r="AO25" s="67">
+        <v>43</v>
+      </c>
+      <c r="AP25" s="67">
+        <v>150</v>
+      </c>
       <c r="AQ25" s="68">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f t="shared" si="26"/>
+        <v>65</v>
       </c>
       <c r="AR25" s="68">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AS25" s="68">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>71</v>
       </c>
       <c r="AT25" s="92">
         <v>15</v>
@@ -6690,47 +6827,47 @@
       <c r="BA25" s="65"/>
       <c r="BB25" s="85"/>
       <c r="BC25" s="81">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f t="shared" si="28"/>
+        <v>1.9152399600000002E-2</v>
       </c>
       <c r="BD25" s="69">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>27.579455424000002</v>
       </c>
       <c r="BE25" s="69">
         <f t="shared" si="17"/>
-        <v>1505</v>
-      </c>
-      <c r="BF25" s="70" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="BG25" s="70" t="e">
-        <f t="shared" si="29"/>
-        <v>#N/A</v>
+        <v>2147.13</v>
+      </c>
+      <c r="BF25" s="70">
+        <f t="shared" si="30"/>
+        <v>0.24264949024977528</v>
+      </c>
+      <c r="BG25" s="70">
+        <f t="shared" si="31"/>
+        <v>0.30647058823529411</v>
       </c>
       <c r="BH25" s="70">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BI25" s="70">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="BJ25" s="70" t="str">
+        <f t="shared" ref="BJ25" si="38">IF(B25="Julia",BA25*BE25/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BK25" s="71" t="str">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="BJ25" s="70" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="BK25" s="71" t="str">
-        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BL25" s="70">
         <f t="shared" si="19"/>
-        <v>11.2875</v>
+        <v>0</v>
       </c>
       <c r="BM25" s="82" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="BM25" si="39">IF(B25="Julia",BB25*BE25,"")</f>
         <v/>
       </c>
       <c r="BN25" s="75">
@@ -6742,11 +6879,11 @@
         <v>0</v>
       </c>
       <c r="BP25" s="73">
-        <f t="shared" si="32"/>
-        <v>11.2875</v>
+        <f t="shared" si="34"/>
+        <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:68" x14ac:dyDescent="0.25">
       <c r="S28" s="39"/>
     </row>
   </sheetData>
@@ -6794,7 +6931,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A841E7D6-1405-4AC8-A599-0CE4601ECD66}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6810,24 +6947,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -7050,6 +7169,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
   <ds:schemaRefs>
@@ -7059,23 +7196,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7092,4 +7212,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>